--- a/processed-data/19_data_uploads/03_manifest/manifest_open.xlsx
+++ b/processed-data/19_data_uploads/03_manifest/manifest_open.xlsx
@@ -716,7 +716,7 @@
     <t xml:space="preserve">75e265f618b0d50aba88f78c5acf6a8b</t>
   </si>
   <si>
-    <t xml:space="preserve">R object is a SpatialExperiment (v1.18.1) and can alternatively be retrieved with spatialLIBD::fetch_data('HD_spe_cell') from spatialLIBD &gt;= 1.25.5.</t>
+    <t xml:space="preserve">R object is a SpatialExperiment (v1.18.1) and can alternatively be retrieved with spatialLIBD::fetch_data('habenula_atlas_HD_spe_cell') from spatialLIBD &gt;= 1.25.5.</t>
   </si>
   <si>
     <t xml:space="preserve">habenula_atlas_HD_spe_cell_pseudobulk.rds</t>
@@ -725,7 +725,7 @@
     <t xml:space="preserve">22ebb432a48cb6f85c6f05063f984f7c</t>
   </si>
   <si>
-    <t xml:space="preserve">R object is a SpatialExperiment (v1.18.1) and can alternatively be retrieved with spatialLIBD::fetch_data('HD_spe_cell_pseudobulk') from spatialLIBD &gt;= 1.25.5.</t>
+    <t xml:space="preserve">R object is a SpatialExperiment (v1.18.1) and can alternatively be retrieved with spatialLIBD::fetch_data('habenula_atlas_HD_spe_cell_pseudobulk') from spatialLIBD &gt;= 1.25.5.</t>
   </si>
   <si>
     <t xml:space="preserve">habenula_atlas_visium_spe.rds</t>
@@ -734,7 +734,7 @@
     <t xml:space="preserve">64ce6ae9151c71717bfb169f21d73f32</t>
   </si>
   <si>
-    <t xml:space="preserve">R object is a SpatialExperiment (v1.18.1) and can alternatively be retrieved with spatialLIBD::fetch_data('visium_spe') from spatialLIBD &gt;= 1.25.5.</t>
+    <t xml:space="preserve">R object is a SpatialExperiment (v1.18.1) and can alternatively be retrieved with spatialLIBD::fetch_data('habenula_atlas_visium_spe') from spatialLIBD &gt;= 1.25.5.</t>
   </si>
   <si>
     <t xml:space="preserve">habenula_atlas_visium_spe_pseudobulk.rds</t>
@@ -743,7 +743,7 @@
     <t xml:space="preserve">d2893cd456f38bbeeb3ebd0b88e8585b</t>
   </si>
   <si>
-    <t xml:space="preserve">R object is a SpatialExperiment (v1.18.1) and can alternatively be retrieved with spatialLIBD::fetch_data('visium_spe_pseudobulk') from spatialLIBD &gt;= 1.25.5.</t>
+    <t xml:space="preserve">R object is a SpatialExperiment (v1.18.1) and can alternatively be retrieved with spatialLIBD::fetch_data('habenula_atlas_visium_spe_pseudobulk') from spatialLIBD &gt;= 1.25.5.</t>
   </si>
   <si>
     <t xml:space="preserve">habenula_atlas_snMultiome_seurat_cell.rds</t>
@@ -752,7 +752,7 @@
     <t xml:space="preserve">feb5a2d65918fd3f7b46391e0155cbc9</t>
   </si>
   <si>
-    <t xml:space="preserve">R object is a Seurat (v5.3.0) object and can alternatively be retrieved with spatialLIBD::fetch_data('snMultiome_seurat_cell') from spatialLIBD &gt;= 1.25.5.</t>
+    <t xml:space="preserve">R object is a Seurat (v5.3.0) object and can alternatively be retrieved with spatialLIBD::fetch_data('habenula_atlas_snMultiome_seurat_cell') from spatialLIBD &gt;= 1.25.5.</t>
   </si>
   <si>
     <t xml:space="preserve">habenula_atlas_snMultiome_seurat_metacell.rds</t>
@@ -761,7 +761,7 @@
     <t xml:space="preserve">1bcb148edbd12085bd41358b5cfd6fee</t>
   </si>
   <si>
-    <t xml:space="preserve">R object is a Seurat (v5.3.0) object and can alternatively be retrieved with spatialLIBD::fetch_data('snMultiome_seurat_metacell') from spatialLIBD &gt;= 1.25.5.</t>
+    <t xml:space="preserve">R object is a Seurat (v5.3.0) object and can alternatively be retrieved with spatialLIBD::fetch_data('habenula_atlas_snMultiome_seurat_metacell') from spatialLIBD &gt;= 1.25.5.</t>
   </si>
   <si>
     <t xml:space="preserve">Br3942_barcodes.tsv.gz</t>

--- a/processed-data/19_data_uploads/03_manifest/manifest_open.xlsx
+++ b/processed-data/19_data_uploads/03_manifest/manifest_open.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="653">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="655">
   <si>
     <t xml:space="preserve">subject_name</t>
   </si>
@@ -707,6 +707,9 @@
     <t xml:space="preserve">habenula_atlas_HD_spe_cell.rds</t>
   </si>
   <si>
+    <t xml:space="preserve">10X Genomics Visium-HD; RNAseq_probe</t>
+  </si>
+  <si>
     <t xml:space="preserve">counts</t>
   </si>
   <si>
@@ -729,6 +732,9 @@
   </si>
   <si>
     <t xml:space="preserve">habenula_atlas_visium_spe.rds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10X Genomics Visium; RNAseq_probe</t>
   </si>
   <si>
     <t xml:space="preserve">64ce6ae9151c71717bfb169f21d73f32</t>
@@ -6483,7 +6489,7 @@
       </c>
       <c r="D10"/>
       <c r="E10" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="F10" t="s">
         <v>60</v>
@@ -6498,17 +6504,17 @@
         <v>102</v>
       </c>
       <c r="J10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K10"/>
       <c r="L10" t="s">
         <v>59</v>
       </c>
       <c r="M10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O10" t="s">
         <v>64</v>
@@ -6521,7 +6527,7 @@
         <v>63</v>
       </c>
       <c r="S10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="T10"/>
       <c r="U10"/>
@@ -6532,7 +6538,7 @@
       <c r="Z10"/>
       <c r="AA10"/>
       <c r="AB10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11">
@@ -6540,14 +6546,14 @@
         <v>209</v>
       </c>
       <c r="B11" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C11" t="s">
         <v>69</v>
       </c>
       <c r="D11"/>
       <c r="E11" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="F11" t="s">
         <v>60</v>
@@ -6562,17 +6568,17 @@
         <v>102</v>
       </c>
       <c r="J11" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K11"/>
       <c r="L11" t="s">
         <v>59</v>
       </c>
       <c r="M11" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N11" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O11" t="s">
         <v>64</v>
@@ -6585,7 +6591,7 @@
         <v>63</v>
       </c>
       <c r="S11" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="T11"/>
       <c r="U11"/>
@@ -6596,7 +6602,7 @@
       <c r="Z11"/>
       <c r="AA11"/>
       <c r="AB11" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="12">
@@ -6604,14 +6610,14 @@
         <v>209</v>
       </c>
       <c r="B12" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C12" t="s">
         <v>69</v>
       </c>
       <c r="D12"/>
       <c r="E12" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F12" t="s">
         <v>60</v>
@@ -6626,17 +6632,17 @@
         <v>102</v>
       </c>
       <c r="J12" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K12"/>
       <c r="L12" t="s">
         <v>59</v>
       </c>
       <c r="M12" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N12" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O12" t="s">
         <v>64</v>
@@ -6649,7 +6655,7 @@
         <v>63</v>
       </c>
       <c r="S12" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="T12"/>
       <c r="U12"/>
@@ -6660,7 +6666,7 @@
       <c r="Z12"/>
       <c r="AA12"/>
       <c r="AB12" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="13">
@@ -6668,14 +6674,14 @@
         <v>209</v>
       </c>
       <c r="B13" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C13" t="s">
         <v>69</v>
       </c>
       <c r="D13"/>
       <c r="E13" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F13" t="s">
         <v>60</v>
@@ -6690,17 +6696,17 @@
         <v>102</v>
       </c>
       <c r="J13" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K13"/>
       <c r="L13" t="s">
         <v>59</v>
       </c>
       <c r="M13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O13" t="s">
         <v>64</v>
@@ -6713,7 +6719,7 @@
         <v>63</v>
       </c>
       <c r="S13" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="T13"/>
       <c r="U13"/>
@@ -6724,7 +6730,7 @@
       <c r="Z13"/>
       <c r="AA13"/>
       <c r="AB13" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="14">
@@ -6732,7 +6738,7 @@
         <v>209</v>
       </c>
       <c r="B14" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C14" t="s">
         <v>69</v>
@@ -6754,17 +6760,17 @@
         <v>102</v>
       </c>
       <c r="J14" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K14"/>
       <c r="L14" t="s">
         <v>59</v>
       </c>
       <c r="M14" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N14" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O14" t="s">
         <v>64</v>
@@ -6777,7 +6783,7 @@
         <v>63</v>
       </c>
       <c r="S14" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="T14"/>
       <c r="U14"/>
@@ -6788,7 +6794,7 @@
       <c r="Z14"/>
       <c r="AA14"/>
       <c r="AB14" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="15">
@@ -6796,7 +6802,7 @@
         <v>209</v>
       </c>
       <c r="B15" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C15" t="s">
         <v>69</v>
@@ -6818,17 +6824,17 @@
         <v>102</v>
       </c>
       <c r="J15" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K15"/>
       <c r="L15" t="s">
         <v>59</v>
       </c>
       <c r="M15" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N15" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O15" t="s">
         <v>64</v>
@@ -6841,7 +6847,7 @@
         <v>63</v>
       </c>
       <c r="S15" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="T15"/>
       <c r="U15"/>
@@ -6852,7 +6858,7 @@
       <c r="Z15"/>
       <c r="AA15"/>
       <c r="AB15" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="16">
@@ -6860,14 +6866,14 @@
         <v>209</v>
       </c>
       <c r="B16" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C16" t="s">
         <v>69</v>
       </c>
       <c r="D16"/>
       <c r="E16" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="F16" t="s">
         <v>60</v>
@@ -6889,10 +6895,10 @@
         <v>59</v>
       </c>
       <c r="M16" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N16" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="O16" t="s">
         <v>64</v>
@@ -6905,7 +6911,7 @@
         <v>63</v>
       </c>
       <c r="S16" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="T16"/>
       <c r="U16"/>
@@ -6922,14 +6928,14 @@
         <v>209</v>
       </c>
       <c r="B17" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C17" t="s">
         <v>69</v>
       </c>
       <c r="D17"/>
       <c r="E17" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="F17" t="s">
         <v>60</v>
@@ -6951,10 +6957,10 @@
         <v>59</v>
       </c>
       <c r="M17" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N17" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="O17" t="s">
         <v>64</v>
@@ -6967,7 +6973,7 @@
         <v>63</v>
       </c>
       <c r="S17" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="T17"/>
       <c r="U17"/>
@@ -6984,14 +6990,14 @@
         <v>209</v>
       </c>
       <c r="B18" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C18" t="s">
         <v>69</v>
       </c>
       <c r="D18"/>
       <c r="E18" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="F18" t="s">
         <v>60</v>
@@ -7006,17 +7012,17 @@
         <v>102</v>
       </c>
       <c r="J18" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K18"/>
       <c r="L18" t="s">
         <v>59</v>
       </c>
       <c r="M18" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="N18" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="O18" t="s">
         <v>64</v>
@@ -7029,7 +7035,7 @@
         <v>63</v>
       </c>
       <c r="S18" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="T18"/>
       <c r="U18"/>
@@ -7046,14 +7052,14 @@
         <v>209</v>
       </c>
       <c r="B19" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C19" t="s">
         <v>69</v>
       </c>
       <c r="D19"/>
       <c r="E19" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="F19" t="s">
         <v>60</v>
@@ -7068,17 +7074,17 @@
         <v>102</v>
       </c>
       <c r="J19" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K19"/>
       <c r="L19" t="s">
         <v>59</v>
       </c>
       <c r="M19" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N19" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O19" t="s">
         <v>64</v>
@@ -7091,7 +7097,7 @@
         <v>63</v>
       </c>
       <c r="S19" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="T19"/>
       <c r="U19"/>
@@ -7108,14 +7114,14 @@
         <v>209</v>
       </c>
       <c r="B20" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C20" t="s">
         <v>69</v>
       </c>
       <c r="D20"/>
       <c r="E20" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="F20" t="s">
         <v>60</v>
@@ -7130,17 +7136,17 @@
         <v>102</v>
       </c>
       <c r="J20" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K20"/>
       <c r="L20" t="s">
         <v>59</v>
       </c>
       <c r="M20" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N20" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="O20" t="s">
         <v>64</v>
@@ -7153,7 +7159,7 @@
         <v>63</v>
       </c>
       <c r="S20" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="T20"/>
       <c r="U20"/>
@@ -7170,14 +7176,14 @@
         <v>209</v>
       </c>
       <c r="B21" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C21" t="s">
         <v>69</v>
       </c>
       <c r="D21"/>
       <c r="E21" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="F21" t="s">
         <v>60</v>
@@ -7192,14 +7198,14 @@
         <v>102</v>
       </c>
       <c r="J21" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K21"/>
       <c r="L21" t="s">
         <v>59</v>
       </c>
       <c r="M21" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="N21" t="s">
         <v>212</v>
@@ -7232,14 +7238,14 @@
         <v>209</v>
       </c>
       <c r="B22" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C22" t="s">
         <v>69</v>
       </c>
       <c r="D22"/>
       <c r="E22" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="F22" t="s">
         <v>60</v>
@@ -7254,17 +7260,17 @@
         <v>102</v>
       </c>
       <c r="J22" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K22"/>
       <c r="L22" t="s">
         <v>59</v>
       </c>
       <c r="M22" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N22" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="O22" t="s">
         <v>64</v>
@@ -7277,7 +7283,7 @@
         <v>63</v>
       </c>
       <c r="S22" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="T22"/>
       <c r="U22"/>
@@ -7294,14 +7300,14 @@
         <v>209</v>
       </c>
       <c r="B23" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C23" t="s">
         <v>69</v>
       </c>
       <c r="D23"/>
       <c r="E23" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="F23" t="s">
         <v>60</v>
@@ -7323,10 +7329,10 @@
         <v>59</v>
       </c>
       <c r="M23" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="N23" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="O23" t="s">
         <v>64</v>
@@ -7339,7 +7345,7 @@
         <v>63</v>
       </c>
       <c r="S23" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="T23"/>
       <c r="U23"/>
@@ -7356,14 +7362,14 @@
         <v>209</v>
       </c>
       <c r="B24" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C24" t="s">
         <v>69</v>
       </c>
       <c r="D24"/>
       <c r="E24" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="F24" t="s">
         <v>60</v>
@@ -7378,17 +7384,17 @@
         <v>102</v>
       </c>
       <c r="J24" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K24"/>
       <c r="L24" t="s">
         <v>59</v>
       </c>
       <c r="M24" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N24" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O24" t="s">
         <v>64</v>
@@ -7401,7 +7407,7 @@
         <v>63</v>
       </c>
       <c r="S24" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="T24"/>
       <c r="U24"/>
@@ -7418,14 +7424,14 @@
         <v>209</v>
       </c>
       <c r="B25" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C25" t="s">
         <v>69</v>
       </c>
       <c r="D25"/>
       <c r="E25" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="F25" t="s">
         <v>60</v>
@@ -7440,17 +7446,17 @@
         <v>102</v>
       </c>
       <c r="J25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K25"/>
       <c r="L25" t="s">
         <v>59</v>
       </c>
       <c r="M25" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N25" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="O25" t="s">
         <v>64</v>
@@ -7463,7 +7469,7 @@
         <v>63</v>
       </c>
       <c r="S25" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="T25"/>
       <c r="U25"/>
@@ -7480,14 +7486,14 @@
         <v>209</v>
       </c>
       <c r="B26" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C26" t="s">
         <v>69</v>
       </c>
       <c r="D26"/>
       <c r="E26" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="F26" t="s">
         <v>60</v>
@@ -7509,10 +7515,10 @@
         <v>59</v>
       </c>
       <c r="M26" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="N26" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="O26" t="s">
         <v>64</v>
@@ -7525,7 +7531,7 @@
         <v>63</v>
       </c>
       <c r="S26" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="T26"/>
       <c r="U26"/>
@@ -7542,14 +7548,14 @@
         <v>209</v>
       </c>
       <c r="B27" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C27" t="s">
         <v>69</v>
       </c>
       <c r="D27"/>
       <c r="E27" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="F27" t="s">
         <v>60</v>
@@ -7571,10 +7577,10 @@
         <v>59</v>
       </c>
       <c r="M27" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N27" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="O27" t="s">
         <v>64</v>
@@ -7587,7 +7593,7 @@
         <v>63</v>
       </c>
       <c r="S27" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="T27"/>
       <c r="U27"/>
@@ -7604,14 +7610,14 @@
         <v>209</v>
       </c>
       <c r="B28" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C28" t="s">
         <v>69</v>
       </c>
       <c r="D28"/>
       <c r="E28" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="F28" t="s">
         <v>60</v>
@@ -7633,10 +7639,10 @@
         <v>59</v>
       </c>
       <c r="M28" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N28" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="O28" t="s">
         <v>64</v>
@@ -7649,7 +7655,7 @@
         <v>63</v>
       </c>
       <c r="S28" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="T28"/>
       <c r="U28"/>
@@ -7666,14 +7672,14 @@
         <v>209</v>
       </c>
       <c r="B29" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C29" t="s">
         <v>69</v>
       </c>
       <c r="D29"/>
       <c r="E29" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="F29" t="s">
         <v>60</v>
@@ -7688,17 +7694,17 @@
         <v>102</v>
       </c>
       <c r="J29" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K29"/>
       <c r="L29" t="s">
         <v>59</v>
       </c>
       <c r="M29" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="N29" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="O29" t="s">
         <v>64</v>
@@ -7711,7 +7717,7 @@
         <v>63</v>
       </c>
       <c r="S29" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="T29"/>
       <c r="U29"/>
@@ -7728,14 +7734,14 @@
         <v>209</v>
       </c>
       <c r="B30" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C30" t="s">
         <v>69</v>
       </c>
       <c r="D30"/>
       <c r="E30" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="F30" t="s">
         <v>60</v>
@@ -7750,17 +7756,17 @@
         <v>102</v>
       </c>
       <c r="J30" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K30"/>
       <c r="L30" t="s">
         <v>59</v>
       </c>
       <c r="M30" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N30" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O30" t="s">
         <v>64</v>
@@ -7773,7 +7779,7 @@
         <v>63</v>
       </c>
       <c r="S30" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="T30"/>
       <c r="U30"/>
@@ -7790,14 +7796,14 @@
         <v>209</v>
       </c>
       <c r="B31" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C31" t="s">
         <v>69</v>
       </c>
       <c r="D31"/>
       <c r="E31" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="F31" t="s">
         <v>60</v>
@@ -7812,17 +7818,17 @@
         <v>102</v>
       </c>
       <c r="J31" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K31"/>
       <c r="L31" t="s">
         <v>59</v>
       </c>
       <c r="M31" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N31" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="O31" t="s">
         <v>64</v>
@@ -7835,7 +7841,7 @@
         <v>63</v>
       </c>
       <c r="S31" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="T31"/>
       <c r="U31"/>
@@ -7852,14 +7858,14 @@
         <v>209</v>
       </c>
       <c r="B32" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C32" t="s">
         <v>69</v>
       </c>
       <c r="D32"/>
       <c r="E32" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="F32" t="s">
         <v>60</v>
@@ -7874,14 +7880,14 @@
         <v>102</v>
       </c>
       <c r="J32" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K32"/>
       <c r="L32" t="s">
         <v>59</v>
       </c>
       <c r="M32" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="N32" t="s">
         <v>212</v>
@@ -7914,14 +7920,14 @@
         <v>209</v>
       </c>
       <c r="B33" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C33" t="s">
         <v>69</v>
       </c>
       <c r="D33"/>
       <c r="E33" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="F33" t="s">
         <v>60</v>
@@ -7936,17 +7942,17 @@
         <v>102</v>
       </c>
       <c r="J33" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K33"/>
       <c r="L33" t="s">
         <v>59</v>
       </c>
       <c r="M33" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N33" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="O33" t="s">
         <v>64</v>
@@ -7959,7 +7965,7 @@
         <v>63</v>
       </c>
       <c r="S33" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="T33"/>
       <c r="U33"/>
@@ -7976,14 +7982,14 @@
         <v>209</v>
       </c>
       <c r="B34" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C34" t="s">
         <v>69</v>
       </c>
       <c r="D34"/>
       <c r="E34" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="F34" t="s">
         <v>60</v>
@@ -8005,10 +8011,10 @@
         <v>59</v>
       </c>
       <c r="M34" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="N34" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="O34" t="s">
         <v>64</v>
@@ -8021,7 +8027,7 @@
         <v>63</v>
       </c>
       <c r="S34" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="T34"/>
       <c r="U34"/>
@@ -8038,14 +8044,14 @@
         <v>209</v>
       </c>
       <c r="B35" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C35" t="s">
         <v>69</v>
       </c>
       <c r="D35"/>
       <c r="E35" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="F35" t="s">
         <v>60</v>
@@ -8060,17 +8066,17 @@
         <v>102</v>
       </c>
       <c r="J35" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K35"/>
       <c r="L35" t="s">
         <v>59</v>
       </c>
       <c r="M35" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N35" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O35" t="s">
         <v>64</v>
@@ -8083,7 +8089,7 @@
         <v>63</v>
       </c>
       <c r="S35" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="T35"/>
       <c r="U35"/>
@@ -8100,14 +8106,14 @@
         <v>209</v>
       </c>
       <c r="B36" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C36" t="s">
         <v>69</v>
       </c>
       <c r="D36"/>
       <c r="E36" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="F36" t="s">
         <v>60</v>
@@ -8122,17 +8128,17 @@
         <v>102</v>
       </c>
       <c r="J36" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K36"/>
       <c r="L36" t="s">
         <v>59</v>
       </c>
       <c r="M36" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N36" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="O36" t="s">
         <v>64</v>
@@ -8145,7 +8151,7 @@
         <v>63</v>
       </c>
       <c r="S36" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="T36"/>
       <c r="U36"/>
@@ -8162,14 +8168,14 @@
         <v>209</v>
       </c>
       <c r="B37" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C37" t="s">
         <v>69</v>
       </c>
       <c r="D37"/>
       <c r="E37" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="F37" t="s">
         <v>60</v>
@@ -8191,10 +8197,10 @@
         <v>59</v>
       </c>
       <c r="M37" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="N37" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="O37" t="s">
         <v>64</v>
@@ -8207,7 +8213,7 @@
         <v>63</v>
       </c>
       <c r="S37" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="T37"/>
       <c r="U37"/>
@@ -8224,14 +8230,14 @@
         <v>209</v>
       </c>
       <c r="B38" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C38" t="s">
         <v>69</v>
       </c>
       <c r="D38"/>
       <c r="E38" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="F38" t="s">
         <v>60</v>
@@ -8253,10 +8259,10 @@
         <v>59</v>
       </c>
       <c r="M38" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N38" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="O38" t="s">
         <v>64</v>
@@ -8269,7 +8275,7 @@
         <v>63</v>
       </c>
       <c r="S38" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="T38"/>
       <c r="U38"/>
@@ -8286,14 +8292,14 @@
         <v>209</v>
       </c>
       <c r="B39" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C39" t="s">
         <v>69</v>
       </c>
       <c r="D39"/>
       <c r="E39" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="F39" t="s">
         <v>60</v>
@@ -8315,10 +8321,10 @@
         <v>59</v>
       </c>
       <c r="M39" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N39" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="O39" t="s">
         <v>64</v>
@@ -8331,7 +8337,7 @@
         <v>63</v>
       </c>
       <c r="S39" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="T39"/>
       <c r="U39"/>
@@ -8348,14 +8354,14 @@
         <v>209</v>
       </c>
       <c r="B40" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C40" t="s">
         <v>69</v>
       </c>
       <c r="D40"/>
       <c r="E40" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="F40" t="s">
         <v>60</v>
@@ -8370,17 +8376,17 @@
         <v>102</v>
       </c>
       <c r="J40" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K40"/>
       <c r="L40" t="s">
         <v>59</v>
       </c>
       <c r="M40" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="N40" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="O40" t="s">
         <v>64</v>
@@ -8393,7 +8399,7 @@
         <v>63</v>
       </c>
       <c r="S40" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="T40"/>
       <c r="U40"/>
@@ -8410,14 +8416,14 @@
         <v>209</v>
       </c>
       <c r="B41" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C41" t="s">
         <v>69</v>
       </c>
       <c r="D41"/>
       <c r="E41" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="F41" t="s">
         <v>60</v>
@@ -8432,17 +8438,17 @@
         <v>102</v>
       </c>
       <c r="J41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K41"/>
       <c r="L41" t="s">
         <v>59</v>
       </c>
       <c r="M41" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N41" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O41" t="s">
         <v>64</v>
@@ -8455,7 +8461,7 @@
         <v>63</v>
       </c>
       <c r="S41" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="T41"/>
       <c r="U41"/>
@@ -8472,14 +8478,14 @@
         <v>209</v>
       </c>
       <c r="B42" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C42" t="s">
         <v>69</v>
       </c>
       <c r="D42"/>
       <c r="E42" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="F42" t="s">
         <v>60</v>
@@ -8494,17 +8500,17 @@
         <v>102</v>
       </c>
       <c r="J42" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K42"/>
       <c r="L42" t="s">
         <v>59</v>
       </c>
       <c r="M42" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N42" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="O42" t="s">
         <v>64</v>
@@ -8517,7 +8523,7 @@
         <v>63</v>
       </c>
       <c r="S42" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="T42"/>
       <c r="U42"/>
@@ -8534,14 +8540,14 @@
         <v>209</v>
       </c>
       <c r="B43" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C43" t="s">
         <v>69</v>
       </c>
       <c r="D43"/>
       <c r="E43" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="F43" t="s">
         <v>60</v>
@@ -8556,14 +8562,14 @@
         <v>102</v>
       </c>
       <c r="J43" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K43"/>
       <c r="L43" t="s">
         <v>59</v>
       </c>
       <c r="M43" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="N43" t="s">
         <v>212</v>
@@ -8596,14 +8602,14 @@
         <v>209</v>
       </c>
       <c r="B44" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C44" t="s">
         <v>69</v>
       </c>
       <c r="D44"/>
       <c r="E44" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="F44" t="s">
         <v>60</v>
@@ -8618,17 +8624,17 @@
         <v>102</v>
       </c>
       <c r="J44" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K44"/>
       <c r="L44" t="s">
         <v>59</v>
       </c>
       <c r="M44" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N44" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="O44" t="s">
         <v>64</v>
@@ -8641,7 +8647,7 @@
         <v>63</v>
       </c>
       <c r="S44" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="T44"/>
       <c r="U44"/>
@@ -8658,14 +8664,14 @@
         <v>209</v>
       </c>
       <c r="B45" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C45" t="s">
         <v>69</v>
       </c>
       <c r="D45"/>
       <c r="E45" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="F45" t="s">
         <v>60</v>
@@ -8687,10 +8693,10 @@
         <v>59</v>
       </c>
       <c r="M45" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="N45" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="O45" t="s">
         <v>64</v>
@@ -8703,7 +8709,7 @@
         <v>63</v>
       </c>
       <c r="S45" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="T45"/>
       <c r="U45"/>
@@ -8720,14 +8726,14 @@
         <v>209</v>
       </c>
       <c r="B46" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C46" t="s">
         <v>69</v>
       </c>
       <c r="D46"/>
       <c r="E46" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="F46" t="s">
         <v>60</v>
@@ -8742,17 +8748,17 @@
         <v>102</v>
       </c>
       <c r="J46" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K46"/>
       <c r="L46" t="s">
         <v>59</v>
       </c>
       <c r="M46" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N46" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O46" t="s">
         <v>64</v>
@@ -8765,7 +8771,7 @@
         <v>63</v>
       </c>
       <c r="S46" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="T46"/>
       <c r="U46"/>
@@ -8782,14 +8788,14 @@
         <v>209</v>
       </c>
       <c r="B47" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C47" t="s">
         <v>69</v>
       </c>
       <c r="D47"/>
       <c r="E47" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="F47" t="s">
         <v>60</v>
@@ -8804,17 +8810,17 @@
         <v>102</v>
       </c>
       <c r="J47" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K47"/>
       <c r="L47" t="s">
         <v>59</v>
       </c>
       <c r="M47" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N47" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="O47" t="s">
         <v>64</v>
@@ -8827,7 +8833,7 @@
         <v>63</v>
       </c>
       <c r="S47" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="T47"/>
       <c r="U47"/>
@@ -8844,14 +8850,14 @@
         <v>209</v>
       </c>
       <c r="B48" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C48" t="s">
         <v>69</v>
       </c>
       <c r="D48"/>
       <c r="E48" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="F48" t="s">
         <v>60</v>
@@ -8873,10 +8879,10 @@
         <v>59</v>
       </c>
       <c r="M48" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="N48" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="O48" t="s">
         <v>64</v>
@@ -8889,7 +8895,7 @@
         <v>63</v>
       </c>
       <c r="S48" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="T48"/>
       <c r="U48"/>
@@ -8906,14 +8912,14 @@
         <v>209</v>
       </c>
       <c r="B49" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C49" t="s">
         <v>69</v>
       </c>
       <c r="D49"/>
       <c r="E49" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="F49" t="s">
         <v>60</v>
@@ -8935,10 +8941,10 @@
         <v>59</v>
       </c>
       <c r="M49" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N49" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="O49" t="s">
         <v>64</v>
@@ -8951,7 +8957,7 @@
         <v>63</v>
       </c>
       <c r="S49" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="T49"/>
       <c r="U49"/>
@@ -8968,14 +8974,14 @@
         <v>209</v>
       </c>
       <c r="B50" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C50" t="s">
         <v>69</v>
       </c>
       <c r="D50"/>
       <c r="E50" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="F50" t="s">
         <v>60</v>
@@ -8997,10 +9003,10 @@
         <v>59</v>
       </c>
       <c r="M50" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N50" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="O50" t="s">
         <v>64</v>
@@ -9013,7 +9019,7 @@
         <v>63</v>
       </c>
       <c r="S50" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="T50"/>
       <c r="U50"/>
@@ -9030,14 +9036,14 @@
         <v>209</v>
       </c>
       <c r="B51" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C51" t="s">
         <v>69</v>
       </c>
       <c r="D51"/>
       <c r="E51" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="F51" t="s">
         <v>60</v>
@@ -9052,17 +9058,17 @@
         <v>102</v>
       </c>
       <c r="J51" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K51"/>
       <c r="L51" t="s">
         <v>59</v>
       </c>
       <c r="M51" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="N51" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="O51" t="s">
         <v>64</v>
@@ -9075,7 +9081,7 @@
         <v>63</v>
       </c>
       <c r="S51" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="T51"/>
       <c r="U51"/>
@@ -9092,14 +9098,14 @@
         <v>209</v>
       </c>
       <c r="B52" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C52" t="s">
         <v>69</v>
       </c>
       <c r="D52"/>
       <c r="E52" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="F52" t="s">
         <v>60</v>
@@ -9114,17 +9120,17 @@
         <v>102</v>
       </c>
       <c r="J52" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K52"/>
       <c r="L52" t="s">
         <v>59</v>
       </c>
       <c r="M52" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N52" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O52" t="s">
         <v>64</v>
@@ -9137,7 +9143,7 @@
         <v>63</v>
       </c>
       <c r="S52" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="T52"/>
       <c r="U52"/>
@@ -9154,14 +9160,14 @@
         <v>209</v>
       </c>
       <c r="B53" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C53" t="s">
         <v>69</v>
       </c>
       <c r="D53"/>
       <c r="E53" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="F53" t="s">
         <v>60</v>
@@ -9176,17 +9182,17 @@
         <v>102</v>
       </c>
       <c r="J53" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K53"/>
       <c r="L53" t="s">
         <v>59</v>
       </c>
       <c r="M53" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N53" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="O53" t="s">
         <v>64</v>
@@ -9199,7 +9205,7 @@
         <v>63</v>
       </c>
       <c r="S53" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="T53"/>
       <c r="U53"/>
@@ -9216,14 +9222,14 @@
         <v>209</v>
       </c>
       <c r="B54" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C54" t="s">
         <v>69</v>
       </c>
       <c r="D54"/>
       <c r="E54" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="F54" t="s">
         <v>60</v>
@@ -9238,14 +9244,14 @@
         <v>102</v>
       </c>
       <c r="J54" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K54"/>
       <c r="L54" t="s">
         <v>59</v>
       </c>
       <c r="M54" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="N54" t="s">
         <v>212</v>
@@ -9278,14 +9284,14 @@
         <v>209</v>
       </c>
       <c r="B55" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C55" t="s">
         <v>69</v>
       </c>
       <c r="D55"/>
       <c r="E55" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="F55" t="s">
         <v>60</v>
@@ -9300,17 +9306,17 @@
         <v>102</v>
       </c>
       <c r="J55" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K55"/>
       <c r="L55" t="s">
         <v>59</v>
       </c>
       <c r="M55" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N55" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="O55" t="s">
         <v>64</v>
@@ -9323,7 +9329,7 @@
         <v>63</v>
       </c>
       <c r="S55" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="T55"/>
       <c r="U55"/>
@@ -9340,14 +9346,14 @@
         <v>209</v>
       </c>
       <c r="B56" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C56" t="s">
         <v>69</v>
       </c>
       <c r="D56"/>
       <c r="E56" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="F56" t="s">
         <v>60</v>
@@ -9369,10 +9375,10 @@
         <v>59</v>
       </c>
       <c r="M56" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="N56" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="O56" t="s">
         <v>64</v>
@@ -9385,7 +9391,7 @@
         <v>63</v>
       </c>
       <c r="S56" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="T56"/>
       <c r="U56"/>
@@ -9402,14 +9408,14 @@
         <v>209</v>
       </c>
       <c r="B57" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C57" t="s">
         <v>69</v>
       </c>
       <c r="D57"/>
       <c r="E57" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="F57" t="s">
         <v>60</v>
@@ -9424,17 +9430,17 @@
         <v>102</v>
       </c>
       <c r="J57" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K57"/>
       <c r="L57" t="s">
         <v>59</v>
       </c>
       <c r="M57" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N57" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O57" t="s">
         <v>64</v>
@@ -9447,7 +9453,7 @@
         <v>63</v>
       </c>
       <c r="S57" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="T57"/>
       <c r="U57"/>
@@ -9464,14 +9470,14 @@
         <v>209</v>
       </c>
       <c r="B58" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C58" t="s">
         <v>69</v>
       </c>
       <c r="D58"/>
       <c r="E58" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="F58" t="s">
         <v>60</v>
@@ -9486,17 +9492,17 @@
         <v>102</v>
       </c>
       <c r="J58" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K58"/>
       <c r="L58" t="s">
         <v>59</v>
       </c>
       <c r="M58" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N58" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="O58" t="s">
         <v>64</v>
@@ -9509,7 +9515,7 @@
         <v>63</v>
       </c>
       <c r="S58" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="T58"/>
       <c r="U58"/>
@@ -9526,14 +9532,14 @@
         <v>209</v>
       </c>
       <c r="B59" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C59" t="s">
         <v>69</v>
       </c>
       <c r="D59"/>
       <c r="E59" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="F59" t="s">
         <v>60</v>
@@ -9555,10 +9561,10 @@
         <v>59</v>
       </c>
       <c r="M59" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="N59" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="O59" t="s">
         <v>64</v>
@@ -9571,7 +9577,7 @@
         <v>63</v>
       </c>
       <c r="S59" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="T59"/>
       <c r="U59"/>
@@ -9588,14 +9594,14 @@
         <v>209</v>
       </c>
       <c r="B60" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C60" t="s">
         <v>69</v>
       </c>
       <c r="D60"/>
       <c r="E60" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="F60" t="s">
         <v>60</v>
@@ -9617,10 +9623,10 @@
         <v>59</v>
       </c>
       <c r="M60" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N60" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="O60" t="s">
         <v>64</v>
@@ -9633,7 +9639,7 @@
         <v>63</v>
       </c>
       <c r="S60" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="T60"/>
       <c r="U60"/>
@@ -9650,14 +9656,14 @@
         <v>209</v>
       </c>
       <c r="B61" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C61" t="s">
         <v>69</v>
       </c>
       <c r="D61"/>
       <c r="E61" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="F61" t="s">
         <v>60</v>
@@ -9679,10 +9685,10 @@
         <v>59</v>
       </c>
       <c r="M61" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N61" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="O61" t="s">
         <v>64</v>
@@ -9695,7 +9701,7 @@
         <v>63</v>
       </c>
       <c r="S61" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="T61"/>
       <c r="U61"/>
@@ -9712,14 +9718,14 @@
         <v>209</v>
       </c>
       <c r="B62" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C62" t="s">
         <v>69</v>
       </c>
       <c r="D62"/>
       <c r="E62" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="F62" t="s">
         <v>60</v>
@@ -9734,17 +9740,17 @@
         <v>102</v>
       </c>
       <c r="J62" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K62"/>
       <c r="L62" t="s">
         <v>59</v>
       </c>
       <c r="M62" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="N62" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="O62" t="s">
         <v>64</v>
@@ -9757,7 +9763,7 @@
         <v>63</v>
       </c>
       <c r="S62" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="T62"/>
       <c r="U62"/>
@@ -9774,14 +9780,14 @@
         <v>209</v>
       </c>
       <c r="B63" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C63" t="s">
         <v>69</v>
       </c>
       <c r="D63"/>
       <c r="E63" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="F63" t="s">
         <v>60</v>
@@ -9796,17 +9802,17 @@
         <v>102</v>
       </c>
       <c r="J63" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K63"/>
       <c r="L63" t="s">
         <v>59</v>
       </c>
       <c r="M63" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N63" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O63" t="s">
         <v>64</v>
@@ -9819,7 +9825,7 @@
         <v>63</v>
       </c>
       <c r="S63" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="T63"/>
       <c r="U63"/>
@@ -9836,14 +9842,14 @@
         <v>209</v>
       </c>
       <c r="B64" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C64" t="s">
         <v>69</v>
       </c>
       <c r="D64"/>
       <c r="E64" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="F64" t="s">
         <v>60</v>
@@ -9858,17 +9864,17 @@
         <v>102</v>
       </c>
       <c r="J64" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K64"/>
       <c r="L64" t="s">
         <v>59</v>
       </c>
       <c r="M64" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N64" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="O64" t="s">
         <v>64</v>
@@ -9881,7 +9887,7 @@
         <v>63</v>
       </c>
       <c r="S64" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="T64"/>
       <c r="U64"/>
@@ -9898,14 +9904,14 @@
         <v>209</v>
       </c>
       <c r="B65" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C65" t="s">
         <v>69</v>
       </c>
       <c r="D65"/>
       <c r="E65" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="F65" t="s">
         <v>60</v>
@@ -9920,14 +9926,14 @@
         <v>102</v>
       </c>
       <c r="J65" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K65"/>
       <c r="L65" t="s">
         <v>59</v>
       </c>
       <c r="M65" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="N65" t="s">
         <v>212</v>
@@ -9960,14 +9966,14 @@
         <v>209</v>
       </c>
       <c r="B66" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C66" t="s">
         <v>69</v>
       </c>
       <c r="D66"/>
       <c r="E66" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="F66" t="s">
         <v>60</v>
@@ -9982,17 +9988,17 @@
         <v>102</v>
       </c>
       <c r="J66" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K66"/>
       <c r="L66" t="s">
         <v>59</v>
       </c>
       <c r="M66" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N66" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="O66" t="s">
         <v>64</v>
@@ -10005,7 +10011,7 @@
         <v>63</v>
       </c>
       <c r="S66" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="T66"/>
       <c r="U66"/>
@@ -10022,14 +10028,14 @@
         <v>209</v>
       </c>
       <c r="B67" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C67" t="s">
         <v>69</v>
       </c>
       <c r="D67"/>
       <c r="E67" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="F67" t="s">
         <v>60</v>
@@ -10051,10 +10057,10 @@
         <v>59</v>
       </c>
       <c r="M67" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="N67" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="O67" t="s">
         <v>64</v>
@@ -10067,7 +10073,7 @@
         <v>63</v>
       </c>
       <c r="S67" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="T67"/>
       <c r="U67"/>
@@ -10084,14 +10090,14 @@
         <v>209</v>
       </c>
       <c r="B68" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C68" t="s">
         <v>69</v>
       </c>
       <c r="D68"/>
       <c r="E68" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="F68" t="s">
         <v>60</v>
@@ -10106,17 +10112,17 @@
         <v>102</v>
       </c>
       <c r="J68" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K68"/>
       <c r="L68" t="s">
         <v>59</v>
       </c>
       <c r="M68" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N68" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O68" t="s">
         <v>64</v>
@@ -10129,7 +10135,7 @@
         <v>63</v>
       </c>
       <c r="S68" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="T68"/>
       <c r="U68"/>
@@ -10146,14 +10152,14 @@
         <v>209</v>
       </c>
       <c r="B69" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C69" t="s">
         <v>69</v>
       </c>
       <c r="D69"/>
       <c r="E69" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="F69" t="s">
         <v>60</v>
@@ -10168,17 +10174,17 @@
         <v>102</v>
       </c>
       <c r="J69" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K69"/>
       <c r="L69" t="s">
         <v>59</v>
       </c>
       <c r="M69" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N69" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="O69" t="s">
         <v>64</v>
@@ -10191,7 +10197,7 @@
         <v>63</v>
       </c>
       <c r="S69" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="T69"/>
       <c r="U69"/>
@@ -10208,14 +10214,14 @@
         <v>209</v>
       </c>
       <c r="B70" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C70" t="s">
         <v>69</v>
       </c>
       <c r="D70"/>
       <c r="E70" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="F70" t="s">
         <v>60</v>
@@ -10237,10 +10243,10 @@
         <v>59</v>
       </c>
       <c r="M70" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="N70" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="O70" t="s">
         <v>64</v>
@@ -10253,7 +10259,7 @@
         <v>63</v>
       </c>
       <c r="S70" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="T70"/>
       <c r="U70"/>
@@ -10270,14 +10276,14 @@
         <v>209</v>
       </c>
       <c r="B71" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C71" t="s">
         <v>69</v>
       </c>
       <c r="D71"/>
       <c r="E71" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F71" t="s">
         <v>60</v>
@@ -10299,10 +10305,10 @@
         <v>59</v>
       </c>
       <c r="M71" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N71" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="O71" t="s">
         <v>64</v>
@@ -10315,7 +10321,7 @@
         <v>63</v>
       </c>
       <c r="S71" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="T71"/>
       <c r="U71"/>
@@ -10332,14 +10338,14 @@
         <v>209</v>
       </c>
       <c r="B72" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C72" t="s">
         <v>69</v>
       </c>
       <c r="D72"/>
       <c r="E72" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F72" t="s">
         <v>60</v>
@@ -10361,10 +10367,10 @@
         <v>59</v>
       </c>
       <c r="M72" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N72" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="O72" t="s">
         <v>64</v>
@@ -10377,7 +10383,7 @@
         <v>63</v>
       </c>
       <c r="S72" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="T72"/>
       <c r="U72"/>
@@ -10394,14 +10400,14 @@
         <v>209</v>
       </c>
       <c r="B73" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C73" t="s">
         <v>69</v>
       </c>
       <c r="D73"/>
       <c r="E73" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F73" t="s">
         <v>60</v>
@@ -10416,17 +10422,17 @@
         <v>102</v>
       </c>
       <c r="J73" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K73"/>
       <c r="L73" t="s">
         <v>59</v>
       </c>
       <c r="M73" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="N73" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="O73" t="s">
         <v>64</v>
@@ -10439,7 +10445,7 @@
         <v>63</v>
       </c>
       <c r="S73" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="T73"/>
       <c r="U73"/>
@@ -10456,14 +10462,14 @@
         <v>209</v>
       </c>
       <c r="B74" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C74" t="s">
         <v>69</v>
       </c>
       <c r="D74"/>
       <c r="E74" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F74" t="s">
         <v>60</v>
@@ -10478,17 +10484,17 @@
         <v>102</v>
       </c>
       <c r="J74" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K74"/>
       <c r="L74" t="s">
         <v>59</v>
       </c>
       <c r="M74" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N74" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O74" t="s">
         <v>64</v>
@@ -10501,7 +10507,7 @@
         <v>63</v>
       </c>
       <c r="S74" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="T74"/>
       <c r="U74"/>
@@ -10518,14 +10524,14 @@
         <v>209</v>
       </c>
       <c r="B75" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C75" t="s">
         <v>69</v>
       </c>
       <c r="D75"/>
       <c r="E75" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F75" t="s">
         <v>60</v>
@@ -10540,17 +10546,17 @@
         <v>102</v>
       </c>
       <c r="J75" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K75"/>
       <c r="L75" t="s">
         <v>59</v>
       </c>
       <c r="M75" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N75" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="O75" t="s">
         <v>64</v>
@@ -10563,7 +10569,7 @@
         <v>63</v>
       </c>
       <c r="S75" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="T75"/>
       <c r="U75"/>
@@ -10580,14 +10586,14 @@
         <v>209</v>
       </c>
       <c r="B76" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C76" t="s">
         <v>69</v>
       </c>
       <c r="D76"/>
       <c r="E76" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F76" t="s">
         <v>60</v>
@@ -10609,10 +10615,10 @@
         <v>59</v>
       </c>
       <c r="M76" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="N76" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="O76" t="s">
         <v>64</v>
@@ -10625,7 +10631,7 @@
         <v>63</v>
       </c>
       <c r="S76" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="T76"/>
       <c r="U76"/>
@@ -10642,14 +10648,14 @@
         <v>209</v>
       </c>
       <c r="B77" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C77" t="s">
         <v>69</v>
       </c>
       <c r="D77"/>
       <c r="E77" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F77" t="s">
         <v>60</v>
@@ -10671,10 +10677,10 @@
         <v>59</v>
       </c>
       <c r="M77" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="N77" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="O77" t="s">
         <v>64</v>
@@ -10687,7 +10693,7 @@
         <v>63</v>
       </c>
       <c r="S77" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="T77"/>
       <c r="U77"/>
@@ -10704,14 +10710,14 @@
         <v>209</v>
       </c>
       <c r="B78" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C78" t="s">
         <v>69</v>
       </c>
       <c r="D78"/>
       <c r="E78" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F78" t="s">
         <v>60</v>
@@ -10726,17 +10732,17 @@
         <v>102</v>
       </c>
       <c r="J78" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K78"/>
       <c r="L78" t="s">
         <v>59</v>
       </c>
       <c r="M78" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N78" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O78" t="s">
         <v>64</v>
@@ -10749,7 +10755,7 @@
         <v>63</v>
       </c>
       <c r="S78" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="T78"/>
       <c r="U78"/>
@@ -10766,14 +10772,14 @@
         <v>209</v>
       </c>
       <c r="B79" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C79" t="s">
         <v>69</v>
       </c>
       <c r="D79"/>
       <c r="E79" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F79" t="s">
         <v>60</v>
@@ -10788,17 +10794,17 @@
         <v>102</v>
       </c>
       <c r="J79" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K79"/>
       <c r="L79" t="s">
         <v>59</v>
       </c>
       <c r="M79" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N79" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="O79" t="s">
         <v>64</v>
@@ -10811,7 +10817,7 @@
         <v>63</v>
       </c>
       <c r="S79" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="T79"/>
       <c r="U79"/>
@@ -10828,14 +10834,14 @@
         <v>209</v>
       </c>
       <c r="B80" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C80" t="s">
         <v>69</v>
       </c>
       <c r="D80"/>
       <c r="E80" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F80" t="s">
         <v>60</v>
@@ -10857,10 +10863,10 @@
         <v>59</v>
       </c>
       <c r="M80" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="N80" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="O80" t="s">
         <v>64</v>
@@ -10873,7 +10879,7 @@
         <v>63</v>
       </c>
       <c r="S80" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="T80"/>
       <c r="U80"/>
@@ -10890,14 +10896,14 @@
         <v>209</v>
       </c>
       <c r="B81" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C81" t="s">
         <v>69</v>
       </c>
       <c r="D81"/>
       <c r="E81" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F81" t="s">
         <v>60</v>
@@ -10919,10 +10925,10 @@
         <v>59</v>
       </c>
       <c r="M81" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N81" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="O81" t="s">
         <v>64</v>
@@ -10935,7 +10941,7 @@
         <v>63</v>
       </c>
       <c r="S81" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="T81"/>
       <c r="U81"/>
@@ -10952,14 +10958,14 @@
         <v>209</v>
       </c>
       <c r="B82" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C82" t="s">
         <v>69</v>
       </c>
       <c r="D82"/>
       <c r="E82" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F82" t="s">
         <v>60</v>
@@ -10981,10 +10987,10 @@
         <v>59</v>
       </c>
       <c r="M82" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N82" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="O82" t="s">
         <v>64</v>
@@ -10997,7 +11003,7 @@
         <v>63</v>
       </c>
       <c r="S82" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="T82"/>
       <c r="U82"/>
@@ -11014,14 +11020,14 @@
         <v>209</v>
       </c>
       <c r="B83" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C83" t="s">
         <v>69</v>
       </c>
       <c r="D83"/>
       <c r="E83" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F83" t="s">
         <v>60</v>
@@ -11036,17 +11042,17 @@
         <v>102</v>
       </c>
       <c r="J83" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K83"/>
       <c r="L83" t="s">
         <v>59</v>
       </c>
       <c r="M83" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="N83" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="O83" t="s">
         <v>64</v>
@@ -11059,7 +11065,7 @@
         <v>63</v>
       </c>
       <c r="S83" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="T83"/>
       <c r="U83"/>
@@ -11076,14 +11082,14 @@
         <v>209</v>
       </c>
       <c r="B84" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C84" t="s">
         <v>69</v>
       </c>
       <c r="D84"/>
       <c r="E84" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F84" t="s">
         <v>60</v>
@@ -11098,17 +11104,17 @@
         <v>102</v>
       </c>
       <c r="J84" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K84"/>
       <c r="L84" t="s">
         <v>59</v>
       </c>
       <c r="M84" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N84" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O84" t="s">
         <v>64</v>
@@ -11121,7 +11127,7 @@
         <v>63</v>
       </c>
       <c r="S84" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="T84"/>
       <c r="U84"/>
@@ -11138,14 +11144,14 @@
         <v>209</v>
       </c>
       <c r="B85" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C85" t="s">
         <v>69</v>
       </c>
       <c r="D85"/>
       <c r="E85" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F85" t="s">
         <v>60</v>
@@ -11160,17 +11166,17 @@
         <v>102</v>
       </c>
       <c r="J85" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K85"/>
       <c r="L85" t="s">
         <v>59</v>
       </c>
       <c r="M85" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N85" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="O85" t="s">
         <v>64</v>
@@ -11183,7 +11189,7 @@
         <v>63</v>
       </c>
       <c r="S85" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="T85"/>
       <c r="U85"/>
@@ -11200,14 +11206,14 @@
         <v>209</v>
       </c>
       <c r="B86" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C86" t="s">
         <v>69</v>
       </c>
       <c r="D86"/>
       <c r="E86" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F86" t="s">
         <v>60</v>
@@ -11229,10 +11235,10 @@
         <v>59</v>
       </c>
       <c r="M86" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="N86" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="O86" t="s">
         <v>64</v>
@@ -11245,7 +11251,7 @@
         <v>63</v>
       </c>
       <c r="S86" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="T86"/>
       <c r="U86"/>
@@ -11262,14 +11268,14 @@
         <v>209</v>
       </c>
       <c r="B87" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C87" t="s">
         <v>69</v>
       </c>
       <c r="D87"/>
       <c r="E87" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F87" t="s">
         <v>60</v>
@@ -11291,10 +11297,10 @@
         <v>59</v>
       </c>
       <c r="M87" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="N87" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="O87" t="s">
         <v>64</v>
@@ -11307,7 +11313,7 @@
         <v>63</v>
       </c>
       <c r="S87" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="T87"/>
       <c r="U87"/>
@@ -11324,14 +11330,14 @@
         <v>209</v>
       </c>
       <c r="B88" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C88" t="s">
         <v>69</v>
       </c>
       <c r="D88"/>
       <c r="E88" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F88" t="s">
         <v>60</v>
@@ -11346,17 +11352,17 @@
         <v>102</v>
       </c>
       <c r="J88" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K88"/>
       <c r="L88" t="s">
         <v>59</v>
       </c>
       <c r="M88" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N88" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O88" t="s">
         <v>64</v>
@@ -11369,7 +11375,7 @@
         <v>63</v>
       </c>
       <c r="S88" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="T88"/>
       <c r="U88"/>
@@ -11386,14 +11392,14 @@
         <v>209</v>
       </c>
       <c r="B89" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C89" t="s">
         <v>69</v>
       </c>
       <c r="D89"/>
       <c r="E89" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F89" t="s">
         <v>60</v>
@@ -11408,17 +11414,17 @@
         <v>102</v>
       </c>
       <c r="J89" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K89"/>
       <c r="L89" t="s">
         <v>59</v>
       </c>
       <c r="M89" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N89" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="O89" t="s">
         <v>64</v>
@@ -11431,7 +11437,7 @@
         <v>63</v>
       </c>
       <c r="S89" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="T89"/>
       <c r="U89"/>
@@ -11448,14 +11454,14 @@
         <v>209</v>
       </c>
       <c r="B90" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C90" t="s">
         <v>69</v>
       </c>
       <c r="D90"/>
       <c r="E90" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F90" t="s">
         <v>60</v>
@@ -11477,10 +11483,10 @@
         <v>59</v>
       </c>
       <c r="M90" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="N90" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="O90" t="s">
         <v>64</v>
@@ -11493,7 +11499,7 @@
         <v>63</v>
       </c>
       <c r="S90" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="T90"/>
       <c r="U90"/>
@@ -11510,14 +11516,14 @@
         <v>209</v>
       </c>
       <c r="B91" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C91" t="s">
         <v>69</v>
       </c>
       <c r="D91"/>
       <c r="E91" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F91" t="s">
         <v>60</v>
@@ -11539,10 +11545,10 @@
         <v>59</v>
       </c>
       <c r="M91" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N91" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="O91" t="s">
         <v>64</v>
@@ -11555,7 +11561,7 @@
         <v>63</v>
       </c>
       <c r="S91" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="T91"/>
       <c r="U91"/>
@@ -11572,14 +11578,14 @@
         <v>209</v>
       </c>
       <c r="B92" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C92" t="s">
         <v>69</v>
       </c>
       <c r="D92"/>
       <c r="E92" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F92" t="s">
         <v>60</v>
@@ -11601,10 +11607,10 @@
         <v>59</v>
       </c>
       <c r="M92" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N92" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="O92" t="s">
         <v>64</v>
@@ -11617,7 +11623,7 @@
         <v>63</v>
       </c>
       <c r="S92" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="T92"/>
       <c r="U92"/>
@@ -11634,14 +11640,14 @@
         <v>209</v>
       </c>
       <c r="B93" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C93" t="s">
         <v>69</v>
       </c>
       <c r="D93"/>
       <c r="E93" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F93" t="s">
         <v>60</v>
@@ -11656,17 +11662,17 @@
         <v>102</v>
       </c>
       <c r="J93" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K93"/>
       <c r="L93" t="s">
         <v>59</v>
       </c>
       <c r="M93" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="N93" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="O93" t="s">
         <v>64</v>
@@ -11679,7 +11685,7 @@
         <v>63</v>
       </c>
       <c r="S93" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="T93"/>
       <c r="U93"/>
@@ -11696,14 +11702,14 @@
         <v>209</v>
       </c>
       <c r="B94" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C94" t="s">
         <v>69</v>
       </c>
       <c r="D94"/>
       <c r="E94" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F94" t="s">
         <v>60</v>
@@ -11718,17 +11724,17 @@
         <v>102</v>
       </c>
       <c r="J94" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K94"/>
       <c r="L94" t="s">
         <v>59</v>
       </c>
       <c r="M94" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N94" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O94" t="s">
         <v>64</v>
@@ -11741,7 +11747,7 @@
         <v>63</v>
       </c>
       <c r="S94" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="T94"/>
       <c r="U94"/>
@@ -11758,14 +11764,14 @@
         <v>209</v>
       </c>
       <c r="B95" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C95" t="s">
         <v>69</v>
       </c>
       <c r="D95"/>
       <c r="E95" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F95" t="s">
         <v>60</v>
@@ -11780,17 +11786,17 @@
         <v>102</v>
       </c>
       <c r="J95" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K95"/>
       <c r="L95" t="s">
         <v>59</v>
       </c>
       <c r="M95" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N95" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="O95" t="s">
         <v>64</v>
@@ -11803,7 +11809,7 @@
         <v>63</v>
       </c>
       <c r="S95" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="T95"/>
       <c r="U95"/>
@@ -11820,14 +11826,14 @@
         <v>209</v>
       </c>
       <c r="B96" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C96" t="s">
         <v>69</v>
       </c>
       <c r="D96"/>
       <c r="E96" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F96" t="s">
         <v>60</v>
@@ -11849,10 +11855,10 @@
         <v>59</v>
       </c>
       <c r="M96" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="N96" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="O96" t="s">
         <v>64</v>
@@ -11865,7 +11871,7 @@
         <v>63</v>
       </c>
       <c r="S96" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="T96"/>
       <c r="U96"/>
@@ -11882,14 +11888,14 @@
         <v>209</v>
       </c>
       <c r="B97" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C97" t="s">
         <v>69</v>
       </c>
       <c r="D97"/>
       <c r="E97" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F97" t="s">
         <v>60</v>
@@ -11911,10 +11917,10 @@
         <v>59</v>
       </c>
       <c r="M97" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="N97" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="O97" t="s">
         <v>64</v>
@@ -11927,7 +11933,7 @@
         <v>63</v>
       </c>
       <c r="S97" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="T97"/>
       <c r="U97"/>
@@ -11944,14 +11950,14 @@
         <v>209</v>
       </c>
       <c r="B98" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C98" t="s">
         <v>69</v>
       </c>
       <c r="D98"/>
       <c r="E98" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F98" t="s">
         <v>60</v>
@@ -11966,17 +11972,17 @@
         <v>102</v>
       </c>
       <c r="J98" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K98"/>
       <c r="L98" t="s">
         <v>59</v>
       </c>
       <c r="M98" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N98" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O98" t="s">
         <v>64</v>
@@ -11989,7 +11995,7 @@
         <v>63</v>
       </c>
       <c r="S98" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="T98"/>
       <c r="U98"/>
@@ -12006,14 +12012,14 @@
         <v>209</v>
       </c>
       <c r="B99" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C99" t="s">
         <v>69</v>
       </c>
       <c r="D99"/>
       <c r="E99" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F99" t="s">
         <v>60</v>
@@ -12028,17 +12034,17 @@
         <v>102</v>
       </c>
       <c r="J99" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K99"/>
       <c r="L99" t="s">
         <v>59</v>
       </c>
       <c r="M99" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N99" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="O99" t="s">
         <v>64</v>
@@ -12051,7 +12057,7 @@
         <v>63</v>
       </c>
       <c r="S99" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="T99"/>
       <c r="U99"/>
@@ -12068,14 +12074,14 @@
         <v>209</v>
       </c>
       <c r="B100" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C100" t="s">
         <v>69</v>
       </c>
       <c r="D100"/>
       <c r="E100" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F100" t="s">
         <v>60</v>
@@ -12097,10 +12103,10 @@
         <v>59</v>
       </c>
       <c r="M100" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="N100" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="O100" t="s">
         <v>64</v>
@@ -12113,7 +12119,7 @@
         <v>63</v>
       </c>
       <c r="S100" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="T100"/>
       <c r="U100"/>
@@ -12130,14 +12136,14 @@
         <v>209</v>
       </c>
       <c r="B101" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C101" t="s">
         <v>69</v>
       </c>
       <c r="D101"/>
       <c r="E101" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F101" t="s">
         <v>60</v>
@@ -12159,10 +12165,10 @@
         <v>59</v>
       </c>
       <c r="M101" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N101" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="O101" t="s">
         <v>64</v>
@@ -12175,7 +12181,7 @@
         <v>63</v>
       </c>
       <c r="S101" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="T101"/>
       <c r="U101"/>
@@ -12192,14 +12198,14 @@
         <v>209</v>
       </c>
       <c r="B102" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C102" t="s">
         <v>69</v>
       </c>
       <c r="D102"/>
       <c r="E102" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F102" t="s">
         <v>60</v>
@@ -12221,10 +12227,10 @@
         <v>59</v>
       </c>
       <c r="M102" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N102" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="O102" t="s">
         <v>64</v>
@@ -12237,7 +12243,7 @@
         <v>63</v>
       </c>
       <c r="S102" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="T102"/>
       <c r="U102"/>
@@ -12254,14 +12260,14 @@
         <v>209</v>
       </c>
       <c r="B103" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C103" t="s">
         <v>69</v>
       </c>
       <c r="D103"/>
       <c r="E103" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F103" t="s">
         <v>60</v>
@@ -12276,17 +12282,17 @@
         <v>102</v>
       </c>
       <c r="J103" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K103"/>
       <c r="L103" t="s">
         <v>59</v>
       </c>
       <c r="M103" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="N103" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="O103" t="s">
         <v>64</v>
@@ -12299,7 +12305,7 @@
         <v>63</v>
       </c>
       <c r="S103" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="T103"/>
       <c r="U103"/>
@@ -12316,14 +12322,14 @@
         <v>209</v>
       </c>
       <c r="B104" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C104" t="s">
         <v>69</v>
       </c>
       <c r="D104"/>
       <c r="E104" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F104" t="s">
         <v>60</v>
@@ -12338,17 +12344,17 @@
         <v>102</v>
       </c>
       <c r="J104" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K104"/>
       <c r="L104" t="s">
         <v>59</v>
       </c>
       <c r="M104" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N104" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O104" t="s">
         <v>64</v>
@@ -12361,7 +12367,7 @@
         <v>63</v>
       </c>
       <c r="S104" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="T104"/>
       <c r="U104"/>
@@ -12378,14 +12384,14 @@
         <v>209</v>
       </c>
       <c r="B105" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C105" t="s">
         <v>69</v>
       </c>
       <c r="D105"/>
       <c r="E105" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F105" t="s">
         <v>60</v>
@@ -12400,17 +12406,17 @@
         <v>102</v>
       </c>
       <c r="J105" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K105"/>
       <c r="L105" t="s">
         <v>59</v>
       </c>
       <c r="M105" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N105" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="O105" t="s">
         <v>64</v>
@@ -12423,7 +12429,7 @@
         <v>63</v>
       </c>
       <c r="S105" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="T105"/>
       <c r="U105"/>
@@ -12440,14 +12446,14 @@
         <v>209</v>
       </c>
       <c r="B106" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C106" t="s">
         <v>69</v>
       </c>
       <c r="D106"/>
       <c r="E106" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F106" t="s">
         <v>60</v>
@@ -12469,10 +12475,10 @@
         <v>59</v>
       </c>
       <c r="M106" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="N106" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="O106" t="s">
         <v>64</v>
@@ -12485,7 +12491,7 @@
         <v>63</v>
       </c>
       <c r="S106" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="T106"/>
       <c r="U106"/>
@@ -12502,14 +12508,14 @@
         <v>209</v>
       </c>
       <c r="B107" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C107" t="s">
         <v>69</v>
       </c>
       <c r="D107"/>
       <c r="E107" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F107" t="s">
         <v>60</v>
@@ -12531,10 +12537,10 @@
         <v>59</v>
       </c>
       <c r="M107" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="N107" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="O107" t="s">
         <v>64</v>
@@ -12547,7 +12553,7 @@
         <v>63</v>
       </c>
       <c r="S107" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="T107"/>
       <c r="U107"/>
@@ -12564,14 +12570,14 @@
         <v>209</v>
       </c>
       <c r="B108" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C108" t="s">
         <v>69</v>
       </c>
       <c r="D108"/>
       <c r="E108" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F108" t="s">
         <v>60</v>
@@ -12586,17 +12592,17 @@
         <v>102</v>
       </c>
       <c r="J108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K108"/>
       <c r="L108" t="s">
         <v>59</v>
       </c>
       <c r="M108" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N108" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O108" t="s">
         <v>64</v>
@@ -12609,7 +12615,7 @@
         <v>63</v>
       </c>
       <c r="S108" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="T108"/>
       <c r="U108"/>
@@ -12626,14 +12632,14 @@
         <v>209</v>
       </c>
       <c r="B109" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C109" t="s">
         <v>69</v>
       </c>
       <c r="D109"/>
       <c r="E109" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F109" t="s">
         <v>60</v>
@@ -12648,17 +12654,17 @@
         <v>102</v>
       </c>
       <c r="J109" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K109"/>
       <c r="L109" t="s">
         <v>59</v>
       </c>
       <c r="M109" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N109" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="O109" t="s">
         <v>64</v>
@@ -12671,7 +12677,7 @@
         <v>63</v>
       </c>
       <c r="S109" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="T109"/>
       <c r="U109"/>
@@ -12688,14 +12694,14 @@
         <v>209</v>
       </c>
       <c r="B110" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C110" t="s">
         <v>69</v>
       </c>
       <c r="D110"/>
       <c r="E110" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F110" t="s">
         <v>60</v>
@@ -12717,10 +12723,10 @@
         <v>59</v>
       </c>
       <c r="M110" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="N110" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="O110" t="s">
         <v>64</v>
@@ -12733,7 +12739,7 @@
         <v>63</v>
       </c>
       <c r="S110" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="T110"/>
       <c r="U110"/>
@@ -12750,14 +12756,14 @@
         <v>209</v>
       </c>
       <c r="B111" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C111" t="s">
         <v>69</v>
       </c>
       <c r="D111"/>
       <c r="E111" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F111" t="s">
         <v>60</v>
@@ -12779,10 +12785,10 @@
         <v>59</v>
       </c>
       <c r="M111" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N111" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="O111" t="s">
         <v>64</v>
@@ -12795,7 +12801,7 @@
         <v>63</v>
       </c>
       <c r="S111" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="T111"/>
       <c r="U111"/>
@@ -12812,14 +12818,14 @@
         <v>209</v>
       </c>
       <c r="B112" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C112" t="s">
         <v>69</v>
       </c>
       <c r="D112"/>
       <c r="E112" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F112" t="s">
         <v>60</v>
@@ -12841,10 +12847,10 @@
         <v>59</v>
       </c>
       <c r="M112" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N112" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="O112" t="s">
         <v>64</v>
@@ -12857,7 +12863,7 @@
         <v>63</v>
       </c>
       <c r="S112" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="T112"/>
       <c r="U112"/>
@@ -12874,14 +12880,14 @@
         <v>209</v>
       </c>
       <c r="B113" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C113" t="s">
         <v>69</v>
       </c>
       <c r="D113"/>
       <c r="E113" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F113" t="s">
         <v>60</v>
@@ -12896,17 +12902,17 @@
         <v>102</v>
       </c>
       <c r="J113" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K113"/>
       <c r="L113" t="s">
         <v>59</v>
       </c>
       <c r="M113" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="N113" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="O113" t="s">
         <v>64</v>
@@ -12919,7 +12925,7 @@
         <v>63</v>
       </c>
       <c r="S113" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="T113"/>
       <c r="U113"/>
@@ -12936,14 +12942,14 @@
         <v>209</v>
       </c>
       <c r="B114" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C114" t="s">
         <v>69</v>
       </c>
       <c r="D114"/>
       <c r="E114" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F114" t="s">
         <v>60</v>
@@ -12958,17 +12964,17 @@
         <v>102</v>
       </c>
       <c r="J114" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K114"/>
       <c r="L114" t="s">
         <v>59</v>
       </c>
       <c r="M114" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N114" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O114" t="s">
         <v>64</v>
@@ -12981,7 +12987,7 @@
         <v>63</v>
       </c>
       <c r="S114" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="T114"/>
       <c r="U114"/>
@@ -12998,14 +13004,14 @@
         <v>209</v>
       </c>
       <c r="B115" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C115" t="s">
         <v>69</v>
       </c>
       <c r="D115"/>
       <c r="E115" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F115" t="s">
         <v>60</v>
@@ -13020,17 +13026,17 @@
         <v>102</v>
       </c>
       <c r="J115" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K115"/>
       <c r="L115" t="s">
         <v>59</v>
       </c>
       <c r="M115" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N115" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="O115" t="s">
         <v>64</v>
@@ -13043,7 +13049,7 @@
         <v>63</v>
       </c>
       <c r="S115" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="T115"/>
       <c r="U115"/>
@@ -13060,14 +13066,14 @@
         <v>209</v>
       </c>
       <c r="B116" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C116" t="s">
         <v>69</v>
       </c>
       <c r="D116"/>
       <c r="E116" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F116" t="s">
         <v>60</v>
@@ -13089,10 +13095,10 @@
         <v>59</v>
       </c>
       <c r="M116" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="N116" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="O116" t="s">
         <v>64</v>
@@ -13105,7 +13111,7 @@
         <v>63</v>
       </c>
       <c r="S116" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="T116"/>
       <c r="U116"/>
@@ -13122,14 +13128,14 @@
         <v>209</v>
       </c>
       <c r="B117" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C117" t="s">
         <v>69</v>
       </c>
       <c r="D117"/>
       <c r="E117" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F117" t="s">
         <v>60</v>
@@ -13151,10 +13157,10 @@
         <v>59</v>
       </c>
       <c r="M117" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="N117" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="O117" t="s">
         <v>64</v>
@@ -13167,7 +13173,7 @@
         <v>63</v>
       </c>
       <c r="S117" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="T117"/>
       <c r="U117"/>
@@ -13184,14 +13190,14 @@
         <v>209</v>
       </c>
       <c r="B118" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C118" t="s">
         <v>69</v>
       </c>
       <c r="D118"/>
       <c r="E118" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F118" t="s">
         <v>60</v>
@@ -13206,17 +13212,17 @@
         <v>102</v>
       </c>
       <c r="J118" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K118"/>
       <c r="L118" t="s">
         <v>59</v>
       </c>
       <c r="M118" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N118" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O118" t="s">
         <v>64</v>
@@ -13229,7 +13235,7 @@
         <v>63</v>
       </c>
       <c r="S118" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="T118"/>
       <c r="U118"/>
@@ -13246,14 +13252,14 @@
         <v>209</v>
       </c>
       <c r="B119" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C119" t="s">
         <v>69</v>
       </c>
       <c r="D119"/>
       <c r="E119" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F119" t="s">
         <v>60</v>
@@ -13268,17 +13274,17 @@
         <v>102</v>
       </c>
       <c r="J119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K119"/>
       <c r="L119" t="s">
         <v>59</v>
       </c>
       <c r="M119" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N119" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="O119" t="s">
         <v>64</v>
@@ -13291,7 +13297,7 @@
         <v>63</v>
       </c>
       <c r="S119" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="T119"/>
       <c r="U119"/>
@@ -13308,14 +13314,14 @@
         <v>209</v>
       </c>
       <c r="B120" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C120" t="s">
         <v>69</v>
       </c>
       <c r="D120"/>
       <c r="E120" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F120" t="s">
         <v>60</v>
@@ -13337,10 +13343,10 @@
         <v>59</v>
       </c>
       <c r="M120" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="N120" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="O120" t="s">
         <v>64</v>
@@ -13353,7 +13359,7 @@
         <v>63</v>
       </c>
       <c r="S120" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="T120"/>
       <c r="U120"/>
@@ -13370,14 +13376,14 @@
         <v>209</v>
       </c>
       <c r="B121" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C121" t="s">
         <v>69</v>
       </c>
       <c r="D121"/>
       <c r="E121" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F121" t="s">
         <v>60</v>
@@ -13399,10 +13405,10 @@
         <v>59</v>
       </c>
       <c r="M121" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N121" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="O121" t="s">
         <v>64</v>
@@ -13415,7 +13421,7 @@
         <v>63</v>
       </c>
       <c r="S121" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="T121"/>
       <c r="U121"/>
@@ -13432,14 +13438,14 @@
         <v>209</v>
       </c>
       <c r="B122" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C122" t="s">
         <v>69</v>
       </c>
       <c r="D122"/>
       <c r="E122" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F122" t="s">
         <v>60</v>
@@ -13461,10 +13467,10 @@
         <v>59</v>
       </c>
       <c r="M122" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N122" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="O122" t="s">
         <v>64</v>
@@ -13477,7 +13483,7 @@
         <v>63</v>
       </c>
       <c r="S122" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="T122"/>
       <c r="U122"/>
@@ -13494,14 +13500,14 @@
         <v>209</v>
       </c>
       <c r="B123" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C123" t="s">
         <v>69</v>
       </c>
       <c r="D123"/>
       <c r="E123" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F123" t="s">
         <v>60</v>
@@ -13516,17 +13522,17 @@
         <v>102</v>
       </c>
       <c r="J123" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K123"/>
       <c r="L123" t="s">
         <v>59</v>
       </c>
       <c r="M123" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="N123" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="O123" t="s">
         <v>64</v>
@@ -13539,7 +13545,7 @@
         <v>63</v>
       </c>
       <c r="S123" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="T123"/>
       <c r="U123"/>
@@ -13556,14 +13562,14 @@
         <v>209</v>
       </c>
       <c r="B124" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C124" t="s">
         <v>69</v>
       </c>
       <c r="D124"/>
       <c r="E124" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F124" t="s">
         <v>60</v>
@@ -13578,17 +13584,17 @@
         <v>102</v>
       </c>
       <c r="J124" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K124"/>
       <c r="L124" t="s">
         <v>59</v>
       </c>
       <c r="M124" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N124" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O124" t="s">
         <v>64</v>
@@ -13601,7 +13607,7 @@
         <v>63</v>
       </c>
       <c r="S124" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="T124"/>
       <c r="U124"/>
@@ -13618,14 +13624,14 @@
         <v>209</v>
       </c>
       <c r="B125" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C125" t="s">
         <v>69</v>
       </c>
       <c r="D125"/>
       <c r="E125" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F125" t="s">
         <v>60</v>
@@ -13640,17 +13646,17 @@
         <v>102</v>
       </c>
       <c r="J125" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K125"/>
       <c r="L125" t="s">
         <v>59</v>
       </c>
       <c r="M125" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N125" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="O125" t="s">
         <v>64</v>
@@ -13663,7 +13669,7 @@
         <v>63</v>
       </c>
       <c r="S125" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="T125"/>
       <c r="U125"/>
@@ -13680,14 +13686,14 @@
         <v>209</v>
       </c>
       <c r="B126" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C126" t="s">
         <v>69</v>
       </c>
       <c r="D126"/>
       <c r="E126" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F126" t="s">
         <v>60</v>
@@ -13709,10 +13715,10 @@
         <v>59</v>
       </c>
       <c r="M126" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="N126" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="O126" t="s">
         <v>64</v>
@@ -13725,7 +13731,7 @@
         <v>63</v>
       </c>
       <c r="S126" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="T126"/>
       <c r="U126"/>
@@ -13742,14 +13748,14 @@
         <v>209</v>
       </c>
       <c r="B127" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C127" t="s">
         <v>69</v>
       </c>
       <c r="D127"/>
       <c r="E127" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F127" t="s">
         <v>60</v>
@@ -13771,10 +13777,10 @@
         <v>59</v>
       </c>
       <c r="M127" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="N127" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="O127" t="s">
         <v>64</v>
@@ -13787,7 +13793,7 @@
         <v>63</v>
       </c>
       <c r="S127" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="T127"/>
       <c r="U127"/>
@@ -13804,14 +13810,14 @@
         <v>209</v>
       </c>
       <c r="B128" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C128" t="s">
         <v>69</v>
       </c>
       <c r="D128"/>
       <c r="E128" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F128" t="s">
         <v>60</v>
@@ -13826,17 +13832,17 @@
         <v>102</v>
       </c>
       <c r="J128" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K128"/>
       <c r="L128" t="s">
         <v>59</v>
       </c>
       <c r="M128" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N128" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O128" t="s">
         <v>64</v>
@@ -13849,7 +13855,7 @@
         <v>63</v>
       </c>
       <c r="S128" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="T128"/>
       <c r="U128"/>
@@ -13866,14 +13872,14 @@
         <v>209</v>
       </c>
       <c r="B129" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C129" t="s">
         <v>69</v>
       </c>
       <c r="D129"/>
       <c r="E129" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F129" t="s">
         <v>60</v>
@@ -13888,17 +13894,17 @@
         <v>102</v>
       </c>
       <c r="J129" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K129"/>
       <c r="L129" t="s">
         <v>59</v>
       </c>
       <c r="M129" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N129" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="O129" t="s">
         <v>64</v>
@@ -13911,7 +13917,7 @@
         <v>63</v>
       </c>
       <c r="S129" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="T129"/>
       <c r="U129"/>
@@ -13928,14 +13934,14 @@
         <v>209</v>
       </c>
       <c r="B130" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C130" t="s">
         <v>69</v>
       </c>
       <c r="D130"/>
       <c r="E130" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F130" t="s">
         <v>60</v>
@@ -13957,10 +13963,10 @@
         <v>59</v>
       </c>
       <c r="M130" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="N130" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="O130" t="s">
         <v>64</v>
@@ -13973,7 +13979,7 @@
         <v>63</v>
       </c>
       <c r="S130" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="T130"/>
       <c r="U130"/>
@@ -13990,14 +13996,14 @@
         <v>209</v>
       </c>
       <c r="B131" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C131" t="s">
         <v>69</v>
       </c>
       <c r="D131"/>
       <c r="E131" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F131" t="s">
         <v>60</v>
@@ -14019,10 +14025,10 @@
         <v>59</v>
       </c>
       <c r="M131" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N131" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="O131" t="s">
         <v>64</v>
@@ -14035,7 +14041,7 @@
         <v>63</v>
       </c>
       <c r="S131" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="T131"/>
       <c r="U131"/>
@@ -14052,14 +14058,14 @@
         <v>209</v>
       </c>
       <c r="B132" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C132" t="s">
         <v>69</v>
       </c>
       <c r="D132"/>
       <c r="E132" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F132" t="s">
         <v>60</v>
@@ -14081,10 +14087,10 @@
         <v>59</v>
       </c>
       <c r="M132" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N132" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="O132" t="s">
         <v>64</v>
@@ -14097,7 +14103,7 @@
         <v>63</v>
       </c>
       <c r="S132" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="T132"/>
       <c r="U132"/>
@@ -14114,14 +14120,14 @@
         <v>209</v>
       </c>
       <c r="B133" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C133" t="s">
         <v>69</v>
       </c>
       <c r="D133"/>
       <c r="E133" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F133" t="s">
         <v>60</v>
@@ -14136,17 +14142,17 @@
         <v>102</v>
       </c>
       <c r="J133" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K133"/>
       <c r="L133" t="s">
         <v>59</v>
       </c>
       <c r="M133" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="N133" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="O133" t="s">
         <v>64</v>
@@ -14159,7 +14165,7 @@
         <v>63</v>
       </c>
       <c r="S133" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="T133"/>
       <c r="U133"/>
@@ -14176,14 +14182,14 @@
         <v>209</v>
       </c>
       <c r="B134" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C134" t="s">
         <v>69</v>
       </c>
       <c r="D134"/>
       <c r="E134" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F134" t="s">
         <v>60</v>
@@ -14198,17 +14204,17 @@
         <v>102</v>
       </c>
       <c r="J134" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K134"/>
       <c r="L134" t="s">
         <v>59</v>
       </c>
       <c r="M134" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N134" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O134" t="s">
         <v>64</v>
@@ -14221,7 +14227,7 @@
         <v>63</v>
       </c>
       <c r="S134" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="T134"/>
       <c r="U134"/>
@@ -14238,14 +14244,14 @@
         <v>209</v>
       </c>
       <c r="B135" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C135" t="s">
         <v>69</v>
       </c>
       <c r="D135"/>
       <c r="E135" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F135" t="s">
         <v>60</v>
@@ -14260,17 +14266,17 @@
         <v>102</v>
       </c>
       <c r="J135" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K135"/>
       <c r="L135" t="s">
         <v>59</v>
       </c>
       <c r="M135" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N135" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="O135" t="s">
         <v>64</v>
@@ -14283,7 +14289,7 @@
         <v>63</v>
       </c>
       <c r="S135" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="T135"/>
       <c r="U135"/>
@@ -14300,14 +14306,14 @@
         <v>209</v>
       </c>
       <c r="B136" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C136" t="s">
         <v>69</v>
       </c>
       <c r="D136"/>
       <c r="E136" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F136" t="s">
         <v>60</v>
@@ -14329,10 +14335,10 @@
         <v>59</v>
       </c>
       <c r="M136" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="N136" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="O136" t="s">
         <v>64</v>
@@ -14345,7 +14351,7 @@
         <v>63</v>
       </c>
       <c r="S136" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="T136"/>
       <c r="U136"/>
@@ -14362,14 +14368,14 @@
         <v>209</v>
       </c>
       <c r="B137" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C137" t="s">
         <v>69</v>
       </c>
       <c r="D137"/>
       <c r="E137" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F137" t="s">
         <v>60</v>
@@ -14391,10 +14397,10 @@
         <v>59</v>
       </c>
       <c r="M137" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="N137" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="O137" t="s">
         <v>64</v>
@@ -14407,7 +14413,7 @@
         <v>63</v>
       </c>
       <c r="S137" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="T137"/>
       <c r="U137"/>
@@ -14424,14 +14430,14 @@
         <v>209</v>
       </c>
       <c r="B138" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C138" t="s">
         <v>69</v>
       </c>
       <c r="D138"/>
       <c r="E138" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F138" t="s">
         <v>60</v>
@@ -14446,17 +14452,17 @@
         <v>102</v>
       </c>
       <c r="J138" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K138"/>
       <c r="L138" t="s">
         <v>59</v>
       </c>
       <c r="M138" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N138" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O138" t="s">
         <v>64</v>
@@ -14469,7 +14475,7 @@
         <v>63</v>
       </c>
       <c r="S138" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="T138"/>
       <c r="U138"/>
@@ -14486,14 +14492,14 @@
         <v>209</v>
       </c>
       <c r="B139" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C139" t="s">
         <v>69</v>
       </c>
       <c r="D139"/>
       <c r="E139" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F139" t="s">
         <v>60</v>
@@ -14508,17 +14514,17 @@
         <v>102</v>
       </c>
       <c r="J139" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K139"/>
       <c r="L139" t="s">
         <v>59</v>
       </c>
       <c r="M139" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N139" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="O139" t="s">
         <v>64</v>
@@ -14531,7 +14537,7 @@
         <v>63</v>
       </c>
       <c r="S139" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="T139"/>
       <c r="U139"/>
@@ -14548,14 +14554,14 @@
         <v>209</v>
       </c>
       <c r="B140" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C140" t="s">
         <v>69</v>
       </c>
       <c r="D140"/>
       <c r="E140" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F140" t="s">
         <v>60</v>
@@ -14577,10 +14583,10 @@
         <v>59</v>
       </c>
       <c r="M140" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="N140" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="O140" t="s">
         <v>64</v>
@@ -14593,7 +14599,7 @@
         <v>63</v>
       </c>
       <c r="S140" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="T140"/>
       <c r="U140"/>
@@ -14610,14 +14616,14 @@
         <v>209</v>
       </c>
       <c r="B141" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C141" t="s">
         <v>69</v>
       </c>
       <c r="D141"/>
       <c r="E141" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F141" t="s">
         <v>60</v>
@@ -14639,10 +14645,10 @@
         <v>59</v>
       </c>
       <c r="M141" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N141" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="O141" t="s">
         <v>64</v>
@@ -14655,7 +14661,7 @@
         <v>63</v>
       </c>
       <c r="S141" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="T141"/>
       <c r="U141"/>
@@ -14672,14 +14678,14 @@
         <v>209</v>
       </c>
       <c r="B142" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C142" t="s">
         <v>69</v>
       </c>
       <c r="D142"/>
       <c r="E142" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F142" t="s">
         <v>60</v>
@@ -14701,10 +14707,10 @@
         <v>59</v>
       </c>
       <c r="M142" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N142" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="O142" t="s">
         <v>64</v>
@@ -14717,7 +14723,7 @@
         <v>63</v>
       </c>
       <c r="S142" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="T142"/>
       <c r="U142"/>
@@ -14734,14 +14740,14 @@
         <v>209</v>
       </c>
       <c r="B143" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C143" t="s">
         <v>69</v>
       </c>
       <c r="D143"/>
       <c r="E143" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F143" t="s">
         <v>60</v>
@@ -14756,17 +14762,17 @@
         <v>102</v>
       </c>
       <c r="J143" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K143"/>
       <c r="L143" t="s">
         <v>59</v>
       </c>
       <c r="M143" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="N143" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="O143" t="s">
         <v>64</v>
@@ -14779,7 +14785,7 @@
         <v>63</v>
       </c>
       <c r="S143" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="T143"/>
       <c r="U143"/>
@@ -14796,14 +14802,14 @@
         <v>209</v>
       </c>
       <c r="B144" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C144" t="s">
         <v>69</v>
       </c>
       <c r="D144"/>
       <c r="E144" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F144" t="s">
         <v>60</v>
@@ -14818,17 +14824,17 @@
         <v>102</v>
       </c>
       <c r="J144" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K144"/>
       <c r="L144" t="s">
         <v>59</v>
       </c>
       <c r="M144" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N144" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O144" t="s">
         <v>64</v>
@@ -14841,7 +14847,7 @@
         <v>63</v>
       </c>
       <c r="S144" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="T144"/>
       <c r="U144"/>
@@ -14858,14 +14864,14 @@
         <v>209</v>
       </c>
       <c r="B145" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C145" t="s">
         <v>69</v>
       </c>
       <c r="D145"/>
       <c r="E145" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F145" t="s">
         <v>60</v>
@@ -14880,17 +14886,17 @@
         <v>102</v>
       </c>
       <c r="J145" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K145"/>
       <c r="L145" t="s">
         <v>59</v>
       </c>
       <c r="M145" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N145" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="O145" t="s">
         <v>64</v>
@@ -14903,7 +14909,7 @@
         <v>63</v>
       </c>
       <c r="S145" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="T145"/>
       <c r="U145"/>
@@ -14920,14 +14926,14 @@
         <v>209</v>
       </c>
       <c r="B146" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="C146" t="s">
         <v>69</v>
       </c>
       <c r="D146"/>
       <c r="E146" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F146" t="s">
         <v>60</v>
@@ -14949,10 +14955,10 @@
         <v>59</v>
       </c>
       <c r="M146" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="N146" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="O146" t="s">
         <v>64</v>
@@ -14965,7 +14971,7 @@
         <v>63</v>
       </c>
       <c r="S146" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="T146"/>
       <c r="U146"/>
@@ -14982,14 +14988,14 @@
         <v>209</v>
       </c>
       <c r="B147" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C147" t="s">
         <v>69</v>
       </c>
       <c r="D147"/>
       <c r="E147" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F147" t="s">
         <v>60</v>
@@ -15011,10 +15017,10 @@
         <v>59</v>
       </c>
       <c r="M147" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="N147" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="O147" t="s">
         <v>64</v>
@@ -15027,7 +15033,7 @@
         <v>63</v>
       </c>
       <c r="S147" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="T147"/>
       <c r="U147"/>
@@ -15044,14 +15050,14 @@
         <v>209</v>
       </c>
       <c r="B148" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C148" t="s">
         <v>69</v>
       </c>
       <c r="D148"/>
       <c r="E148" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F148" t="s">
         <v>60</v>
@@ -15066,17 +15072,17 @@
         <v>102</v>
       </c>
       <c r="J148" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K148"/>
       <c r="L148" t="s">
         <v>59</v>
       </c>
       <c r="M148" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N148" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O148" t="s">
         <v>64</v>
@@ -15089,7 +15095,7 @@
         <v>63</v>
       </c>
       <c r="S148" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="T148"/>
       <c r="U148"/>
@@ -15106,14 +15112,14 @@
         <v>209</v>
       </c>
       <c r="B149" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C149" t="s">
         <v>69</v>
       </c>
       <c r="D149"/>
       <c r="E149" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F149" t="s">
         <v>60</v>
@@ -15128,17 +15134,17 @@
         <v>102</v>
       </c>
       <c r="J149" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K149"/>
       <c r="L149" t="s">
         <v>59</v>
       </c>
       <c r="M149" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N149" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="O149" t="s">
         <v>64</v>
@@ -15151,7 +15157,7 @@
         <v>63</v>
       </c>
       <c r="S149" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="T149"/>
       <c r="U149"/>
@@ -15168,14 +15174,14 @@
         <v>209</v>
       </c>
       <c r="B150" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C150" t="s">
         <v>69</v>
       </c>
       <c r="D150"/>
       <c r="E150" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F150" t="s">
         <v>60</v>
@@ -15197,10 +15203,10 @@
         <v>59</v>
       </c>
       <c r="M150" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="N150" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="O150" t="s">
         <v>64</v>
@@ -15213,7 +15219,7 @@
         <v>63</v>
       </c>
       <c r="S150" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="T150"/>
       <c r="U150"/>
@@ -15230,14 +15236,14 @@
         <v>209</v>
       </c>
       <c r="B151" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C151" t="s">
         <v>69</v>
       </c>
       <c r="D151"/>
       <c r="E151" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F151" t="s">
         <v>60</v>
@@ -15259,10 +15265,10 @@
         <v>59</v>
       </c>
       <c r="M151" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N151" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="O151" t="s">
         <v>64</v>
@@ -15275,7 +15281,7 @@
         <v>63</v>
       </c>
       <c r="S151" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="T151"/>
       <c r="U151"/>
@@ -15292,14 +15298,14 @@
         <v>209</v>
       </c>
       <c r="B152" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C152" t="s">
         <v>69</v>
       </c>
       <c r="D152"/>
       <c r="E152" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F152" t="s">
         <v>60</v>
@@ -15321,10 +15327,10 @@
         <v>59</v>
       </c>
       <c r="M152" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N152" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="O152" t="s">
         <v>64</v>
@@ -15337,7 +15343,7 @@
         <v>63</v>
       </c>
       <c r="S152" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="T152"/>
       <c r="U152"/>
@@ -15354,14 +15360,14 @@
         <v>209</v>
       </c>
       <c r="B153" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C153" t="s">
         <v>69</v>
       </c>
       <c r="D153"/>
       <c r="E153" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F153" t="s">
         <v>60</v>
@@ -15376,17 +15382,17 @@
         <v>102</v>
       </c>
       <c r="J153" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K153"/>
       <c r="L153" t="s">
         <v>59</v>
       </c>
       <c r="M153" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="N153" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="O153" t="s">
         <v>64</v>
@@ -15399,7 +15405,7 @@
         <v>63</v>
       </c>
       <c r="S153" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="T153"/>
       <c r="U153"/>
@@ -15416,14 +15422,14 @@
         <v>209</v>
       </c>
       <c r="B154" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C154" t="s">
         <v>69</v>
       </c>
       <c r="D154"/>
       <c r="E154" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F154" t="s">
         <v>60</v>
@@ -15438,17 +15444,17 @@
         <v>102</v>
       </c>
       <c r="J154" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K154"/>
       <c r="L154" t="s">
         <v>59</v>
       </c>
       <c r="M154" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N154" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O154" t="s">
         <v>64</v>
@@ -15461,7 +15467,7 @@
         <v>63</v>
       </c>
       <c r="S154" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="T154"/>
       <c r="U154"/>
@@ -15478,14 +15484,14 @@
         <v>209</v>
       </c>
       <c r="B155" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C155" t="s">
         <v>69</v>
       </c>
       <c r="D155"/>
       <c r="E155" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F155" t="s">
         <v>60</v>
@@ -15500,17 +15506,17 @@
         <v>102</v>
       </c>
       <c r="J155" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K155"/>
       <c r="L155" t="s">
         <v>59</v>
       </c>
       <c r="M155" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N155" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="O155" t="s">
         <v>64</v>
@@ -15523,7 +15529,7 @@
         <v>63</v>
       </c>
       <c r="S155" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="T155"/>
       <c r="U155"/>
@@ -15540,14 +15546,14 @@
         <v>209</v>
       </c>
       <c r="B156" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C156" t="s">
         <v>69</v>
       </c>
       <c r="D156"/>
       <c r="E156" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F156" t="s">
         <v>60</v>
@@ -15569,10 +15575,10 @@
         <v>59</v>
       </c>
       <c r="M156" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="N156" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="O156" t="s">
         <v>64</v>
@@ -15585,7 +15591,7 @@
         <v>63</v>
       </c>
       <c r="S156" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="T156"/>
       <c r="U156"/>
@@ -15602,14 +15608,14 @@
         <v>209</v>
       </c>
       <c r="B157" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C157" t="s">
         <v>69</v>
       </c>
       <c r="D157"/>
       <c r="E157" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F157" t="s">
         <v>60</v>
@@ -15631,10 +15637,10 @@
         <v>59</v>
       </c>
       <c r="M157" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="N157" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="O157" t="s">
         <v>64</v>
@@ -15647,7 +15653,7 @@
         <v>63</v>
       </c>
       <c r="S157" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="T157"/>
       <c r="U157"/>
@@ -15664,14 +15670,14 @@
         <v>209</v>
       </c>
       <c r="B158" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C158" t="s">
         <v>69</v>
       </c>
       <c r="D158"/>
       <c r="E158" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F158" t="s">
         <v>60</v>
@@ -15686,17 +15692,17 @@
         <v>102</v>
       </c>
       <c r="J158" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K158"/>
       <c r="L158" t="s">
         <v>59</v>
       </c>
       <c r="M158" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N158" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O158" t="s">
         <v>64</v>
@@ -15709,7 +15715,7 @@
         <v>63</v>
       </c>
       <c r="S158" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="T158"/>
       <c r="U158"/>
@@ -15726,14 +15732,14 @@
         <v>209</v>
       </c>
       <c r="B159" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="C159" t="s">
         <v>69</v>
       </c>
       <c r="D159"/>
       <c r="E159" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F159" t="s">
         <v>60</v>
@@ -15748,17 +15754,17 @@
         <v>102</v>
       </c>
       <c r="J159" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K159"/>
       <c r="L159" t="s">
         <v>59</v>
       </c>
       <c r="M159" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N159" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="O159" t="s">
         <v>64</v>
@@ -15771,7 +15777,7 @@
         <v>63</v>
       </c>
       <c r="S159" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="T159"/>
       <c r="U159"/>
@@ -15788,14 +15794,14 @@
         <v>209</v>
       </c>
       <c r="B160" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C160" t="s">
         <v>69</v>
       </c>
       <c r="D160"/>
       <c r="E160" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F160" t="s">
         <v>60</v>
@@ -15817,10 +15823,10 @@
         <v>59</v>
       </c>
       <c r="M160" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="N160" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="O160" t="s">
         <v>64</v>
@@ -15833,7 +15839,7 @@
         <v>63</v>
       </c>
       <c r="S160" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="T160"/>
       <c r="U160"/>
@@ -15850,14 +15856,14 @@
         <v>209</v>
       </c>
       <c r="B161" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C161" t="s">
         <v>69</v>
       </c>
       <c r="D161"/>
       <c r="E161" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F161" t="s">
         <v>60</v>
@@ -15879,10 +15885,10 @@
         <v>59</v>
       </c>
       <c r="M161" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N161" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="O161" t="s">
         <v>64</v>
@@ -15895,7 +15901,7 @@
         <v>63</v>
       </c>
       <c r="S161" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="T161"/>
       <c r="U161"/>
@@ -15912,14 +15918,14 @@
         <v>209</v>
       </c>
       <c r="B162" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C162" t="s">
         <v>69</v>
       </c>
       <c r="D162"/>
       <c r="E162" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F162" t="s">
         <v>60</v>
@@ -15941,10 +15947,10 @@
         <v>59</v>
       </c>
       <c r="M162" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N162" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="O162" t="s">
         <v>64</v>
@@ -15957,7 +15963,7 @@
         <v>63</v>
       </c>
       <c r="S162" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="T162"/>
       <c r="U162"/>
@@ -15974,14 +15980,14 @@
         <v>209</v>
       </c>
       <c r="B163" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C163" t="s">
         <v>69</v>
       </c>
       <c r="D163"/>
       <c r="E163" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F163" t="s">
         <v>60</v>
@@ -15996,17 +16002,17 @@
         <v>102</v>
       </c>
       <c r="J163" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K163"/>
       <c r="L163" t="s">
         <v>59</v>
       </c>
       <c r="M163" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="N163" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="O163" t="s">
         <v>64</v>
@@ -16019,7 +16025,7 @@
         <v>63</v>
       </c>
       <c r="S163" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="T163"/>
       <c r="U163"/>
@@ -16036,14 +16042,14 @@
         <v>209</v>
       </c>
       <c r="B164" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C164" t="s">
         <v>69</v>
       </c>
       <c r="D164"/>
       <c r="E164" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F164" t="s">
         <v>60</v>
@@ -16058,17 +16064,17 @@
         <v>102</v>
       </c>
       <c r="J164" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K164"/>
       <c r="L164" t="s">
         <v>59</v>
       </c>
       <c r="M164" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N164" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O164" t="s">
         <v>64</v>
@@ -16081,7 +16087,7 @@
         <v>63</v>
       </c>
       <c r="S164" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="T164"/>
       <c r="U164"/>
@@ -16098,14 +16104,14 @@
         <v>209</v>
       </c>
       <c r="B165" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="C165" t="s">
         <v>69</v>
       </c>
       <c r="D165"/>
       <c r="E165" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F165" t="s">
         <v>60</v>
@@ -16120,17 +16126,17 @@
         <v>102</v>
       </c>
       <c r="J165" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K165"/>
       <c r="L165" t="s">
         <v>59</v>
       </c>
       <c r="M165" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N165" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="O165" t="s">
         <v>64</v>
@@ -16143,7 +16149,7 @@
         <v>63</v>
       </c>
       <c r="S165" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="T165"/>
       <c r="U165"/>
@@ -16160,14 +16166,14 @@
         <v>209</v>
       </c>
       <c r="B166" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="C166" t="s">
         <v>69</v>
       </c>
       <c r="D166"/>
       <c r="E166" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F166" t="s">
         <v>60</v>
@@ -16189,10 +16195,10 @@
         <v>59</v>
       </c>
       <c r="M166" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="N166" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="O166" t="s">
         <v>64</v>
@@ -16205,7 +16211,7 @@
         <v>63</v>
       </c>
       <c r="S166" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="T166"/>
       <c r="U166"/>
@@ -16222,14 +16228,14 @@
         <v>209</v>
       </c>
       <c r="B167" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C167" t="s">
         <v>69</v>
       </c>
       <c r="D167"/>
       <c r="E167" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F167" t="s">
         <v>60</v>
@@ -16251,10 +16257,10 @@
         <v>59</v>
       </c>
       <c r="M167" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="N167" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="O167" t="s">
         <v>64</v>
@@ -16267,7 +16273,7 @@
         <v>63</v>
       </c>
       <c r="S167" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="T167"/>
       <c r="U167"/>
@@ -16284,14 +16290,14 @@
         <v>209</v>
       </c>
       <c r="B168" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="C168" t="s">
         <v>69</v>
       </c>
       <c r="D168"/>
       <c r="E168" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F168" t="s">
         <v>60</v>
@@ -16306,17 +16312,17 @@
         <v>102</v>
       </c>
       <c r="J168" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K168"/>
       <c r="L168" t="s">
         <v>59</v>
       </c>
       <c r="M168" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N168" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O168" t="s">
         <v>64</v>
@@ -16329,7 +16335,7 @@
         <v>63</v>
       </c>
       <c r="S168" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="T168"/>
       <c r="U168"/>
@@ -16346,14 +16352,14 @@
         <v>209</v>
       </c>
       <c r="B169" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="C169" t="s">
         <v>69</v>
       </c>
       <c r="D169"/>
       <c r="E169" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F169" t="s">
         <v>60</v>
@@ -16368,17 +16374,17 @@
         <v>102</v>
       </c>
       <c r="J169" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K169"/>
       <c r="L169" t="s">
         <v>59</v>
       </c>
       <c r="M169" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N169" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="O169" t="s">
         <v>64</v>
@@ -16391,7 +16397,7 @@
         <v>63</v>
       </c>
       <c r="S169" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="T169"/>
       <c r="U169"/>
@@ -16408,14 +16414,14 @@
         <v>209</v>
       </c>
       <c r="B170" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="C170" t="s">
         <v>69</v>
       </c>
       <c r="D170"/>
       <c r="E170" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F170" t="s">
         <v>60</v>
@@ -16437,10 +16443,10 @@
         <v>59</v>
       </c>
       <c r="M170" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="N170" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="O170" t="s">
         <v>64</v>
@@ -16453,7 +16459,7 @@
         <v>63</v>
       </c>
       <c r="S170" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="T170"/>
       <c r="U170"/>
@@ -16470,14 +16476,14 @@
         <v>209</v>
       </c>
       <c r="B171" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C171" t="s">
         <v>69</v>
       </c>
       <c r="D171"/>
       <c r="E171" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F171" t="s">
         <v>60</v>
@@ -16499,10 +16505,10 @@
         <v>59</v>
       </c>
       <c r="M171" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N171" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="O171" t="s">
         <v>64</v>
@@ -16515,7 +16521,7 @@
         <v>63</v>
       </c>
       <c r="S171" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="T171"/>
       <c r="U171"/>
@@ -16532,14 +16538,14 @@
         <v>209</v>
       </c>
       <c r="B172" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="C172" t="s">
         <v>69</v>
       </c>
       <c r="D172"/>
       <c r="E172" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F172" t="s">
         <v>60</v>
@@ -16561,10 +16567,10 @@
         <v>59</v>
       </c>
       <c r="M172" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N172" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="O172" t="s">
         <v>64</v>
@@ -16577,7 +16583,7 @@
         <v>63</v>
       </c>
       <c r="S172" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="T172"/>
       <c r="U172"/>
@@ -16594,14 +16600,14 @@
         <v>209</v>
       </c>
       <c r="B173" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C173" t="s">
         <v>69</v>
       </c>
       <c r="D173"/>
       <c r="E173" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F173" t="s">
         <v>60</v>
@@ -16616,17 +16622,17 @@
         <v>102</v>
       </c>
       <c r="J173" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K173"/>
       <c r="L173" t="s">
         <v>59</v>
       </c>
       <c r="M173" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="N173" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="O173" t="s">
         <v>64</v>
@@ -16639,7 +16645,7 @@
         <v>63</v>
       </c>
       <c r="S173" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="T173"/>
       <c r="U173"/>
@@ -16656,14 +16662,14 @@
         <v>209</v>
       </c>
       <c r="B174" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C174" t="s">
         <v>69</v>
       </c>
       <c r="D174"/>
       <c r="E174" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F174" t="s">
         <v>60</v>
@@ -16678,17 +16684,17 @@
         <v>102</v>
       </c>
       <c r="J174" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K174"/>
       <c r="L174" t="s">
         <v>59</v>
       </c>
       <c r="M174" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N174" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O174" t="s">
         <v>64</v>
@@ -16701,7 +16707,7 @@
         <v>63</v>
       </c>
       <c r="S174" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="T174"/>
       <c r="U174"/>
@@ -16718,14 +16724,14 @@
         <v>209</v>
       </c>
       <c r="B175" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C175" t="s">
         <v>69</v>
       </c>
       <c r="D175"/>
       <c r="E175" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F175" t="s">
         <v>60</v>
@@ -16740,17 +16746,17 @@
         <v>102</v>
       </c>
       <c r="J175" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K175"/>
       <c r="L175" t="s">
         <v>59</v>
       </c>
       <c r="M175" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N175" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="O175" t="s">
         <v>64</v>
@@ -16763,7 +16769,7 @@
         <v>63</v>
       </c>
       <c r="S175" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="T175"/>
       <c r="U175"/>
@@ -16780,14 +16786,14 @@
         <v>209</v>
       </c>
       <c r="B176" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="C176" t="s">
         <v>69</v>
       </c>
       <c r="D176"/>
       <c r="E176" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F176" t="s">
         <v>60</v>
@@ -16809,10 +16815,10 @@
         <v>59</v>
       </c>
       <c r="M176" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="N176" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="O176" t="s">
         <v>64</v>
@@ -16825,7 +16831,7 @@
         <v>63</v>
       </c>
       <c r="S176" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="T176"/>
       <c r="U176"/>
@@ -16842,14 +16848,14 @@
         <v>209</v>
       </c>
       <c r="B177" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="C177" t="s">
         <v>69</v>
       </c>
       <c r="D177"/>
       <c r="E177" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F177" t="s">
         <v>60</v>
@@ -16871,10 +16877,10 @@
         <v>59</v>
       </c>
       <c r="M177" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="N177" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="O177" t="s">
         <v>64</v>
@@ -16887,7 +16893,7 @@
         <v>63</v>
       </c>
       <c r="S177" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="T177"/>
       <c r="U177"/>
@@ -16904,14 +16910,14 @@
         <v>209</v>
       </c>
       <c r="B178" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C178" t="s">
         <v>69</v>
       </c>
       <c r="D178"/>
       <c r="E178" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F178" t="s">
         <v>60</v>
@@ -16926,17 +16932,17 @@
         <v>102</v>
       </c>
       <c r="J178" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K178"/>
       <c r="L178" t="s">
         <v>59</v>
       </c>
       <c r="M178" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N178" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O178" t="s">
         <v>64</v>
@@ -16949,7 +16955,7 @@
         <v>63</v>
       </c>
       <c r="S178" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="T178"/>
       <c r="U178"/>
@@ -16966,14 +16972,14 @@
         <v>209</v>
       </c>
       <c r="B179" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C179" t="s">
         <v>69</v>
       </c>
       <c r="D179"/>
       <c r="E179" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F179" t="s">
         <v>60</v>
@@ -16988,17 +16994,17 @@
         <v>102</v>
       </c>
       <c r="J179" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K179"/>
       <c r="L179" t="s">
         <v>59</v>
       </c>
       <c r="M179" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N179" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="O179" t="s">
         <v>64</v>
@@ -17011,7 +17017,7 @@
         <v>63</v>
       </c>
       <c r="S179" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="T179"/>
       <c r="U179"/>
@@ -17028,14 +17034,14 @@
         <v>209</v>
       </c>
       <c r="B180" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="C180" t="s">
         <v>69</v>
       </c>
       <c r="D180"/>
       <c r="E180" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F180" t="s">
         <v>60</v>
@@ -17057,10 +17063,10 @@
         <v>59</v>
       </c>
       <c r="M180" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="N180" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="O180" t="s">
         <v>64</v>
@@ -17073,7 +17079,7 @@
         <v>63</v>
       </c>
       <c r="S180" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="T180"/>
       <c r="U180"/>
@@ -17090,14 +17096,14 @@
         <v>209</v>
       </c>
       <c r="B181" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C181" t="s">
         <v>69</v>
       </c>
       <c r="D181"/>
       <c r="E181" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F181" t="s">
         <v>60</v>
@@ -17119,10 +17125,10 @@
         <v>59</v>
       </c>
       <c r="M181" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N181" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="O181" t="s">
         <v>64</v>
@@ -17135,7 +17141,7 @@
         <v>63</v>
       </c>
       <c r="S181" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="T181"/>
       <c r="U181"/>
@@ -17152,14 +17158,14 @@
         <v>209</v>
       </c>
       <c r="B182" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="C182" t="s">
         <v>69</v>
       </c>
       <c r="D182"/>
       <c r="E182" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F182" t="s">
         <v>60</v>
@@ -17181,10 +17187,10 @@
         <v>59</v>
       </c>
       <c r="M182" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N182" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="O182" t="s">
         <v>64</v>
@@ -17197,7 +17203,7 @@
         <v>63</v>
       </c>
       <c r="S182" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="T182"/>
       <c r="U182"/>
@@ -17214,14 +17220,14 @@
         <v>209</v>
       </c>
       <c r="B183" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C183" t="s">
         <v>69</v>
       </c>
       <c r="D183"/>
       <c r="E183" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F183" t="s">
         <v>60</v>
@@ -17236,17 +17242,17 @@
         <v>102</v>
       </c>
       <c r="J183" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K183"/>
       <c r="L183" t="s">
         <v>59</v>
       </c>
       <c r="M183" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="N183" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="O183" t="s">
         <v>64</v>
@@ -17259,7 +17265,7 @@
         <v>63</v>
       </c>
       <c r="S183" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="T183"/>
       <c r="U183"/>
@@ -17276,14 +17282,14 @@
         <v>209</v>
       </c>
       <c r="B184" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="C184" t="s">
         <v>69</v>
       </c>
       <c r="D184"/>
       <c r="E184" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F184" t="s">
         <v>60</v>
@@ -17298,17 +17304,17 @@
         <v>102</v>
       </c>
       <c r="J184" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K184"/>
       <c r="L184" t="s">
         <v>59</v>
       </c>
       <c r="M184" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N184" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O184" t="s">
         <v>64</v>
@@ -17321,7 +17327,7 @@
         <v>63</v>
       </c>
       <c r="S184" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="T184"/>
       <c r="U184"/>
@@ -17338,14 +17344,14 @@
         <v>209</v>
       </c>
       <c r="B185" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="C185" t="s">
         <v>69</v>
       </c>
       <c r="D185"/>
       <c r="E185" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F185" t="s">
         <v>60</v>
@@ -17360,17 +17366,17 @@
         <v>102</v>
       </c>
       <c r="J185" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K185"/>
       <c r="L185" t="s">
         <v>59</v>
       </c>
       <c r="M185" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N185" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="O185" t="s">
         <v>64</v>
@@ -17383,7 +17389,7 @@
         <v>63</v>
       </c>
       <c r="S185" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="T185"/>
       <c r="U185"/>
@@ -17400,14 +17406,14 @@
         <v>209</v>
       </c>
       <c r="B186" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C186" t="s">
         <v>69</v>
       </c>
       <c r="D186"/>
       <c r="E186" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F186" t="s">
         <v>60</v>
@@ -17429,10 +17435,10 @@
         <v>59</v>
       </c>
       <c r="M186" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="N186" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="O186" t="s">
         <v>64</v>
@@ -17445,7 +17451,7 @@
         <v>63</v>
       </c>
       <c r="S186" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="T186"/>
       <c r="U186"/>
@@ -17462,14 +17468,14 @@
         <v>209</v>
       </c>
       <c r="B187" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C187" t="s">
         <v>69</v>
       </c>
       <c r="D187"/>
       <c r="E187" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F187" t="s">
         <v>60</v>
@@ -17491,10 +17497,10 @@
         <v>59</v>
       </c>
       <c r="M187" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="N187" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="O187" t="s">
         <v>64</v>
@@ -17507,7 +17513,7 @@
         <v>63</v>
       </c>
       <c r="S187" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="T187"/>
       <c r="U187"/>
@@ -17524,14 +17530,14 @@
         <v>209</v>
       </c>
       <c r="B188" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C188" t="s">
         <v>69</v>
       </c>
       <c r="D188"/>
       <c r="E188" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F188" t="s">
         <v>60</v>
@@ -17546,17 +17552,17 @@
         <v>102</v>
       </c>
       <c r="J188" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K188"/>
       <c r="L188" t="s">
         <v>59</v>
       </c>
       <c r="M188" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N188" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O188" t="s">
         <v>64</v>
@@ -17569,7 +17575,7 @@
         <v>63</v>
       </c>
       <c r="S188" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="T188"/>
       <c r="U188"/>
@@ -17586,14 +17592,14 @@
         <v>209</v>
       </c>
       <c r="B189" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="C189" t="s">
         <v>69</v>
       </c>
       <c r="D189"/>
       <c r="E189" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F189" t="s">
         <v>60</v>
@@ -17608,17 +17614,17 @@
         <v>102</v>
       </c>
       <c r="J189" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K189"/>
       <c r="L189" t="s">
         <v>59</v>
       </c>
       <c r="M189" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N189" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="O189" t="s">
         <v>64</v>
@@ -17631,7 +17637,7 @@
         <v>63</v>
       </c>
       <c r="S189" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="T189"/>
       <c r="U189"/>
@@ -17648,14 +17654,14 @@
         <v>209</v>
       </c>
       <c r="B190" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="C190" t="s">
         <v>69</v>
       </c>
       <c r="D190"/>
       <c r="E190" t="s">
-        <v>184</v>
+        <v>239</v>
       </c>
       <c r="F190" t="s">
         <v>60</v>
@@ -17677,10 +17683,10 @@
         <v>59</v>
       </c>
       <c r="M190" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="N190" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="O190" t="s">
         <v>64</v>
@@ -17693,7 +17699,7 @@
         <v>63</v>
       </c>
       <c r="S190" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="T190"/>
       <c r="U190"/>
@@ -17710,7 +17716,7 @@
         <v>209</v>
       </c>
       <c r="B191" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C191" t="s">
         <v>69</v>
@@ -17739,10 +17745,10 @@
         <v>59</v>
       </c>
       <c r="M191" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N191" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="O191" t="s">
         <v>64</v>
@@ -17755,7 +17761,7 @@
         <v>63</v>
       </c>
       <c r="S191" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="T191"/>
       <c r="U191"/>
@@ -17772,7 +17778,7 @@
         <v>209</v>
       </c>
       <c r="B192" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="C192" t="s">
         <v>69</v>
@@ -17801,10 +17807,10 @@
         <v>59</v>
       </c>
       <c r="M192" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="N192" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="O192" t="s">
         <v>64</v>
@@ -17817,7 +17823,7 @@
         <v>63</v>
       </c>
       <c r="S192" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="T192"/>
       <c r="U192"/>
@@ -17834,7 +17840,7 @@
         <v>209</v>
       </c>
       <c r="B193" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C193" t="s">
         <v>69</v>
@@ -17856,17 +17862,17 @@
         <v>102</v>
       </c>
       <c r="J193" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K193"/>
       <c r="L193" t="s">
         <v>59</v>
       </c>
       <c r="M193" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="N193" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="O193" t="s">
         <v>64</v>
@@ -17879,7 +17885,7 @@
         <v>63</v>
       </c>
       <c r="S193" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="T193"/>
       <c r="U193"/>
@@ -17896,7 +17902,7 @@
         <v>209</v>
       </c>
       <c r="B194" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="C194" t="s">
         <v>69</v>
@@ -17925,10 +17931,10 @@
         <v>59</v>
       </c>
       <c r="M194" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N194" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="O194" t="s">
         <v>64</v>
@@ -17941,7 +17947,7 @@
         <v>63</v>
       </c>
       <c r="S194" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="T194"/>
       <c r="U194"/>
@@ -17958,7 +17964,7 @@
         <v>209</v>
       </c>
       <c r="B195" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="C195" t="s">
         <v>69</v>
@@ -17987,10 +17993,10 @@
         <v>59</v>
       </c>
       <c r="M195" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="N195" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="O195" t="s">
         <v>64</v>
@@ -18003,7 +18009,7 @@
         <v>63</v>
       </c>
       <c r="S195" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="T195"/>
       <c r="U195"/>
@@ -18020,7 +18026,7 @@
         <v>209</v>
       </c>
       <c r="B196" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="C196" t="s">
         <v>69</v>
@@ -18042,17 +18048,17 @@
         <v>102</v>
       </c>
       <c r="J196" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K196"/>
       <c r="L196" t="s">
         <v>59</v>
       </c>
       <c r="M196" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="N196" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="O196" t="s">
         <v>64</v>
@@ -18065,7 +18071,7 @@
         <v>63</v>
       </c>
       <c r="S196" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="T196"/>
       <c r="U196"/>
@@ -18082,7 +18088,7 @@
         <v>209</v>
       </c>
       <c r="B197" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="C197" t="s">
         <v>69</v>
@@ -18111,10 +18117,10 @@
         <v>59</v>
       </c>
       <c r="M197" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N197" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="O197" t="s">
         <v>64</v>
@@ -18127,7 +18133,7 @@
         <v>63</v>
       </c>
       <c r="S197" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="T197"/>
       <c r="U197"/>
@@ -18144,7 +18150,7 @@
         <v>209</v>
       </c>
       <c r="B198" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C198" t="s">
         <v>69</v>
@@ -18173,10 +18179,10 @@
         <v>59</v>
       </c>
       <c r="M198" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="N198" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="O198" t="s">
         <v>64</v>
@@ -18189,7 +18195,7 @@
         <v>63</v>
       </c>
       <c r="S198" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="T198"/>
       <c r="U198"/>
@@ -18206,7 +18212,7 @@
         <v>209</v>
       </c>
       <c r="B199" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="C199" t="s">
         <v>69</v>
@@ -18228,17 +18234,17 @@
         <v>102</v>
       </c>
       <c r="J199" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K199"/>
       <c r="L199" t="s">
         <v>59</v>
       </c>
       <c r="M199" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="N199" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="O199" t="s">
         <v>64</v>
@@ -18251,7 +18257,7 @@
         <v>63</v>
       </c>
       <c r="S199" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="T199"/>
       <c r="U199"/>
@@ -18268,7 +18274,7 @@
         <v>209</v>
       </c>
       <c r="B200" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C200" t="s">
         <v>69</v>
@@ -18297,10 +18303,10 @@
         <v>59</v>
       </c>
       <c r="M200" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N200" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="O200" t="s">
         <v>64</v>
@@ -18313,7 +18319,7 @@
         <v>63</v>
       </c>
       <c r="S200" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="T200"/>
       <c r="U200"/>
@@ -18330,7 +18336,7 @@
         <v>209</v>
       </c>
       <c r="B201" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="C201" t="s">
         <v>69</v>
@@ -18359,10 +18365,10 @@
         <v>59</v>
       </c>
       <c r="M201" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="N201" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="O201" t="s">
         <v>64</v>
@@ -18375,7 +18381,7 @@
         <v>63</v>
       </c>
       <c r="S201" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="T201"/>
       <c r="U201"/>
@@ -18392,7 +18398,7 @@
         <v>209</v>
       </c>
       <c r="B202" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C202" t="s">
         <v>69</v>
@@ -18414,17 +18420,17 @@
         <v>102</v>
       </c>
       <c r="J202" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K202"/>
       <c r="L202" t="s">
         <v>59</v>
       </c>
       <c r="M202" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="N202" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="O202" t="s">
         <v>64</v>
@@ -18437,7 +18443,7 @@
         <v>63</v>
       </c>
       <c r="S202" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="T202"/>
       <c r="U202"/>
@@ -18454,7 +18460,7 @@
         <v>209</v>
       </c>
       <c r="B203" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="C203" t="s">
         <v>69</v>
@@ -18483,10 +18489,10 @@
         <v>59</v>
       </c>
       <c r="M203" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N203" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="O203" t="s">
         <v>64</v>
@@ -18499,7 +18505,7 @@
         <v>63</v>
       </c>
       <c r="S203" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="T203"/>
       <c r="U203"/>
@@ -18516,7 +18522,7 @@
         <v>209</v>
       </c>
       <c r="B204" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="C204" t="s">
         <v>69</v>
@@ -18545,10 +18551,10 @@
         <v>59</v>
       </c>
       <c r="M204" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="N204" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="O204" t="s">
         <v>64</v>
@@ -18561,7 +18567,7 @@
         <v>63</v>
       </c>
       <c r="S204" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="T204"/>
       <c r="U204"/>
@@ -18578,7 +18584,7 @@
         <v>209</v>
       </c>
       <c r="B205" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="C205" t="s">
         <v>69</v>
@@ -18600,17 +18606,17 @@
         <v>102</v>
       </c>
       <c r="J205" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K205"/>
       <c r="L205" t="s">
         <v>59</v>
       </c>
       <c r="M205" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="N205" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="O205" t="s">
         <v>64</v>
@@ -18623,7 +18629,7 @@
         <v>63</v>
       </c>
       <c r="S205" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="T205"/>
       <c r="U205"/>
@@ -18640,7 +18646,7 @@
         <v>209</v>
       </c>
       <c r="B206" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="C206" t="s">
         <v>69</v>
@@ -18669,10 +18675,10 @@
         <v>59</v>
       </c>
       <c r="M206" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N206" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="O206" t="s">
         <v>64</v>
@@ -18685,7 +18691,7 @@
         <v>63</v>
       </c>
       <c r="S206" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="T206"/>
       <c r="U206"/>
@@ -18702,7 +18708,7 @@
         <v>209</v>
       </c>
       <c r="B207" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="C207" t="s">
         <v>69</v>
@@ -18731,10 +18737,10 @@
         <v>59</v>
       </c>
       <c r="M207" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="N207" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="O207" t="s">
         <v>64</v>
@@ -18747,7 +18753,7 @@
         <v>63</v>
       </c>
       <c r="S207" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="T207"/>
       <c r="U207"/>
@@ -18764,7 +18770,7 @@
         <v>209</v>
       </c>
       <c r="B208" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="C208" t="s">
         <v>69</v>
@@ -18786,17 +18792,17 @@
         <v>102</v>
       </c>
       <c r="J208" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K208"/>
       <c r="L208" t="s">
         <v>59</v>
       </c>
       <c r="M208" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="N208" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="O208" t="s">
         <v>64</v>
@@ -18809,7 +18815,7 @@
         <v>63</v>
       </c>
       <c r="S208" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="T208"/>
       <c r="U208"/>
@@ -18826,7 +18832,7 @@
         <v>209</v>
       </c>
       <c r="B209" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="C209" t="s">
         <v>69</v>
@@ -18855,10 +18861,10 @@
         <v>59</v>
       </c>
       <c r="M209" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N209" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="O209" t="s">
         <v>64</v>
@@ -18871,7 +18877,7 @@
         <v>63</v>
       </c>
       <c r="S209" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="T209"/>
       <c r="U209"/>
@@ -18888,7 +18894,7 @@
         <v>209</v>
       </c>
       <c r="B210" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="C210" t="s">
         <v>69</v>
@@ -18917,10 +18923,10 @@
         <v>59</v>
       </c>
       <c r="M210" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="N210" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="O210" t="s">
         <v>64</v>
@@ -18933,7 +18939,7 @@
         <v>63</v>
       </c>
       <c r="S210" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="T210"/>
       <c r="U210"/>
@@ -18950,7 +18956,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="C211" t="s">
         <v>69</v>
@@ -18972,17 +18978,17 @@
         <v>102</v>
       </c>
       <c r="J211" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K211"/>
       <c r="L211" t="s">
         <v>59</v>
       </c>
       <c r="M211" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="N211" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="O211" t="s">
         <v>64</v>
@@ -18995,7 +19001,7 @@
         <v>63</v>
       </c>
       <c r="S211" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="T211"/>
       <c r="U211"/>
@@ -19012,7 +19018,7 @@
         <v>209</v>
       </c>
       <c r="B212" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="C212" t="s">
         <v>69</v>
@@ -19041,10 +19047,10 @@
         <v>59</v>
       </c>
       <c r="M212" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N212" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="O212" t="s">
         <v>64</v>
@@ -19057,7 +19063,7 @@
         <v>63</v>
       </c>
       <c r="S212" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="T212"/>
       <c r="U212"/>
@@ -19074,7 +19080,7 @@
         <v>209</v>
       </c>
       <c r="B213" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="C213" t="s">
         <v>69</v>
@@ -19103,10 +19109,10 @@
         <v>59</v>
       </c>
       <c r="M213" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="N213" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="O213" t="s">
         <v>64</v>
@@ -19119,7 +19125,7 @@
         <v>63</v>
       </c>
       <c r="S213" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="T213"/>
       <c r="U213"/>
@@ -19136,7 +19142,7 @@
         <v>209</v>
       </c>
       <c r="B214" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="C214" t="s">
         <v>69</v>
@@ -19158,17 +19164,17 @@
         <v>102</v>
       </c>
       <c r="J214" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K214"/>
       <c r="L214" t="s">
         <v>59</v>
       </c>
       <c r="M214" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="N214" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="O214" t="s">
         <v>64</v>
@@ -19181,7 +19187,7 @@
         <v>63</v>
       </c>
       <c r="S214" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="T214"/>
       <c r="U214"/>
@@ -19198,7 +19204,7 @@
         <v>209</v>
       </c>
       <c r="B215" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="C215" t="s">
         <v>69</v>
@@ -19227,10 +19233,10 @@
         <v>59</v>
       </c>
       <c r="M215" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N215" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="O215" t="s">
         <v>64</v>
@@ -19243,7 +19249,7 @@
         <v>63</v>
       </c>
       <c r="S215" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="T215"/>
       <c r="U215"/>
@@ -19260,7 +19266,7 @@
         <v>209</v>
       </c>
       <c r="B216" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="C216" t="s">
         <v>69</v>
@@ -19289,10 +19295,10 @@
         <v>59</v>
       </c>
       <c r="M216" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="N216" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="O216" t="s">
         <v>64</v>
@@ -19305,7 +19311,7 @@
         <v>63</v>
       </c>
       <c r="S216" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="T216"/>
       <c r="U216"/>
@@ -19322,7 +19328,7 @@
         <v>209</v>
       </c>
       <c r="B217" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="C217" t="s">
         <v>69</v>
@@ -19344,17 +19350,17 @@
         <v>102</v>
       </c>
       <c r="J217" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K217"/>
       <c r="L217" t="s">
         <v>59</v>
       </c>
       <c r="M217" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="N217" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="O217" t="s">
         <v>64</v>
@@ -19367,7 +19373,7 @@
         <v>63</v>
       </c>
       <c r="S217" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="T217"/>
       <c r="U217"/>
@@ -19384,7 +19390,7 @@
         <v>209</v>
       </c>
       <c r="B218" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C218" t="s">
         <v>69</v>
@@ -19413,10 +19419,10 @@
         <v>59</v>
       </c>
       <c r="M218" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N218" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="O218" t="s">
         <v>64</v>
@@ -19429,7 +19435,7 @@
         <v>63</v>
       </c>
       <c r="S218" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="T218"/>
       <c r="U218"/>
@@ -19446,7 +19452,7 @@
         <v>209</v>
       </c>
       <c r="B219" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="C219" t="s">
         <v>69</v>
@@ -19475,10 +19481,10 @@
         <v>59</v>
       </c>
       <c r="M219" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="N219" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="O219" t="s">
         <v>64</v>
@@ -19491,7 +19497,7 @@
         <v>63</v>
       </c>
       <c r="S219" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="T219"/>
       <c r="U219"/>
@@ -19508,7 +19514,7 @@
         <v>209</v>
       </c>
       <c r="B220" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="C220" t="s">
         <v>69</v>
@@ -19530,17 +19536,17 @@
         <v>102</v>
       </c>
       <c r="J220" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K220"/>
       <c r="L220" t="s">
         <v>59</v>
       </c>
       <c r="M220" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="N220" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="O220" t="s">
         <v>64</v>
@@ -19553,7 +19559,7 @@
         <v>63</v>
       </c>
       <c r="S220" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="T220"/>
       <c r="U220"/>

--- a/processed-data/19_data_uploads/03_manifest/manifest_open.xlsx
+++ b/processed-data/19_data_uploads/03_manifest/manifest_open.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="655">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="653">
   <si>
     <t xml:space="preserve">subject_name</t>
   </si>
@@ -533,7 +533,7 @@
     <t xml:space="preserve">lib_Br3942_1</t>
   </si>
   <si>
-    <t xml:space="preserve">10X Genomics Visium HD probe-based</t>
+    <t xml:space="preserve">10X Genomics Visium-HD; RNAseq_probe</t>
   </si>
   <si>
     <t xml:space="preserve">bulk</t>
@@ -569,7 +569,7 @@
     <t xml:space="preserve">lib_V13B23-280_1</t>
   </si>
   <si>
-    <t xml:space="preserve">10X Genomics Visium probe-based</t>
+    <t xml:space="preserve">10X Genomics Visium; RNAseq_probe</t>
   </si>
   <si>
     <t xml:space="preserve">lib_V13B23-285</t>
@@ -707,9 +707,6 @@
     <t xml:space="preserve">habenula_atlas_HD_spe_cell.rds</t>
   </si>
   <si>
-    <t xml:space="preserve">10X Genomics Visium-HD; RNAseq_probe</t>
-  </si>
-  <si>
     <t xml:space="preserve">counts</t>
   </si>
   <si>
@@ -732,9 +729,6 @@
   </si>
   <si>
     <t xml:space="preserve">habenula_atlas_visium_spe.rds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10X Genomics Visium; RNAseq_probe</t>
   </si>
   <si>
     <t xml:space="preserve">64ce6ae9151c71717bfb169f21d73f32</t>
@@ -6489,32 +6483,32 @@
       </c>
       <c r="D10"/>
       <c r="E10" t="s">
+        <v>172</v>
+      </c>
+      <c r="F10" t="s">
+        <v>60</v>
+      </c>
+      <c r="G10" t="s">
+        <v>61</v>
+      </c>
+      <c r="H10" t="s">
+        <v>62</v>
+      </c>
+      <c r="I10" t="s">
+        <v>102</v>
+      </c>
+      <c r="J10" t="s">
         <v>230</v>
-      </c>
-      <c r="F10" t="s">
-        <v>60</v>
-      </c>
-      <c r="G10" t="s">
-        <v>61</v>
-      </c>
-      <c r="H10" t="s">
-        <v>62</v>
-      </c>
-      <c r="I10" t="s">
-        <v>102</v>
-      </c>
-      <c r="J10" t="s">
-        <v>231</v>
       </c>
       <c r="K10"/>
       <c r="L10" t="s">
         <v>59</v>
       </c>
       <c r="M10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="N10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O10" t="s">
         <v>64</v>
@@ -6527,7 +6521,7 @@
         <v>63</v>
       </c>
       <c r="S10" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="T10"/>
       <c r="U10"/>
@@ -6538,7 +6532,7 @@
       <c r="Z10"/>
       <c r="AA10"/>
       <c r="AB10" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11">
@@ -6546,39 +6540,39 @@
         <v>209</v>
       </c>
       <c r="B11" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C11" t="s">
         <v>69</v>
       </c>
       <c r="D11"/>
       <c r="E11" t="s">
+        <v>172</v>
+      </c>
+      <c r="F11" t="s">
+        <v>60</v>
+      </c>
+      <c r="G11" t="s">
+        <v>61</v>
+      </c>
+      <c r="H11" t="s">
+        <v>62</v>
+      </c>
+      <c r="I11" t="s">
+        <v>102</v>
+      </c>
+      <c r="J11" t="s">
         <v>230</v>
-      </c>
-      <c r="F11" t="s">
-        <v>60</v>
-      </c>
-      <c r="G11" t="s">
-        <v>61</v>
-      </c>
-      <c r="H11" t="s">
-        <v>62</v>
-      </c>
-      <c r="I11" t="s">
-        <v>102</v>
-      </c>
-      <c r="J11" t="s">
-        <v>231</v>
       </c>
       <c r="K11"/>
       <c r="L11" t="s">
         <v>59</v>
       </c>
       <c r="M11" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="N11" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O11" t="s">
         <v>64</v>
@@ -6591,7 +6585,7 @@
         <v>63</v>
       </c>
       <c r="S11" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="T11"/>
       <c r="U11"/>
@@ -6602,7 +6596,7 @@
       <c r="Z11"/>
       <c r="AA11"/>
       <c r="AB11" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="12">
@@ -6610,14 +6604,14 @@
         <v>209</v>
       </c>
       <c r="B12" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C12" t="s">
         <v>69</v>
       </c>
       <c r="D12"/>
       <c r="E12" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F12" t="s">
         <v>60</v>
@@ -6632,17 +6626,17 @@
         <v>102</v>
       </c>
       <c r="J12" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K12"/>
       <c r="L12" t="s">
         <v>59</v>
       </c>
       <c r="M12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="N12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O12" t="s">
         <v>64</v>
@@ -6655,7 +6649,7 @@
         <v>63</v>
       </c>
       <c r="S12" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="T12"/>
       <c r="U12"/>
@@ -6666,7 +6660,7 @@
       <c r="Z12"/>
       <c r="AA12"/>
       <c r="AB12" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="13">
@@ -6674,14 +6668,14 @@
         <v>209</v>
       </c>
       <c r="B13" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C13" t="s">
         <v>69</v>
       </c>
       <c r="D13"/>
       <c r="E13" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F13" t="s">
         <v>60</v>
@@ -6696,17 +6690,17 @@
         <v>102</v>
       </c>
       <c r="J13" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K13"/>
       <c r="L13" t="s">
         <v>59</v>
       </c>
       <c r="M13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="N13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O13" t="s">
         <v>64</v>
@@ -6719,7 +6713,7 @@
         <v>63</v>
       </c>
       <c r="S13" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="T13"/>
       <c r="U13"/>
@@ -6730,7 +6724,7 @@
       <c r="Z13"/>
       <c r="AA13"/>
       <c r="AB13" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="14">
@@ -6738,7 +6732,7 @@
         <v>209</v>
       </c>
       <c r="B14" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C14" t="s">
         <v>69</v>
@@ -6760,17 +6754,17 @@
         <v>102</v>
       </c>
       <c r="J14" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K14"/>
       <c r="L14" t="s">
         <v>59</v>
       </c>
       <c r="M14" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="N14" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O14" t="s">
         <v>64</v>
@@ -6783,7 +6777,7 @@
         <v>63</v>
       </c>
       <c r="S14" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="T14"/>
       <c r="U14"/>
@@ -6794,7 +6788,7 @@
       <c r="Z14"/>
       <c r="AA14"/>
       <c r="AB14" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="15">
@@ -6802,7 +6796,7 @@
         <v>209</v>
       </c>
       <c r="B15" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C15" t="s">
         <v>69</v>
@@ -6824,17 +6818,17 @@
         <v>102</v>
       </c>
       <c r="J15" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K15"/>
       <c r="L15" t="s">
         <v>59</v>
       </c>
       <c r="M15" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="N15" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O15" t="s">
         <v>64</v>
@@ -6847,7 +6841,7 @@
         <v>63</v>
       </c>
       <c r="S15" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="T15"/>
       <c r="U15"/>
@@ -6858,7 +6852,7 @@
       <c r="Z15"/>
       <c r="AA15"/>
       <c r="AB15" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="16">
@@ -6866,14 +6860,14 @@
         <v>209</v>
       </c>
       <c r="B16" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C16" t="s">
         <v>69</v>
       </c>
       <c r="D16"/>
       <c r="E16" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
       <c r="F16" t="s">
         <v>60</v>
@@ -6895,10 +6889,10 @@
         <v>59</v>
       </c>
       <c r="M16" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="N16" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="O16" t="s">
         <v>64</v>
@@ -6911,7 +6905,7 @@
         <v>63</v>
       </c>
       <c r="S16" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="T16"/>
       <c r="U16"/>
@@ -6928,14 +6922,14 @@
         <v>209</v>
       </c>
       <c r="B17" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C17" t="s">
         <v>69</v>
       </c>
       <c r="D17"/>
       <c r="E17" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
       <c r="F17" t="s">
         <v>60</v>
@@ -6957,10 +6951,10 @@
         <v>59</v>
       </c>
       <c r="M17" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="N17" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="O17" t="s">
         <v>64</v>
@@ -6973,7 +6967,7 @@
         <v>63</v>
       </c>
       <c r="S17" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="T17"/>
       <c r="U17"/>
@@ -6990,39 +6984,39 @@
         <v>209</v>
       </c>
       <c r="B18" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C18" t="s">
         <v>69</v>
       </c>
       <c r="D18"/>
       <c r="E18" t="s">
+        <v>172</v>
+      </c>
+      <c r="F18" t="s">
+        <v>60</v>
+      </c>
+      <c r="G18" t="s">
+        <v>61</v>
+      </c>
+      <c r="H18" t="s">
+        <v>62</v>
+      </c>
+      <c r="I18" t="s">
+        <v>102</v>
+      </c>
+      <c r="J18" t="s">
         <v>230</v>
-      </c>
-      <c r="F18" t="s">
-        <v>60</v>
-      </c>
-      <c r="G18" t="s">
-        <v>61</v>
-      </c>
-      <c r="H18" t="s">
-        <v>62</v>
-      </c>
-      <c r="I18" t="s">
-        <v>102</v>
-      </c>
-      <c r="J18" t="s">
-        <v>231</v>
       </c>
       <c r="K18"/>
       <c r="L18" t="s">
         <v>59</v>
       </c>
       <c r="M18" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="N18" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="O18" t="s">
         <v>64</v>
@@ -7035,7 +7029,7 @@
         <v>63</v>
       </c>
       <c r="S18" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="T18"/>
       <c r="U18"/>
@@ -7052,14 +7046,14 @@
         <v>209</v>
       </c>
       <c r="B19" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C19" t="s">
         <v>69</v>
       </c>
       <c r="D19"/>
       <c r="E19" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
       <c r="F19" t="s">
         <v>60</v>
@@ -7074,17 +7068,17 @@
         <v>102</v>
       </c>
       <c r="J19" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K19"/>
       <c r="L19" t="s">
         <v>59</v>
       </c>
       <c r="M19" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="N19" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="O19" t="s">
         <v>64</v>
@@ -7097,7 +7091,7 @@
         <v>63</v>
       </c>
       <c r="S19" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="T19"/>
       <c r="U19"/>
@@ -7114,14 +7108,14 @@
         <v>209</v>
       </c>
       <c r="B20" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C20" t="s">
         <v>69</v>
       </c>
       <c r="D20"/>
       <c r="E20" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
       <c r="F20" t="s">
         <v>60</v>
@@ -7136,17 +7130,17 @@
         <v>102</v>
       </c>
       <c r="J20" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K20"/>
       <c r="L20" t="s">
         <v>59</v>
       </c>
       <c r="M20" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="N20" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="O20" t="s">
         <v>64</v>
@@ -7159,7 +7153,7 @@
         <v>63</v>
       </c>
       <c r="S20" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="T20"/>
       <c r="U20"/>
@@ -7176,14 +7170,14 @@
         <v>209</v>
       </c>
       <c r="B21" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C21" t="s">
         <v>69</v>
       </c>
       <c r="D21"/>
       <c r="E21" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
       <c r="F21" t="s">
         <v>60</v>
@@ -7198,14 +7192,14 @@
         <v>102</v>
       </c>
       <c r="J21" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K21"/>
       <c r="L21" t="s">
         <v>59</v>
       </c>
       <c r="M21" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="N21" t="s">
         <v>212</v>
@@ -7238,14 +7232,14 @@
         <v>209</v>
       </c>
       <c r="B22" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C22" t="s">
         <v>69</v>
       </c>
       <c r="D22"/>
       <c r="E22" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
       <c r="F22" t="s">
         <v>60</v>
@@ -7260,17 +7254,17 @@
         <v>102</v>
       </c>
       <c r="J22" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K22"/>
       <c r="L22" t="s">
         <v>59</v>
       </c>
       <c r="M22" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="N22" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="O22" t="s">
         <v>64</v>
@@ -7283,7 +7277,7 @@
         <v>63</v>
       </c>
       <c r="S22" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="T22"/>
       <c r="U22"/>
@@ -7300,14 +7294,14 @@
         <v>209</v>
       </c>
       <c r="B23" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C23" t="s">
         <v>69</v>
       </c>
       <c r="D23"/>
       <c r="E23" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
       <c r="F23" t="s">
         <v>60</v>
@@ -7329,10 +7323,10 @@
         <v>59</v>
       </c>
       <c r="M23" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="N23" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="O23" t="s">
         <v>64</v>
@@ -7345,7 +7339,7 @@
         <v>63</v>
       </c>
       <c r="S23" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="T23"/>
       <c r="U23"/>
@@ -7362,14 +7356,14 @@
         <v>209</v>
       </c>
       <c r="B24" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C24" t="s">
         <v>69</v>
       </c>
       <c r="D24"/>
       <c r="E24" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
       <c r="F24" t="s">
         <v>60</v>
@@ -7384,17 +7378,17 @@
         <v>102</v>
       </c>
       <c r="J24" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K24"/>
       <c r="L24" t="s">
         <v>59</v>
       </c>
       <c r="M24" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="N24" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="O24" t="s">
         <v>64</v>
@@ -7407,7 +7401,7 @@
         <v>63</v>
       </c>
       <c r="S24" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="T24"/>
       <c r="U24"/>
@@ -7424,14 +7418,14 @@
         <v>209</v>
       </c>
       <c r="B25" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C25" t="s">
         <v>69</v>
       </c>
       <c r="D25"/>
       <c r="E25" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
       <c r="F25" t="s">
         <v>60</v>
@@ -7446,17 +7440,17 @@
         <v>102</v>
       </c>
       <c r="J25" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K25"/>
       <c r="L25" t="s">
         <v>59</v>
       </c>
       <c r="M25" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="N25" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="O25" t="s">
         <v>64</v>
@@ -7469,7 +7463,7 @@
         <v>63</v>
       </c>
       <c r="S25" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="T25"/>
       <c r="U25"/>
@@ -7486,14 +7480,14 @@
         <v>209</v>
       </c>
       <c r="B26" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C26" t="s">
         <v>69</v>
       </c>
       <c r="D26"/>
       <c r="E26" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
       <c r="F26" t="s">
         <v>60</v>
@@ -7515,10 +7509,10 @@
         <v>59</v>
       </c>
       <c r="M26" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="N26" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="O26" t="s">
         <v>64</v>
@@ -7531,7 +7525,7 @@
         <v>63</v>
       </c>
       <c r="S26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="T26"/>
       <c r="U26"/>
@@ -7548,14 +7542,14 @@
         <v>209</v>
       </c>
       <c r="B27" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C27" t="s">
         <v>69</v>
       </c>
       <c r="D27"/>
       <c r="E27" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
       <c r="F27" t="s">
         <v>60</v>
@@ -7577,10 +7571,10 @@
         <v>59</v>
       </c>
       <c r="M27" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="N27" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="O27" t="s">
         <v>64</v>
@@ -7593,7 +7587,7 @@
         <v>63</v>
       </c>
       <c r="S27" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="T27"/>
       <c r="U27"/>
@@ -7610,14 +7604,14 @@
         <v>209</v>
       </c>
       <c r="B28" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C28" t="s">
         <v>69</v>
       </c>
       <c r="D28"/>
       <c r="E28" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
       <c r="F28" t="s">
         <v>60</v>
@@ -7639,10 +7633,10 @@
         <v>59</v>
       </c>
       <c r="M28" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="N28" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="O28" t="s">
         <v>64</v>
@@ -7655,7 +7649,7 @@
         <v>63</v>
       </c>
       <c r="S28" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="T28"/>
       <c r="U28"/>
@@ -7672,39 +7666,39 @@
         <v>209</v>
       </c>
       <c r="B29" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C29" t="s">
         <v>69</v>
       </c>
       <c r="D29"/>
       <c r="E29" t="s">
+        <v>172</v>
+      </c>
+      <c r="F29" t="s">
+        <v>60</v>
+      </c>
+      <c r="G29" t="s">
+        <v>61</v>
+      </c>
+      <c r="H29" t="s">
+        <v>62</v>
+      </c>
+      <c r="I29" t="s">
+        <v>102</v>
+      </c>
+      <c r="J29" t="s">
         <v>230</v>
-      </c>
-      <c r="F29" t="s">
-        <v>60</v>
-      </c>
-      <c r="G29" t="s">
-        <v>61</v>
-      </c>
-      <c r="H29" t="s">
-        <v>62</v>
-      </c>
-      <c r="I29" t="s">
-        <v>102</v>
-      </c>
-      <c r="J29" t="s">
-        <v>231</v>
       </c>
       <c r="K29"/>
       <c r="L29" t="s">
         <v>59</v>
       </c>
       <c r="M29" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="N29" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="O29" t="s">
         <v>64</v>
@@ -7717,7 +7711,7 @@
         <v>63</v>
       </c>
       <c r="S29" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="T29"/>
       <c r="U29"/>
@@ -7734,14 +7728,14 @@
         <v>209</v>
       </c>
       <c r="B30" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C30" t="s">
         <v>69</v>
       </c>
       <c r="D30"/>
       <c r="E30" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
       <c r="F30" t="s">
         <v>60</v>
@@ -7756,17 +7750,17 @@
         <v>102</v>
       </c>
       <c r="J30" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K30"/>
       <c r="L30" t="s">
         <v>59</v>
       </c>
       <c r="M30" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="N30" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="O30" t="s">
         <v>64</v>
@@ -7779,7 +7773,7 @@
         <v>63</v>
       </c>
       <c r="S30" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="T30"/>
       <c r="U30"/>
@@ -7796,14 +7790,14 @@
         <v>209</v>
       </c>
       <c r="B31" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C31" t="s">
         <v>69</v>
       </c>
       <c r="D31"/>
       <c r="E31" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
       <c r="F31" t="s">
         <v>60</v>
@@ -7818,17 +7812,17 @@
         <v>102</v>
       </c>
       <c r="J31" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K31"/>
       <c r="L31" t="s">
         <v>59</v>
       </c>
       <c r="M31" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="N31" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="O31" t="s">
         <v>64</v>
@@ -7841,7 +7835,7 @@
         <v>63</v>
       </c>
       <c r="S31" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="T31"/>
       <c r="U31"/>
@@ -7858,14 +7852,14 @@
         <v>209</v>
       </c>
       <c r="B32" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C32" t="s">
         <v>69</v>
       </c>
       <c r="D32"/>
       <c r="E32" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
       <c r="F32" t="s">
         <v>60</v>
@@ -7880,14 +7874,14 @@
         <v>102</v>
       </c>
       <c r="J32" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K32"/>
       <c r="L32" t="s">
         <v>59</v>
       </c>
       <c r="M32" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="N32" t="s">
         <v>212</v>
@@ -7920,14 +7914,14 @@
         <v>209</v>
       </c>
       <c r="B33" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C33" t="s">
         <v>69</v>
       </c>
       <c r="D33"/>
       <c r="E33" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
       <c r="F33" t="s">
         <v>60</v>
@@ -7942,17 +7936,17 @@
         <v>102</v>
       </c>
       <c r="J33" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K33"/>
       <c r="L33" t="s">
         <v>59</v>
       </c>
       <c r="M33" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="N33" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="O33" t="s">
         <v>64</v>
@@ -7965,7 +7959,7 @@
         <v>63</v>
       </c>
       <c r="S33" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="T33"/>
       <c r="U33"/>
@@ -7982,14 +7976,14 @@
         <v>209</v>
       </c>
       <c r="B34" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C34" t="s">
         <v>69</v>
       </c>
       <c r="D34"/>
       <c r="E34" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
       <c r="F34" t="s">
         <v>60</v>
@@ -8011,10 +8005,10 @@
         <v>59</v>
       </c>
       <c r="M34" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="N34" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="O34" t="s">
         <v>64</v>
@@ -8027,7 +8021,7 @@
         <v>63</v>
       </c>
       <c r="S34" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="T34"/>
       <c r="U34"/>
@@ -8044,14 +8038,14 @@
         <v>209</v>
       </c>
       <c r="B35" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C35" t="s">
         <v>69</v>
       </c>
       <c r="D35"/>
       <c r="E35" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
       <c r="F35" t="s">
         <v>60</v>
@@ -8066,17 +8060,17 @@
         <v>102</v>
       </c>
       <c r="J35" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K35"/>
       <c r="L35" t="s">
         <v>59</v>
       </c>
       <c r="M35" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="N35" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="O35" t="s">
         <v>64</v>
@@ -8089,7 +8083,7 @@
         <v>63</v>
       </c>
       <c r="S35" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="T35"/>
       <c r="U35"/>
@@ -8106,14 +8100,14 @@
         <v>209</v>
       </c>
       <c r="B36" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C36" t="s">
         <v>69</v>
       </c>
       <c r="D36"/>
       <c r="E36" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
       <c r="F36" t="s">
         <v>60</v>
@@ -8128,17 +8122,17 @@
         <v>102</v>
       </c>
       <c r="J36" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K36"/>
       <c r="L36" t="s">
         <v>59</v>
       </c>
       <c r="M36" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="N36" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="O36" t="s">
         <v>64</v>
@@ -8151,7 +8145,7 @@
         <v>63</v>
       </c>
       <c r="S36" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="T36"/>
       <c r="U36"/>
@@ -8168,14 +8162,14 @@
         <v>209</v>
       </c>
       <c r="B37" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C37" t="s">
         <v>69</v>
       </c>
       <c r="D37"/>
       <c r="E37" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
       <c r="F37" t="s">
         <v>60</v>
@@ -8197,10 +8191,10 @@
         <v>59</v>
       </c>
       <c r="M37" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="N37" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="O37" t="s">
         <v>64</v>
@@ -8213,7 +8207,7 @@
         <v>63</v>
       </c>
       <c r="S37" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="T37"/>
       <c r="U37"/>
@@ -8230,14 +8224,14 @@
         <v>209</v>
       </c>
       <c r="B38" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C38" t="s">
         <v>69</v>
       </c>
       <c r="D38"/>
       <c r="E38" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
       <c r="F38" t="s">
         <v>60</v>
@@ -8259,10 +8253,10 @@
         <v>59</v>
       </c>
       <c r="M38" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="N38" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="O38" t="s">
         <v>64</v>
@@ -8275,7 +8269,7 @@
         <v>63</v>
       </c>
       <c r="S38" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="T38"/>
       <c r="U38"/>
@@ -8292,14 +8286,14 @@
         <v>209</v>
       </c>
       <c r="B39" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C39" t="s">
         <v>69</v>
       </c>
       <c r="D39"/>
       <c r="E39" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
       <c r="F39" t="s">
         <v>60</v>
@@ -8321,10 +8315,10 @@
         <v>59</v>
       </c>
       <c r="M39" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="N39" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="O39" t="s">
         <v>64</v>
@@ -8337,7 +8331,7 @@
         <v>63</v>
       </c>
       <c r="S39" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="T39"/>
       <c r="U39"/>
@@ -8354,39 +8348,39 @@
         <v>209</v>
       </c>
       <c r="B40" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C40" t="s">
         <v>69</v>
       </c>
       <c r="D40"/>
       <c r="E40" t="s">
+        <v>172</v>
+      </c>
+      <c r="F40" t="s">
+        <v>60</v>
+      </c>
+      <c r="G40" t="s">
+        <v>61</v>
+      </c>
+      <c r="H40" t="s">
+        <v>62</v>
+      </c>
+      <c r="I40" t="s">
+        <v>102</v>
+      </c>
+      <c r="J40" t="s">
         <v>230</v>
-      </c>
-      <c r="F40" t="s">
-        <v>60</v>
-      </c>
-      <c r="G40" t="s">
-        <v>61</v>
-      </c>
-      <c r="H40" t="s">
-        <v>62</v>
-      </c>
-      <c r="I40" t="s">
-        <v>102</v>
-      </c>
-      <c r="J40" t="s">
-        <v>231</v>
       </c>
       <c r="K40"/>
       <c r="L40" t="s">
         <v>59</v>
       </c>
       <c r="M40" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="N40" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="O40" t="s">
         <v>64</v>
@@ -8399,7 +8393,7 @@
         <v>63</v>
       </c>
       <c r="S40" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="T40"/>
       <c r="U40"/>
@@ -8416,14 +8410,14 @@
         <v>209</v>
       </c>
       <c r="B41" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C41" t="s">
         <v>69</v>
       </c>
       <c r="D41"/>
       <c r="E41" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
       <c r="F41" t="s">
         <v>60</v>
@@ -8438,17 +8432,17 @@
         <v>102</v>
       </c>
       <c r="J41" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K41"/>
       <c r="L41" t="s">
         <v>59</v>
       </c>
       <c r="M41" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="N41" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="O41" t="s">
         <v>64</v>
@@ -8461,7 +8455,7 @@
         <v>63</v>
       </c>
       <c r="S41" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="T41"/>
       <c r="U41"/>
@@ -8478,14 +8472,14 @@
         <v>209</v>
       </c>
       <c r="B42" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C42" t="s">
         <v>69</v>
       </c>
       <c r="D42"/>
       <c r="E42" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
       <c r="F42" t="s">
         <v>60</v>
@@ -8500,17 +8494,17 @@
         <v>102</v>
       </c>
       <c r="J42" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K42"/>
       <c r="L42" t="s">
         <v>59</v>
       </c>
       <c r="M42" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="N42" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="O42" t="s">
         <v>64</v>
@@ -8523,7 +8517,7 @@
         <v>63</v>
       </c>
       <c r="S42" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="T42"/>
       <c r="U42"/>
@@ -8540,14 +8534,14 @@
         <v>209</v>
       </c>
       <c r="B43" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C43" t="s">
         <v>69</v>
       </c>
       <c r="D43"/>
       <c r="E43" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
       <c r="F43" t="s">
         <v>60</v>
@@ -8562,14 +8556,14 @@
         <v>102</v>
       </c>
       <c r="J43" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K43"/>
       <c r="L43" t="s">
         <v>59</v>
       </c>
       <c r="M43" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="N43" t="s">
         <v>212</v>
@@ -8602,14 +8596,14 @@
         <v>209</v>
       </c>
       <c r="B44" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C44" t="s">
         <v>69</v>
       </c>
       <c r="D44"/>
       <c r="E44" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
       <c r="F44" t="s">
         <v>60</v>
@@ -8624,17 +8618,17 @@
         <v>102</v>
       </c>
       <c r="J44" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K44"/>
       <c r="L44" t="s">
         <v>59</v>
       </c>
       <c r="M44" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="N44" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="O44" t="s">
         <v>64</v>
@@ -8647,7 +8641,7 @@
         <v>63</v>
       </c>
       <c r="S44" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="T44"/>
       <c r="U44"/>
@@ -8664,14 +8658,14 @@
         <v>209</v>
       </c>
       <c r="B45" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C45" t="s">
         <v>69</v>
       </c>
       <c r="D45"/>
       <c r="E45" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
       <c r="F45" t="s">
         <v>60</v>
@@ -8693,10 +8687,10 @@
         <v>59</v>
       </c>
       <c r="M45" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="N45" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="O45" t="s">
         <v>64</v>
@@ -8709,7 +8703,7 @@
         <v>63</v>
       </c>
       <c r="S45" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="T45"/>
       <c r="U45"/>
@@ -8726,14 +8720,14 @@
         <v>209</v>
       </c>
       <c r="B46" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C46" t="s">
         <v>69</v>
       </c>
       <c r="D46"/>
       <c r="E46" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
       <c r="F46" t="s">
         <v>60</v>
@@ -8748,17 +8742,17 @@
         <v>102</v>
       </c>
       <c r="J46" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K46"/>
       <c r="L46" t="s">
         <v>59</v>
       </c>
       <c r="M46" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="N46" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="O46" t="s">
         <v>64</v>
@@ -8771,7 +8765,7 @@
         <v>63</v>
       </c>
       <c r="S46" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="T46"/>
       <c r="U46"/>
@@ -8788,14 +8782,14 @@
         <v>209</v>
       </c>
       <c r="B47" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C47" t="s">
         <v>69</v>
       </c>
       <c r="D47"/>
       <c r="E47" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
       <c r="F47" t="s">
         <v>60</v>
@@ -8810,17 +8804,17 @@
         <v>102</v>
       </c>
       <c r="J47" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K47"/>
       <c r="L47" t="s">
         <v>59</v>
       </c>
       <c r="M47" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="N47" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="O47" t="s">
         <v>64</v>
@@ -8833,7 +8827,7 @@
         <v>63</v>
       </c>
       <c r="S47" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="T47"/>
       <c r="U47"/>
@@ -8850,14 +8844,14 @@
         <v>209</v>
       </c>
       <c r="B48" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C48" t="s">
         <v>69</v>
       </c>
       <c r="D48"/>
       <c r="E48" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
       <c r="F48" t="s">
         <v>60</v>
@@ -8879,10 +8873,10 @@
         <v>59</v>
       </c>
       <c r="M48" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="N48" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="O48" t="s">
         <v>64</v>
@@ -8895,7 +8889,7 @@
         <v>63</v>
       </c>
       <c r="S48" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="T48"/>
       <c r="U48"/>
@@ -8912,14 +8906,14 @@
         <v>209</v>
       </c>
       <c r="B49" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C49" t="s">
         <v>69</v>
       </c>
       <c r="D49"/>
       <c r="E49" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
       <c r="F49" t="s">
         <v>60</v>
@@ -8941,10 +8935,10 @@
         <v>59</v>
       </c>
       <c r="M49" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="N49" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="O49" t="s">
         <v>64</v>
@@ -8957,7 +8951,7 @@
         <v>63</v>
       </c>
       <c r="S49" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="T49"/>
       <c r="U49"/>
@@ -8974,14 +8968,14 @@
         <v>209</v>
       </c>
       <c r="B50" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C50" t="s">
         <v>69</v>
       </c>
       <c r="D50"/>
       <c r="E50" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
       <c r="F50" t="s">
         <v>60</v>
@@ -9003,10 +8997,10 @@
         <v>59</v>
       </c>
       <c r="M50" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="N50" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="O50" t="s">
         <v>64</v>
@@ -9019,7 +9013,7 @@
         <v>63</v>
       </c>
       <c r="S50" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="T50"/>
       <c r="U50"/>
@@ -9036,39 +9030,39 @@
         <v>209</v>
       </c>
       <c r="B51" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C51" t="s">
         <v>69</v>
       </c>
       <c r="D51"/>
       <c r="E51" t="s">
+        <v>172</v>
+      </c>
+      <c r="F51" t="s">
+        <v>60</v>
+      </c>
+      <c r="G51" t="s">
+        <v>61</v>
+      </c>
+      <c r="H51" t="s">
+        <v>62</v>
+      </c>
+      <c r="I51" t="s">
+        <v>102</v>
+      </c>
+      <c r="J51" t="s">
         <v>230</v>
-      </c>
-      <c r="F51" t="s">
-        <v>60</v>
-      </c>
-      <c r="G51" t="s">
-        <v>61</v>
-      </c>
-      <c r="H51" t="s">
-        <v>62</v>
-      </c>
-      <c r="I51" t="s">
-        <v>102</v>
-      </c>
-      <c r="J51" t="s">
-        <v>231</v>
       </c>
       <c r="K51"/>
       <c r="L51" t="s">
         <v>59</v>
       </c>
       <c r="M51" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="N51" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="O51" t="s">
         <v>64</v>
@@ -9081,7 +9075,7 @@
         <v>63</v>
       </c>
       <c r="S51" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="T51"/>
       <c r="U51"/>
@@ -9098,14 +9092,14 @@
         <v>209</v>
       </c>
       <c r="B52" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C52" t="s">
         <v>69</v>
       </c>
       <c r="D52"/>
       <c r="E52" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
       <c r="F52" t="s">
         <v>60</v>
@@ -9120,17 +9114,17 @@
         <v>102</v>
       </c>
       <c r="J52" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K52"/>
       <c r="L52" t="s">
         <v>59</v>
       </c>
       <c r="M52" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="N52" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="O52" t="s">
         <v>64</v>
@@ -9143,7 +9137,7 @@
         <v>63</v>
       </c>
       <c r="S52" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="T52"/>
       <c r="U52"/>
@@ -9160,14 +9154,14 @@
         <v>209</v>
       </c>
       <c r="B53" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C53" t="s">
         <v>69</v>
       </c>
       <c r="D53"/>
       <c r="E53" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
       <c r="F53" t="s">
         <v>60</v>
@@ -9182,17 +9176,17 @@
         <v>102</v>
       </c>
       <c r="J53" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K53"/>
       <c r="L53" t="s">
         <v>59</v>
       </c>
       <c r="M53" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="N53" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="O53" t="s">
         <v>64</v>
@@ -9205,7 +9199,7 @@
         <v>63</v>
       </c>
       <c r="S53" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="T53"/>
       <c r="U53"/>
@@ -9222,14 +9216,14 @@
         <v>209</v>
       </c>
       <c r="B54" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C54" t="s">
         <v>69</v>
       </c>
       <c r="D54"/>
       <c r="E54" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
       <c r="F54" t="s">
         <v>60</v>
@@ -9244,14 +9238,14 @@
         <v>102</v>
       </c>
       <c r="J54" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K54"/>
       <c r="L54" t="s">
         <v>59</v>
       </c>
       <c r="M54" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="N54" t="s">
         <v>212</v>
@@ -9284,14 +9278,14 @@
         <v>209</v>
       </c>
       <c r="B55" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C55" t="s">
         <v>69</v>
       </c>
       <c r="D55"/>
       <c r="E55" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
       <c r="F55" t="s">
         <v>60</v>
@@ -9306,17 +9300,17 @@
         <v>102</v>
       </c>
       <c r="J55" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K55"/>
       <c r="L55" t="s">
         <v>59</v>
       </c>
       <c r="M55" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="N55" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="O55" t="s">
         <v>64</v>
@@ -9329,7 +9323,7 @@
         <v>63</v>
       </c>
       <c r="S55" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="T55"/>
       <c r="U55"/>
@@ -9346,14 +9340,14 @@
         <v>209</v>
       </c>
       <c r="B56" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C56" t="s">
         <v>69</v>
       </c>
       <c r="D56"/>
       <c r="E56" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
       <c r="F56" t="s">
         <v>60</v>
@@ -9375,10 +9369,10 @@
         <v>59</v>
       </c>
       <c r="M56" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="N56" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="O56" t="s">
         <v>64</v>
@@ -9391,7 +9385,7 @@
         <v>63</v>
       </c>
       <c r="S56" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="T56"/>
       <c r="U56"/>
@@ -9408,14 +9402,14 @@
         <v>209</v>
       </c>
       <c r="B57" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C57" t="s">
         <v>69</v>
       </c>
       <c r="D57"/>
       <c r="E57" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
       <c r="F57" t="s">
         <v>60</v>
@@ -9430,17 +9424,17 @@
         <v>102</v>
       </c>
       <c r="J57" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K57"/>
       <c r="L57" t="s">
         <v>59</v>
       </c>
       <c r="M57" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="N57" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="O57" t="s">
         <v>64</v>
@@ -9453,7 +9447,7 @@
         <v>63</v>
       </c>
       <c r="S57" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="T57"/>
       <c r="U57"/>
@@ -9470,14 +9464,14 @@
         <v>209</v>
       </c>
       <c r="B58" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C58" t="s">
         <v>69</v>
       </c>
       <c r="D58"/>
       <c r="E58" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
       <c r="F58" t="s">
         <v>60</v>
@@ -9492,17 +9486,17 @@
         <v>102</v>
       </c>
       <c r="J58" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K58"/>
       <c r="L58" t="s">
         <v>59</v>
       </c>
       <c r="M58" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="N58" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="O58" t="s">
         <v>64</v>
@@ -9515,7 +9509,7 @@
         <v>63</v>
       </c>
       <c r="S58" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="T58"/>
       <c r="U58"/>
@@ -9532,14 +9526,14 @@
         <v>209</v>
       </c>
       <c r="B59" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C59" t="s">
         <v>69</v>
       </c>
       <c r="D59"/>
       <c r="E59" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
       <c r="F59" t="s">
         <v>60</v>
@@ -9561,10 +9555,10 @@
         <v>59</v>
       </c>
       <c r="M59" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="N59" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="O59" t="s">
         <v>64</v>
@@ -9577,7 +9571,7 @@
         <v>63</v>
       </c>
       <c r="S59" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="T59"/>
       <c r="U59"/>
@@ -9594,14 +9588,14 @@
         <v>209</v>
       </c>
       <c r="B60" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C60" t="s">
         <v>69</v>
       </c>
       <c r="D60"/>
       <c r="E60" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
       <c r="F60" t="s">
         <v>60</v>
@@ -9623,10 +9617,10 @@
         <v>59</v>
       </c>
       <c r="M60" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="N60" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="O60" t="s">
         <v>64</v>
@@ -9639,7 +9633,7 @@
         <v>63</v>
       </c>
       <c r="S60" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="T60"/>
       <c r="U60"/>
@@ -9656,14 +9650,14 @@
         <v>209</v>
       </c>
       <c r="B61" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C61" t="s">
         <v>69</v>
       </c>
       <c r="D61"/>
       <c r="E61" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
       <c r="F61" t="s">
         <v>60</v>
@@ -9685,10 +9679,10 @@
         <v>59</v>
       </c>
       <c r="M61" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="N61" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="O61" t="s">
         <v>64</v>
@@ -9701,7 +9695,7 @@
         <v>63</v>
       </c>
       <c r="S61" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="T61"/>
       <c r="U61"/>
@@ -9718,39 +9712,39 @@
         <v>209</v>
       </c>
       <c r="B62" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C62" t="s">
         <v>69</v>
       </c>
       <c r="D62"/>
       <c r="E62" t="s">
+        <v>172</v>
+      </c>
+      <c r="F62" t="s">
+        <v>60</v>
+      </c>
+      <c r="G62" t="s">
+        <v>61</v>
+      </c>
+      <c r="H62" t="s">
+        <v>62</v>
+      </c>
+      <c r="I62" t="s">
+        <v>102</v>
+      </c>
+      <c r="J62" t="s">
         <v>230</v>
-      </c>
-      <c r="F62" t="s">
-        <v>60</v>
-      </c>
-      <c r="G62" t="s">
-        <v>61</v>
-      </c>
-      <c r="H62" t="s">
-        <v>62</v>
-      </c>
-      <c r="I62" t="s">
-        <v>102</v>
-      </c>
-      <c r="J62" t="s">
-        <v>231</v>
       </c>
       <c r="K62"/>
       <c r="L62" t="s">
         <v>59</v>
       </c>
       <c r="M62" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="N62" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="O62" t="s">
         <v>64</v>
@@ -9763,7 +9757,7 @@
         <v>63</v>
       </c>
       <c r="S62" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="T62"/>
       <c r="U62"/>
@@ -9780,14 +9774,14 @@
         <v>209</v>
       </c>
       <c r="B63" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C63" t="s">
         <v>69</v>
       </c>
       <c r="D63"/>
       <c r="E63" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
       <c r="F63" t="s">
         <v>60</v>
@@ -9802,17 +9796,17 @@
         <v>102</v>
       </c>
       <c r="J63" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K63"/>
       <c r="L63" t="s">
         <v>59</v>
       </c>
       <c r="M63" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="N63" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="O63" t="s">
         <v>64</v>
@@ -9825,7 +9819,7 @@
         <v>63</v>
       </c>
       <c r="S63" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="T63"/>
       <c r="U63"/>
@@ -9842,14 +9836,14 @@
         <v>209</v>
       </c>
       <c r="B64" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C64" t="s">
         <v>69</v>
       </c>
       <c r="D64"/>
       <c r="E64" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
       <c r="F64" t="s">
         <v>60</v>
@@ -9864,17 +9858,17 @@
         <v>102</v>
       </c>
       <c r="J64" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K64"/>
       <c r="L64" t="s">
         <v>59</v>
       </c>
       <c r="M64" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="N64" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="O64" t="s">
         <v>64</v>
@@ -9887,7 +9881,7 @@
         <v>63</v>
       </c>
       <c r="S64" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="T64"/>
       <c r="U64"/>
@@ -9904,14 +9898,14 @@
         <v>209</v>
       </c>
       <c r="B65" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C65" t="s">
         <v>69</v>
       </c>
       <c r="D65"/>
       <c r="E65" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
       <c r="F65" t="s">
         <v>60</v>
@@ -9926,14 +9920,14 @@
         <v>102</v>
       </c>
       <c r="J65" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K65"/>
       <c r="L65" t="s">
         <v>59</v>
       </c>
       <c r="M65" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="N65" t="s">
         <v>212</v>
@@ -9966,14 +9960,14 @@
         <v>209</v>
       </c>
       <c r="B66" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C66" t="s">
         <v>69</v>
       </c>
       <c r="D66"/>
       <c r="E66" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
       <c r="F66" t="s">
         <v>60</v>
@@ -9988,17 +9982,17 @@
         <v>102</v>
       </c>
       <c r="J66" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K66"/>
       <c r="L66" t="s">
         <v>59</v>
       </c>
       <c r="M66" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="N66" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="O66" t="s">
         <v>64</v>
@@ -10011,7 +10005,7 @@
         <v>63</v>
       </c>
       <c r="S66" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="T66"/>
       <c r="U66"/>
@@ -10028,14 +10022,14 @@
         <v>209</v>
       </c>
       <c r="B67" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C67" t="s">
         <v>69</v>
       </c>
       <c r="D67"/>
       <c r="E67" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
       <c r="F67" t="s">
         <v>60</v>
@@ -10057,10 +10051,10 @@
         <v>59</v>
       </c>
       <c r="M67" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="N67" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="O67" t="s">
         <v>64</v>
@@ -10073,7 +10067,7 @@
         <v>63</v>
       </c>
       <c r="S67" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="T67"/>
       <c r="U67"/>
@@ -10090,14 +10084,14 @@
         <v>209</v>
       </c>
       <c r="B68" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C68" t="s">
         <v>69</v>
       </c>
       <c r="D68"/>
       <c r="E68" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
       <c r="F68" t="s">
         <v>60</v>
@@ -10112,17 +10106,17 @@
         <v>102</v>
       </c>
       <c r="J68" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K68"/>
       <c r="L68" t="s">
         <v>59</v>
       </c>
       <c r="M68" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="N68" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="O68" t="s">
         <v>64</v>
@@ -10135,7 +10129,7 @@
         <v>63</v>
       </c>
       <c r="S68" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="T68"/>
       <c r="U68"/>
@@ -10152,14 +10146,14 @@
         <v>209</v>
       </c>
       <c r="B69" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C69" t="s">
         <v>69</v>
       </c>
       <c r="D69"/>
       <c r="E69" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
       <c r="F69" t="s">
         <v>60</v>
@@ -10174,17 +10168,17 @@
         <v>102</v>
       </c>
       <c r="J69" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K69"/>
       <c r="L69" t="s">
         <v>59</v>
       </c>
       <c r="M69" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="N69" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="O69" t="s">
         <v>64</v>
@@ -10197,7 +10191,7 @@
         <v>63</v>
       </c>
       <c r="S69" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="T69"/>
       <c r="U69"/>
@@ -10214,14 +10208,14 @@
         <v>209</v>
       </c>
       <c r="B70" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C70" t="s">
         <v>69</v>
       </c>
       <c r="D70"/>
       <c r="E70" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
       <c r="F70" t="s">
         <v>60</v>
@@ -10243,10 +10237,10 @@
         <v>59</v>
       </c>
       <c r="M70" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="N70" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="O70" t="s">
         <v>64</v>
@@ -10259,7 +10253,7 @@
         <v>63</v>
       </c>
       <c r="S70" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="T70"/>
       <c r="U70"/>
@@ -10276,14 +10270,14 @@
         <v>209</v>
       </c>
       <c r="B71" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C71" t="s">
         <v>69</v>
       </c>
       <c r="D71"/>
       <c r="E71" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F71" t="s">
         <v>60</v>
@@ -10305,10 +10299,10 @@
         <v>59</v>
       </c>
       <c r="M71" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="N71" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="O71" t="s">
         <v>64</v>
@@ -10321,7 +10315,7 @@
         <v>63</v>
       </c>
       <c r="S71" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="T71"/>
       <c r="U71"/>
@@ -10338,14 +10332,14 @@
         <v>209</v>
       </c>
       <c r="B72" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C72" t="s">
         <v>69</v>
       </c>
       <c r="D72"/>
       <c r="E72" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F72" t="s">
         <v>60</v>
@@ -10367,10 +10361,10 @@
         <v>59</v>
       </c>
       <c r="M72" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="N72" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="O72" t="s">
         <v>64</v>
@@ -10383,7 +10377,7 @@
         <v>63</v>
       </c>
       <c r="S72" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="T72"/>
       <c r="U72"/>
@@ -10400,14 +10394,14 @@
         <v>209</v>
       </c>
       <c r="B73" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C73" t="s">
         <v>69</v>
       </c>
       <c r="D73"/>
       <c r="E73" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F73" t="s">
         <v>60</v>
@@ -10422,17 +10416,17 @@
         <v>102</v>
       </c>
       <c r="J73" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K73"/>
       <c r="L73" t="s">
         <v>59</v>
       </c>
       <c r="M73" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="N73" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="O73" t="s">
         <v>64</v>
@@ -10445,7 +10439,7 @@
         <v>63</v>
       </c>
       <c r="S73" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="T73"/>
       <c r="U73"/>
@@ -10462,14 +10456,14 @@
         <v>209</v>
       </c>
       <c r="B74" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C74" t="s">
         <v>69</v>
       </c>
       <c r="D74"/>
       <c r="E74" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F74" t="s">
         <v>60</v>
@@ -10484,17 +10478,17 @@
         <v>102</v>
       </c>
       <c r="J74" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K74"/>
       <c r="L74" t="s">
         <v>59</v>
       </c>
       <c r="M74" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="N74" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="O74" t="s">
         <v>64</v>
@@ -10507,7 +10501,7 @@
         <v>63</v>
       </c>
       <c r="S74" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="T74"/>
       <c r="U74"/>
@@ -10524,14 +10518,14 @@
         <v>209</v>
       </c>
       <c r="B75" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C75" t="s">
         <v>69</v>
       </c>
       <c r="D75"/>
       <c r="E75" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F75" t="s">
         <v>60</v>
@@ -10546,17 +10540,17 @@
         <v>102</v>
       </c>
       <c r="J75" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K75"/>
       <c r="L75" t="s">
         <v>59</v>
       </c>
       <c r="M75" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="N75" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="O75" t="s">
         <v>64</v>
@@ -10569,7 +10563,7 @@
         <v>63</v>
       </c>
       <c r="S75" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="T75"/>
       <c r="U75"/>
@@ -10586,14 +10580,14 @@
         <v>209</v>
       </c>
       <c r="B76" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C76" t="s">
         <v>69</v>
       </c>
       <c r="D76"/>
       <c r="E76" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F76" t="s">
         <v>60</v>
@@ -10615,10 +10609,10 @@
         <v>59</v>
       </c>
       <c r="M76" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="N76" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="O76" t="s">
         <v>64</v>
@@ -10631,7 +10625,7 @@
         <v>63</v>
       </c>
       <c r="S76" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="T76"/>
       <c r="U76"/>
@@ -10648,14 +10642,14 @@
         <v>209</v>
       </c>
       <c r="B77" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C77" t="s">
         <v>69</v>
       </c>
       <c r="D77"/>
       <c r="E77" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F77" t="s">
         <v>60</v>
@@ -10677,10 +10671,10 @@
         <v>59</v>
       </c>
       <c r="M77" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="N77" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="O77" t="s">
         <v>64</v>
@@ -10693,7 +10687,7 @@
         <v>63</v>
       </c>
       <c r="S77" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="T77"/>
       <c r="U77"/>
@@ -10710,14 +10704,14 @@
         <v>209</v>
       </c>
       <c r="B78" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C78" t="s">
         <v>69</v>
       </c>
       <c r="D78"/>
       <c r="E78" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F78" t="s">
         <v>60</v>
@@ -10732,17 +10726,17 @@
         <v>102</v>
       </c>
       <c r="J78" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K78"/>
       <c r="L78" t="s">
         <v>59</v>
       </c>
       <c r="M78" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="N78" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="O78" t="s">
         <v>64</v>
@@ -10755,7 +10749,7 @@
         <v>63</v>
       </c>
       <c r="S78" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="T78"/>
       <c r="U78"/>
@@ -10772,14 +10766,14 @@
         <v>209</v>
       </c>
       <c r="B79" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C79" t="s">
         <v>69</v>
       </c>
       <c r="D79"/>
       <c r="E79" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F79" t="s">
         <v>60</v>
@@ -10794,17 +10788,17 @@
         <v>102</v>
       </c>
       <c r="J79" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K79"/>
       <c r="L79" t="s">
         <v>59</v>
       </c>
       <c r="M79" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="N79" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="O79" t="s">
         <v>64</v>
@@ -10817,7 +10811,7 @@
         <v>63</v>
       </c>
       <c r="S79" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="T79"/>
       <c r="U79"/>
@@ -10834,14 +10828,14 @@
         <v>209</v>
       </c>
       <c r="B80" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C80" t="s">
         <v>69</v>
       </c>
       <c r="D80"/>
       <c r="E80" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F80" t="s">
         <v>60</v>
@@ -10863,10 +10857,10 @@
         <v>59</v>
       </c>
       <c r="M80" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="N80" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="O80" t="s">
         <v>64</v>
@@ -10879,7 +10873,7 @@
         <v>63</v>
       </c>
       <c r="S80" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="T80"/>
       <c r="U80"/>
@@ -10896,14 +10890,14 @@
         <v>209</v>
       </c>
       <c r="B81" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C81" t="s">
         <v>69</v>
       </c>
       <c r="D81"/>
       <c r="E81" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F81" t="s">
         <v>60</v>
@@ -10925,10 +10919,10 @@
         <v>59</v>
       </c>
       <c r="M81" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="N81" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="O81" t="s">
         <v>64</v>
@@ -10941,7 +10935,7 @@
         <v>63</v>
       </c>
       <c r="S81" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="T81"/>
       <c r="U81"/>
@@ -10958,14 +10952,14 @@
         <v>209</v>
       </c>
       <c r="B82" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C82" t="s">
         <v>69</v>
       </c>
       <c r="D82"/>
       <c r="E82" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F82" t="s">
         <v>60</v>
@@ -10987,10 +10981,10 @@
         <v>59</v>
       </c>
       <c r="M82" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="N82" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="O82" t="s">
         <v>64</v>
@@ -11003,7 +10997,7 @@
         <v>63</v>
       </c>
       <c r="S82" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="T82"/>
       <c r="U82"/>
@@ -11020,14 +11014,14 @@
         <v>209</v>
       </c>
       <c r="B83" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C83" t="s">
         <v>69</v>
       </c>
       <c r="D83"/>
       <c r="E83" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F83" t="s">
         <v>60</v>
@@ -11042,17 +11036,17 @@
         <v>102</v>
       </c>
       <c r="J83" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K83"/>
       <c r="L83" t="s">
         <v>59</v>
       </c>
       <c r="M83" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="N83" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="O83" t="s">
         <v>64</v>
@@ -11065,7 +11059,7 @@
         <v>63</v>
       </c>
       <c r="S83" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="T83"/>
       <c r="U83"/>
@@ -11082,14 +11076,14 @@
         <v>209</v>
       </c>
       <c r="B84" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C84" t="s">
         <v>69</v>
       </c>
       <c r="D84"/>
       <c r="E84" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F84" t="s">
         <v>60</v>
@@ -11104,17 +11098,17 @@
         <v>102</v>
       </c>
       <c r="J84" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K84"/>
       <c r="L84" t="s">
         <v>59</v>
       </c>
       <c r="M84" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="N84" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="O84" t="s">
         <v>64</v>
@@ -11127,7 +11121,7 @@
         <v>63</v>
       </c>
       <c r="S84" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="T84"/>
       <c r="U84"/>
@@ -11144,14 +11138,14 @@
         <v>209</v>
       </c>
       <c r="B85" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C85" t="s">
         <v>69</v>
       </c>
       <c r="D85"/>
       <c r="E85" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F85" t="s">
         <v>60</v>
@@ -11166,17 +11160,17 @@
         <v>102</v>
       </c>
       <c r="J85" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K85"/>
       <c r="L85" t="s">
         <v>59</v>
       </c>
       <c r="M85" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="N85" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="O85" t="s">
         <v>64</v>
@@ -11189,7 +11183,7 @@
         <v>63</v>
       </c>
       <c r="S85" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="T85"/>
       <c r="U85"/>
@@ -11206,14 +11200,14 @@
         <v>209</v>
       </c>
       <c r="B86" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C86" t="s">
         <v>69</v>
       </c>
       <c r="D86"/>
       <c r="E86" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F86" t="s">
         <v>60</v>
@@ -11235,10 +11229,10 @@
         <v>59</v>
       </c>
       <c r="M86" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="N86" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="O86" t="s">
         <v>64</v>
@@ -11251,7 +11245,7 @@
         <v>63</v>
       </c>
       <c r="S86" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="T86"/>
       <c r="U86"/>
@@ -11268,14 +11262,14 @@
         <v>209</v>
       </c>
       <c r="B87" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C87" t="s">
         <v>69</v>
       </c>
       <c r="D87"/>
       <c r="E87" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F87" t="s">
         <v>60</v>
@@ -11297,10 +11291,10 @@
         <v>59</v>
       </c>
       <c r="M87" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="N87" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="O87" t="s">
         <v>64</v>
@@ -11313,7 +11307,7 @@
         <v>63</v>
       </c>
       <c r="S87" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="T87"/>
       <c r="U87"/>
@@ -11330,14 +11324,14 @@
         <v>209</v>
       </c>
       <c r="B88" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C88" t="s">
         <v>69</v>
       </c>
       <c r="D88"/>
       <c r="E88" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F88" t="s">
         <v>60</v>
@@ -11352,17 +11346,17 @@
         <v>102</v>
       </c>
       <c r="J88" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K88"/>
       <c r="L88" t="s">
         <v>59</v>
       </c>
       <c r="M88" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="N88" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="O88" t="s">
         <v>64</v>
@@ -11375,7 +11369,7 @@
         <v>63</v>
       </c>
       <c r="S88" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="T88"/>
       <c r="U88"/>
@@ -11392,14 +11386,14 @@
         <v>209</v>
       </c>
       <c r="B89" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C89" t="s">
         <v>69</v>
       </c>
       <c r="D89"/>
       <c r="E89" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F89" t="s">
         <v>60</v>
@@ -11414,17 +11408,17 @@
         <v>102</v>
       </c>
       <c r="J89" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K89"/>
       <c r="L89" t="s">
         <v>59</v>
       </c>
       <c r="M89" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="N89" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="O89" t="s">
         <v>64</v>
@@ -11437,7 +11431,7 @@
         <v>63</v>
       </c>
       <c r="S89" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="T89"/>
       <c r="U89"/>
@@ -11454,14 +11448,14 @@
         <v>209</v>
       </c>
       <c r="B90" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C90" t="s">
         <v>69</v>
       </c>
       <c r="D90"/>
       <c r="E90" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F90" t="s">
         <v>60</v>
@@ -11483,10 +11477,10 @@
         <v>59</v>
       </c>
       <c r="M90" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="N90" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="O90" t="s">
         <v>64</v>
@@ -11499,7 +11493,7 @@
         <v>63</v>
       </c>
       <c r="S90" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="T90"/>
       <c r="U90"/>
@@ -11516,14 +11510,14 @@
         <v>209</v>
       </c>
       <c r="B91" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C91" t="s">
         <v>69</v>
       </c>
       <c r="D91"/>
       <c r="E91" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F91" t="s">
         <v>60</v>
@@ -11545,10 +11539,10 @@
         <v>59</v>
       </c>
       <c r="M91" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="N91" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="O91" t="s">
         <v>64</v>
@@ -11561,7 +11555,7 @@
         <v>63</v>
       </c>
       <c r="S91" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="T91"/>
       <c r="U91"/>
@@ -11578,14 +11572,14 @@
         <v>209</v>
       </c>
       <c r="B92" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C92" t="s">
         <v>69</v>
       </c>
       <c r="D92"/>
       <c r="E92" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F92" t="s">
         <v>60</v>
@@ -11607,10 +11601,10 @@
         <v>59</v>
       </c>
       <c r="M92" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="N92" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="O92" t="s">
         <v>64</v>
@@ -11623,7 +11617,7 @@
         <v>63</v>
       </c>
       <c r="S92" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="T92"/>
       <c r="U92"/>
@@ -11640,14 +11634,14 @@
         <v>209</v>
       </c>
       <c r="B93" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C93" t="s">
         <v>69</v>
       </c>
       <c r="D93"/>
       <c r="E93" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F93" t="s">
         <v>60</v>
@@ -11662,17 +11656,17 @@
         <v>102</v>
       </c>
       <c r="J93" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K93"/>
       <c r="L93" t="s">
         <v>59</v>
       </c>
       <c r="M93" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="N93" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="O93" t="s">
         <v>64</v>
@@ -11685,7 +11679,7 @@
         <v>63</v>
       </c>
       <c r="S93" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="T93"/>
       <c r="U93"/>
@@ -11702,14 +11696,14 @@
         <v>209</v>
       </c>
       <c r="B94" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C94" t="s">
         <v>69</v>
       </c>
       <c r="D94"/>
       <c r="E94" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F94" t="s">
         <v>60</v>
@@ -11724,17 +11718,17 @@
         <v>102</v>
       </c>
       <c r="J94" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K94"/>
       <c r="L94" t="s">
         <v>59</v>
       </c>
       <c r="M94" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="N94" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="O94" t="s">
         <v>64</v>
@@ -11747,7 +11741,7 @@
         <v>63</v>
       </c>
       <c r="S94" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="T94"/>
       <c r="U94"/>
@@ -11764,14 +11758,14 @@
         <v>209</v>
       </c>
       <c r="B95" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C95" t="s">
         <v>69</v>
       </c>
       <c r="D95"/>
       <c r="E95" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F95" t="s">
         <v>60</v>
@@ -11786,17 +11780,17 @@
         <v>102</v>
       </c>
       <c r="J95" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K95"/>
       <c r="L95" t="s">
         <v>59</v>
       </c>
       <c r="M95" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="N95" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="O95" t="s">
         <v>64</v>
@@ -11809,7 +11803,7 @@
         <v>63</v>
       </c>
       <c r="S95" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="T95"/>
       <c r="U95"/>
@@ -11826,14 +11820,14 @@
         <v>209</v>
       </c>
       <c r="B96" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C96" t="s">
         <v>69</v>
       </c>
       <c r="D96"/>
       <c r="E96" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F96" t="s">
         <v>60</v>
@@ -11855,10 +11849,10 @@
         <v>59</v>
       </c>
       <c r="M96" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="N96" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="O96" t="s">
         <v>64</v>
@@ -11871,7 +11865,7 @@
         <v>63</v>
       </c>
       <c r="S96" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="T96"/>
       <c r="U96"/>
@@ -11888,14 +11882,14 @@
         <v>209</v>
       </c>
       <c r="B97" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C97" t="s">
         <v>69</v>
       </c>
       <c r="D97"/>
       <c r="E97" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F97" t="s">
         <v>60</v>
@@ -11917,10 +11911,10 @@
         <v>59</v>
       </c>
       <c r="M97" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="N97" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="O97" t="s">
         <v>64</v>
@@ -11933,7 +11927,7 @@
         <v>63</v>
       </c>
       <c r="S97" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="T97"/>
       <c r="U97"/>
@@ -11950,14 +11944,14 @@
         <v>209</v>
       </c>
       <c r="B98" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C98" t="s">
         <v>69</v>
       </c>
       <c r="D98"/>
       <c r="E98" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F98" t="s">
         <v>60</v>
@@ -11972,17 +11966,17 @@
         <v>102</v>
       </c>
       <c r="J98" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K98"/>
       <c r="L98" t="s">
         <v>59</v>
       </c>
       <c r="M98" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="N98" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="O98" t="s">
         <v>64</v>
@@ -11995,7 +11989,7 @@
         <v>63</v>
       </c>
       <c r="S98" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="T98"/>
       <c r="U98"/>
@@ -12012,14 +12006,14 @@
         <v>209</v>
       </c>
       <c r="B99" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C99" t="s">
         <v>69</v>
       </c>
       <c r="D99"/>
       <c r="E99" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F99" t="s">
         <v>60</v>
@@ -12034,17 +12028,17 @@
         <v>102</v>
       </c>
       <c r="J99" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K99"/>
       <c r="L99" t="s">
         <v>59</v>
       </c>
       <c r="M99" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="N99" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="O99" t="s">
         <v>64</v>
@@ -12057,7 +12051,7 @@
         <v>63</v>
       </c>
       <c r="S99" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="T99"/>
       <c r="U99"/>
@@ -12074,14 +12068,14 @@
         <v>209</v>
       </c>
       <c r="B100" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C100" t="s">
         <v>69</v>
       </c>
       <c r="D100"/>
       <c r="E100" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F100" t="s">
         <v>60</v>
@@ -12103,10 +12097,10 @@
         <v>59</v>
       </c>
       <c r="M100" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="N100" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="O100" t="s">
         <v>64</v>
@@ -12119,7 +12113,7 @@
         <v>63</v>
       </c>
       <c r="S100" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="T100"/>
       <c r="U100"/>
@@ -12136,14 +12130,14 @@
         <v>209</v>
       </c>
       <c r="B101" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C101" t="s">
         <v>69</v>
       </c>
       <c r="D101"/>
       <c r="E101" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F101" t="s">
         <v>60</v>
@@ -12165,10 +12159,10 @@
         <v>59</v>
       </c>
       <c r="M101" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="N101" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="O101" t="s">
         <v>64</v>
@@ -12181,7 +12175,7 @@
         <v>63</v>
       </c>
       <c r="S101" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="T101"/>
       <c r="U101"/>
@@ -12198,14 +12192,14 @@
         <v>209</v>
       </c>
       <c r="B102" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C102" t="s">
         <v>69</v>
       </c>
       <c r="D102"/>
       <c r="E102" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F102" t="s">
         <v>60</v>
@@ -12227,10 +12221,10 @@
         <v>59</v>
       </c>
       <c r="M102" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="N102" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="O102" t="s">
         <v>64</v>
@@ -12243,7 +12237,7 @@
         <v>63</v>
       </c>
       <c r="S102" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="T102"/>
       <c r="U102"/>
@@ -12260,14 +12254,14 @@
         <v>209</v>
       </c>
       <c r="B103" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C103" t="s">
         <v>69</v>
       </c>
       <c r="D103"/>
       <c r="E103" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F103" t="s">
         <v>60</v>
@@ -12282,17 +12276,17 @@
         <v>102</v>
       </c>
       <c r="J103" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K103"/>
       <c r="L103" t="s">
         <v>59</v>
       </c>
       <c r="M103" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="N103" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="O103" t="s">
         <v>64</v>
@@ -12305,7 +12299,7 @@
         <v>63</v>
       </c>
       <c r="S103" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="T103"/>
       <c r="U103"/>
@@ -12322,14 +12316,14 @@
         <v>209</v>
       </c>
       <c r="B104" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C104" t="s">
         <v>69</v>
       </c>
       <c r="D104"/>
       <c r="E104" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F104" t="s">
         <v>60</v>
@@ -12344,17 +12338,17 @@
         <v>102</v>
       </c>
       <c r="J104" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K104"/>
       <c r="L104" t="s">
         <v>59</v>
       </c>
       <c r="M104" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="N104" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="O104" t="s">
         <v>64</v>
@@ -12367,7 +12361,7 @@
         <v>63</v>
       </c>
       <c r="S104" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="T104"/>
       <c r="U104"/>
@@ -12384,14 +12378,14 @@
         <v>209</v>
       </c>
       <c r="B105" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C105" t="s">
         <v>69</v>
       </c>
       <c r="D105"/>
       <c r="E105" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F105" t="s">
         <v>60</v>
@@ -12406,17 +12400,17 @@
         <v>102</v>
       </c>
       <c r="J105" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K105"/>
       <c r="L105" t="s">
         <v>59</v>
       </c>
       <c r="M105" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="N105" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="O105" t="s">
         <v>64</v>
@@ -12429,7 +12423,7 @@
         <v>63</v>
       </c>
       <c r="S105" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="T105"/>
       <c r="U105"/>
@@ -12446,14 +12440,14 @@
         <v>209</v>
       </c>
       <c r="B106" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C106" t="s">
         <v>69</v>
       </c>
       <c r="D106"/>
       <c r="E106" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F106" t="s">
         <v>60</v>
@@ -12475,10 +12469,10 @@
         <v>59</v>
       </c>
       <c r="M106" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="N106" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="O106" t="s">
         <v>64</v>
@@ -12491,7 +12485,7 @@
         <v>63</v>
       </c>
       <c r="S106" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="T106"/>
       <c r="U106"/>
@@ -12508,14 +12502,14 @@
         <v>209</v>
       </c>
       <c r="B107" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C107" t="s">
         <v>69</v>
       </c>
       <c r="D107"/>
       <c r="E107" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F107" t="s">
         <v>60</v>
@@ -12537,10 +12531,10 @@
         <v>59</v>
       </c>
       <c r="M107" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="N107" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="O107" t="s">
         <v>64</v>
@@ -12553,7 +12547,7 @@
         <v>63</v>
       </c>
       <c r="S107" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="T107"/>
       <c r="U107"/>
@@ -12570,14 +12564,14 @@
         <v>209</v>
       </c>
       <c r="B108" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C108" t="s">
         <v>69</v>
       </c>
       <c r="D108"/>
       <c r="E108" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F108" t="s">
         <v>60</v>
@@ -12592,17 +12586,17 @@
         <v>102</v>
       </c>
       <c r="J108" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K108"/>
       <c r="L108" t="s">
         <v>59</v>
       </c>
       <c r="M108" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="N108" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="O108" t="s">
         <v>64</v>
@@ -12615,7 +12609,7 @@
         <v>63</v>
       </c>
       <c r="S108" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="T108"/>
       <c r="U108"/>
@@ -12632,14 +12626,14 @@
         <v>209</v>
       </c>
       <c r="B109" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C109" t="s">
         <v>69</v>
       </c>
       <c r="D109"/>
       <c r="E109" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F109" t="s">
         <v>60</v>
@@ -12654,17 +12648,17 @@
         <v>102</v>
       </c>
       <c r="J109" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K109"/>
       <c r="L109" t="s">
         <v>59</v>
       </c>
       <c r="M109" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="N109" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="O109" t="s">
         <v>64</v>
@@ -12677,7 +12671,7 @@
         <v>63</v>
       </c>
       <c r="S109" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="T109"/>
       <c r="U109"/>
@@ -12694,14 +12688,14 @@
         <v>209</v>
       </c>
       <c r="B110" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C110" t="s">
         <v>69</v>
       </c>
       <c r="D110"/>
       <c r="E110" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F110" t="s">
         <v>60</v>
@@ -12723,10 +12717,10 @@
         <v>59</v>
       </c>
       <c r="M110" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="N110" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="O110" t="s">
         <v>64</v>
@@ -12739,7 +12733,7 @@
         <v>63</v>
       </c>
       <c r="S110" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="T110"/>
       <c r="U110"/>
@@ -12756,14 +12750,14 @@
         <v>209</v>
       </c>
       <c r="B111" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C111" t="s">
         <v>69</v>
       </c>
       <c r="D111"/>
       <c r="E111" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F111" t="s">
         <v>60</v>
@@ -12785,10 +12779,10 @@
         <v>59</v>
       </c>
       <c r="M111" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="N111" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="O111" t="s">
         <v>64</v>
@@ -12801,7 +12795,7 @@
         <v>63</v>
       </c>
       <c r="S111" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="T111"/>
       <c r="U111"/>
@@ -12818,14 +12812,14 @@
         <v>209</v>
       </c>
       <c r="B112" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C112" t="s">
         <v>69</v>
       </c>
       <c r="D112"/>
       <c r="E112" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F112" t="s">
         <v>60</v>
@@ -12847,10 +12841,10 @@
         <v>59</v>
       </c>
       <c r="M112" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="N112" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="O112" t="s">
         <v>64</v>
@@ -12863,7 +12857,7 @@
         <v>63</v>
       </c>
       <c r="S112" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="T112"/>
       <c r="U112"/>
@@ -12880,14 +12874,14 @@
         <v>209</v>
       </c>
       <c r="B113" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C113" t="s">
         <v>69</v>
       </c>
       <c r="D113"/>
       <c r="E113" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F113" t="s">
         <v>60</v>
@@ -12902,17 +12896,17 @@
         <v>102</v>
       </c>
       <c r="J113" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K113"/>
       <c r="L113" t="s">
         <v>59</v>
       </c>
       <c r="M113" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="N113" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="O113" t="s">
         <v>64</v>
@@ -12925,7 +12919,7 @@
         <v>63</v>
       </c>
       <c r="S113" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="T113"/>
       <c r="U113"/>
@@ -12942,14 +12936,14 @@
         <v>209</v>
       </c>
       <c r="B114" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C114" t="s">
         <v>69</v>
       </c>
       <c r="D114"/>
       <c r="E114" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F114" t="s">
         <v>60</v>
@@ -12964,17 +12958,17 @@
         <v>102</v>
       </c>
       <c r="J114" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K114"/>
       <c r="L114" t="s">
         <v>59</v>
       </c>
       <c r="M114" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="N114" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="O114" t="s">
         <v>64</v>
@@ -12987,7 +12981,7 @@
         <v>63</v>
       </c>
       <c r="S114" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="T114"/>
       <c r="U114"/>
@@ -13004,14 +12998,14 @@
         <v>209</v>
       </c>
       <c r="B115" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C115" t="s">
         <v>69</v>
       </c>
       <c r="D115"/>
       <c r="E115" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F115" t="s">
         <v>60</v>
@@ -13026,17 +13020,17 @@
         <v>102</v>
       </c>
       <c r="J115" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K115"/>
       <c r="L115" t="s">
         <v>59</v>
       </c>
       <c r="M115" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="N115" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="O115" t="s">
         <v>64</v>
@@ -13049,7 +13043,7 @@
         <v>63</v>
       </c>
       <c r="S115" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="T115"/>
       <c r="U115"/>
@@ -13066,14 +13060,14 @@
         <v>209</v>
       </c>
       <c r="B116" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C116" t="s">
         <v>69</v>
       </c>
       <c r="D116"/>
       <c r="E116" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F116" t="s">
         <v>60</v>
@@ -13095,10 +13089,10 @@
         <v>59</v>
       </c>
       <c r="M116" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="N116" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="O116" t="s">
         <v>64</v>
@@ -13111,7 +13105,7 @@
         <v>63</v>
       </c>
       <c r="S116" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="T116"/>
       <c r="U116"/>
@@ -13128,14 +13122,14 @@
         <v>209</v>
       </c>
       <c r="B117" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C117" t="s">
         <v>69</v>
       </c>
       <c r="D117"/>
       <c r="E117" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F117" t="s">
         <v>60</v>
@@ -13157,10 +13151,10 @@
         <v>59</v>
       </c>
       <c r="M117" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="N117" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="O117" t="s">
         <v>64</v>
@@ -13173,7 +13167,7 @@
         <v>63</v>
       </c>
       <c r="S117" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="T117"/>
       <c r="U117"/>
@@ -13190,14 +13184,14 @@
         <v>209</v>
       </c>
       <c r="B118" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C118" t="s">
         <v>69</v>
       </c>
       <c r="D118"/>
       <c r="E118" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F118" t="s">
         <v>60</v>
@@ -13212,17 +13206,17 @@
         <v>102</v>
       </c>
       <c r="J118" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K118"/>
       <c r="L118" t="s">
         <v>59</v>
       </c>
       <c r="M118" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="N118" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="O118" t="s">
         <v>64</v>
@@ -13235,7 +13229,7 @@
         <v>63</v>
       </c>
       <c r="S118" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="T118"/>
       <c r="U118"/>
@@ -13252,14 +13246,14 @@
         <v>209</v>
       </c>
       <c r="B119" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C119" t="s">
         <v>69</v>
       </c>
       <c r="D119"/>
       <c r="E119" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F119" t="s">
         <v>60</v>
@@ -13274,17 +13268,17 @@
         <v>102</v>
       </c>
       <c r="J119" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K119"/>
       <c r="L119" t="s">
         <v>59</v>
       </c>
       <c r="M119" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="N119" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="O119" t="s">
         <v>64</v>
@@ -13297,7 +13291,7 @@
         <v>63</v>
       </c>
       <c r="S119" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="T119"/>
       <c r="U119"/>
@@ -13314,14 +13308,14 @@
         <v>209</v>
       </c>
       <c r="B120" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C120" t="s">
         <v>69</v>
       </c>
       <c r="D120"/>
       <c r="E120" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F120" t="s">
         <v>60</v>
@@ -13343,10 +13337,10 @@
         <v>59</v>
       </c>
       <c r="M120" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="N120" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="O120" t="s">
         <v>64</v>
@@ -13359,7 +13353,7 @@
         <v>63</v>
       </c>
       <c r="S120" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="T120"/>
       <c r="U120"/>
@@ -13376,14 +13370,14 @@
         <v>209</v>
       </c>
       <c r="B121" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C121" t="s">
         <v>69</v>
       </c>
       <c r="D121"/>
       <c r="E121" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F121" t="s">
         <v>60</v>
@@ -13405,10 +13399,10 @@
         <v>59</v>
       </c>
       <c r="M121" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="N121" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="O121" t="s">
         <v>64</v>
@@ -13421,7 +13415,7 @@
         <v>63</v>
       </c>
       <c r="S121" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="T121"/>
       <c r="U121"/>
@@ -13438,14 +13432,14 @@
         <v>209</v>
       </c>
       <c r="B122" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C122" t="s">
         <v>69</v>
       </c>
       <c r="D122"/>
       <c r="E122" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F122" t="s">
         <v>60</v>
@@ -13467,10 +13461,10 @@
         <v>59</v>
       </c>
       <c r="M122" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="N122" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="O122" t="s">
         <v>64</v>
@@ -13483,7 +13477,7 @@
         <v>63</v>
       </c>
       <c r="S122" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="T122"/>
       <c r="U122"/>
@@ -13500,14 +13494,14 @@
         <v>209</v>
       </c>
       <c r="B123" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C123" t="s">
         <v>69</v>
       </c>
       <c r="D123"/>
       <c r="E123" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F123" t="s">
         <v>60</v>
@@ -13522,17 +13516,17 @@
         <v>102</v>
       </c>
       <c r="J123" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K123"/>
       <c r="L123" t="s">
         <v>59</v>
       </c>
       <c r="M123" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="N123" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="O123" t="s">
         <v>64</v>
@@ -13545,7 +13539,7 @@
         <v>63</v>
       </c>
       <c r="S123" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="T123"/>
       <c r="U123"/>
@@ -13562,14 +13556,14 @@
         <v>209</v>
       </c>
       <c r="B124" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C124" t="s">
         <v>69</v>
       </c>
       <c r="D124"/>
       <c r="E124" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F124" t="s">
         <v>60</v>
@@ -13584,17 +13578,17 @@
         <v>102</v>
       </c>
       <c r="J124" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K124"/>
       <c r="L124" t="s">
         <v>59</v>
       </c>
       <c r="M124" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="N124" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="O124" t="s">
         <v>64</v>
@@ -13607,7 +13601,7 @@
         <v>63</v>
       </c>
       <c r="S124" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="T124"/>
       <c r="U124"/>
@@ -13624,14 +13618,14 @@
         <v>209</v>
       </c>
       <c r="B125" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C125" t="s">
         <v>69</v>
       </c>
       <c r="D125"/>
       <c r="E125" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F125" t="s">
         <v>60</v>
@@ -13646,17 +13640,17 @@
         <v>102</v>
       </c>
       <c r="J125" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K125"/>
       <c r="L125" t="s">
         <v>59</v>
       </c>
       <c r="M125" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="N125" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="O125" t="s">
         <v>64</v>
@@ -13669,7 +13663,7 @@
         <v>63</v>
       </c>
       <c r="S125" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="T125"/>
       <c r="U125"/>
@@ -13686,14 +13680,14 @@
         <v>209</v>
       </c>
       <c r="B126" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C126" t="s">
         <v>69</v>
       </c>
       <c r="D126"/>
       <c r="E126" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F126" t="s">
         <v>60</v>
@@ -13715,10 +13709,10 @@
         <v>59</v>
       </c>
       <c r="M126" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="N126" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="O126" t="s">
         <v>64</v>
@@ -13731,7 +13725,7 @@
         <v>63</v>
       </c>
       <c r="S126" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="T126"/>
       <c r="U126"/>
@@ -13748,14 +13742,14 @@
         <v>209</v>
       </c>
       <c r="B127" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C127" t="s">
         <v>69</v>
       </c>
       <c r="D127"/>
       <c r="E127" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F127" t="s">
         <v>60</v>
@@ -13777,10 +13771,10 @@
         <v>59</v>
       </c>
       <c r="M127" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="N127" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="O127" t="s">
         <v>64</v>
@@ -13793,7 +13787,7 @@
         <v>63</v>
       </c>
       <c r="S127" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="T127"/>
       <c r="U127"/>
@@ -13810,14 +13804,14 @@
         <v>209</v>
       </c>
       <c r="B128" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C128" t="s">
         <v>69</v>
       </c>
       <c r="D128"/>
       <c r="E128" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F128" t="s">
         <v>60</v>
@@ -13832,17 +13826,17 @@
         <v>102</v>
       </c>
       <c r="J128" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K128"/>
       <c r="L128" t="s">
         <v>59</v>
       </c>
       <c r="M128" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="N128" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="O128" t="s">
         <v>64</v>
@@ -13855,7 +13849,7 @@
         <v>63</v>
       </c>
       <c r="S128" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="T128"/>
       <c r="U128"/>
@@ -13872,14 +13866,14 @@
         <v>209</v>
       </c>
       <c r="B129" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C129" t="s">
         <v>69</v>
       </c>
       <c r="D129"/>
       <c r="E129" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F129" t="s">
         <v>60</v>
@@ -13894,17 +13888,17 @@
         <v>102</v>
       </c>
       <c r="J129" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K129"/>
       <c r="L129" t="s">
         <v>59</v>
       </c>
       <c r="M129" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="N129" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="O129" t="s">
         <v>64</v>
@@ -13917,7 +13911,7 @@
         <v>63</v>
       </c>
       <c r="S129" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="T129"/>
       <c r="U129"/>
@@ -13934,14 +13928,14 @@
         <v>209</v>
       </c>
       <c r="B130" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C130" t="s">
         <v>69</v>
       </c>
       <c r="D130"/>
       <c r="E130" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F130" t="s">
         <v>60</v>
@@ -13963,10 +13957,10 @@
         <v>59</v>
       </c>
       <c r="M130" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="N130" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="O130" t="s">
         <v>64</v>
@@ -13979,7 +13973,7 @@
         <v>63</v>
       </c>
       <c r="S130" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="T130"/>
       <c r="U130"/>
@@ -13996,14 +13990,14 @@
         <v>209</v>
       </c>
       <c r="B131" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C131" t="s">
         <v>69</v>
       </c>
       <c r="D131"/>
       <c r="E131" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F131" t="s">
         <v>60</v>
@@ -14025,10 +14019,10 @@
         <v>59</v>
       </c>
       <c r="M131" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="N131" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="O131" t="s">
         <v>64</v>
@@ -14041,7 +14035,7 @@
         <v>63</v>
       </c>
       <c r="S131" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="T131"/>
       <c r="U131"/>
@@ -14058,14 +14052,14 @@
         <v>209</v>
       </c>
       <c r="B132" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C132" t="s">
         <v>69</v>
       </c>
       <c r="D132"/>
       <c r="E132" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F132" t="s">
         <v>60</v>
@@ -14087,10 +14081,10 @@
         <v>59</v>
       </c>
       <c r="M132" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="N132" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="O132" t="s">
         <v>64</v>
@@ -14103,7 +14097,7 @@
         <v>63</v>
       </c>
       <c r="S132" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="T132"/>
       <c r="U132"/>
@@ -14120,14 +14114,14 @@
         <v>209</v>
       </c>
       <c r="B133" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C133" t="s">
         <v>69</v>
       </c>
       <c r="D133"/>
       <c r="E133" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F133" t="s">
         <v>60</v>
@@ -14142,17 +14136,17 @@
         <v>102</v>
       </c>
       <c r="J133" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K133"/>
       <c r="L133" t="s">
         <v>59</v>
       </c>
       <c r="M133" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="N133" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="O133" t="s">
         <v>64</v>
@@ -14165,7 +14159,7 @@
         <v>63</v>
       </c>
       <c r="S133" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="T133"/>
       <c r="U133"/>
@@ -14182,14 +14176,14 @@
         <v>209</v>
       </c>
       <c r="B134" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C134" t="s">
         <v>69</v>
       </c>
       <c r="D134"/>
       <c r="E134" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F134" t="s">
         <v>60</v>
@@ -14204,17 +14198,17 @@
         <v>102</v>
       </c>
       <c r="J134" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K134"/>
       <c r="L134" t="s">
         <v>59</v>
       </c>
       <c r="M134" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="N134" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="O134" t="s">
         <v>64</v>
@@ -14227,7 +14221,7 @@
         <v>63</v>
       </c>
       <c r="S134" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="T134"/>
       <c r="U134"/>
@@ -14244,14 +14238,14 @@
         <v>209</v>
       </c>
       <c r="B135" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C135" t="s">
         <v>69</v>
       </c>
       <c r="D135"/>
       <c r="E135" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F135" t="s">
         <v>60</v>
@@ -14266,17 +14260,17 @@
         <v>102</v>
       </c>
       <c r="J135" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K135"/>
       <c r="L135" t="s">
         <v>59</v>
       </c>
       <c r="M135" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="N135" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="O135" t="s">
         <v>64</v>
@@ -14289,7 +14283,7 @@
         <v>63</v>
       </c>
       <c r="S135" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="T135"/>
       <c r="U135"/>
@@ -14306,14 +14300,14 @@
         <v>209</v>
       </c>
       <c r="B136" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C136" t="s">
         <v>69</v>
       </c>
       <c r="D136"/>
       <c r="E136" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F136" t="s">
         <v>60</v>
@@ -14335,10 +14329,10 @@
         <v>59</v>
       </c>
       <c r="M136" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="N136" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="O136" t="s">
         <v>64</v>
@@ -14351,7 +14345,7 @@
         <v>63</v>
       </c>
       <c r="S136" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="T136"/>
       <c r="U136"/>
@@ -14368,14 +14362,14 @@
         <v>209</v>
       </c>
       <c r="B137" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C137" t="s">
         <v>69</v>
       </c>
       <c r="D137"/>
       <c r="E137" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F137" t="s">
         <v>60</v>
@@ -14397,10 +14391,10 @@
         <v>59</v>
       </c>
       <c r="M137" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="N137" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="O137" t="s">
         <v>64</v>
@@ -14413,7 +14407,7 @@
         <v>63</v>
       </c>
       <c r="S137" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="T137"/>
       <c r="U137"/>
@@ -14430,14 +14424,14 @@
         <v>209</v>
       </c>
       <c r="B138" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C138" t="s">
         <v>69</v>
       </c>
       <c r="D138"/>
       <c r="E138" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F138" t="s">
         <v>60</v>
@@ -14452,17 +14446,17 @@
         <v>102</v>
       </c>
       <c r="J138" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K138"/>
       <c r="L138" t="s">
         <v>59</v>
       </c>
       <c r="M138" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="N138" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="O138" t="s">
         <v>64</v>
@@ -14475,7 +14469,7 @@
         <v>63</v>
       </c>
       <c r="S138" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="T138"/>
       <c r="U138"/>
@@ -14492,14 +14486,14 @@
         <v>209</v>
       </c>
       <c r="B139" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="C139" t="s">
         <v>69</v>
       </c>
       <c r="D139"/>
       <c r="E139" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F139" t="s">
         <v>60</v>
@@ -14514,17 +14508,17 @@
         <v>102</v>
       </c>
       <c r="J139" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K139"/>
       <c r="L139" t="s">
         <v>59</v>
       </c>
       <c r="M139" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="N139" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="O139" t="s">
         <v>64</v>
@@ -14537,7 +14531,7 @@
         <v>63</v>
       </c>
       <c r="S139" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="T139"/>
       <c r="U139"/>
@@ -14554,14 +14548,14 @@
         <v>209</v>
       </c>
       <c r="B140" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C140" t="s">
         <v>69</v>
       </c>
       <c r="D140"/>
       <c r="E140" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F140" t="s">
         <v>60</v>
@@ -14583,10 +14577,10 @@
         <v>59</v>
       </c>
       <c r="M140" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="N140" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="O140" t="s">
         <v>64</v>
@@ -14599,7 +14593,7 @@
         <v>63</v>
       </c>
       <c r="S140" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="T140"/>
       <c r="U140"/>
@@ -14616,14 +14610,14 @@
         <v>209</v>
       </c>
       <c r="B141" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C141" t="s">
         <v>69</v>
       </c>
       <c r="D141"/>
       <c r="E141" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F141" t="s">
         <v>60</v>
@@ -14645,10 +14639,10 @@
         <v>59</v>
       </c>
       <c r="M141" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="N141" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="O141" t="s">
         <v>64</v>
@@ -14661,7 +14655,7 @@
         <v>63</v>
       </c>
       <c r="S141" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="T141"/>
       <c r="U141"/>
@@ -14678,14 +14672,14 @@
         <v>209</v>
       </c>
       <c r="B142" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C142" t="s">
         <v>69</v>
       </c>
       <c r="D142"/>
       <c r="E142" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F142" t="s">
         <v>60</v>
@@ -14707,10 +14701,10 @@
         <v>59</v>
       </c>
       <c r="M142" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="N142" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="O142" t="s">
         <v>64</v>
@@ -14723,7 +14717,7 @@
         <v>63</v>
       </c>
       <c r="S142" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="T142"/>
       <c r="U142"/>
@@ -14740,14 +14734,14 @@
         <v>209</v>
       </c>
       <c r="B143" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C143" t="s">
         <v>69</v>
       </c>
       <c r="D143"/>
       <c r="E143" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F143" t="s">
         <v>60</v>
@@ -14762,17 +14756,17 @@
         <v>102</v>
       </c>
       <c r="J143" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K143"/>
       <c r="L143" t="s">
         <v>59</v>
       </c>
       <c r="M143" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="N143" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="O143" t="s">
         <v>64</v>
@@ -14785,7 +14779,7 @@
         <v>63</v>
       </c>
       <c r="S143" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="T143"/>
       <c r="U143"/>
@@ -14802,14 +14796,14 @@
         <v>209</v>
       </c>
       <c r="B144" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C144" t="s">
         <v>69</v>
       </c>
       <c r="D144"/>
       <c r="E144" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F144" t="s">
         <v>60</v>
@@ -14824,17 +14818,17 @@
         <v>102</v>
       </c>
       <c r="J144" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K144"/>
       <c r="L144" t="s">
         <v>59</v>
       </c>
       <c r="M144" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="N144" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="O144" t="s">
         <v>64</v>
@@ -14847,7 +14841,7 @@
         <v>63</v>
       </c>
       <c r="S144" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="T144"/>
       <c r="U144"/>
@@ -14864,14 +14858,14 @@
         <v>209</v>
       </c>
       <c r="B145" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C145" t="s">
         <v>69</v>
       </c>
       <c r="D145"/>
       <c r="E145" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F145" t="s">
         <v>60</v>
@@ -14886,17 +14880,17 @@
         <v>102</v>
       </c>
       <c r="J145" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K145"/>
       <c r="L145" t="s">
         <v>59</v>
       </c>
       <c r="M145" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="N145" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="O145" t="s">
         <v>64</v>
@@ -14909,7 +14903,7 @@
         <v>63</v>
       </c>
       <c r="S145" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="T145"/>
       <c r="U145"/>
@@ -14926,14 +14920,14 @@
         <v>209</v>
       </c>
       <c r="B146" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C146" t="s">
         <v>69</v>
       </c>
       <c r="D146"/>
       <c r="E146" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F146" t="s">
         <v>60</v>
@@ -14955,10 +14949,10 @@
         <v>59</v>
       </c>
       <c r="M146" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="N146" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="O146" t="s">
         <v>64</v>
@@ -14971,7 +14965,7 @@
         <v>63</v>
       </c>
       <c r="S146" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="T146"/>
       <c r="U146"/>
@@ -14988,14 +14982,14 @@
         <v>209</v>
       </c>
       <c r="B147" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C147" t="s">
         <v>69</v>
       </c>
       <c r="D147"/>
       <c r="E147" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F147" t="s">
         <v>60</v>
@@ -15017,10 +15011,10 @@
         <v>59</v>
       </c>
       <c r="M147" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="N147" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="O147" t="s">
         <v>64</v>
@@ -15033,7 +15027,7 @@
         <v>63</v>
       </c>
       <c r="S147" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="T147"/>
       <c r="U147"/>
@@ -15050,14 +15044,14 @@
         <v>209</v>
       </c>
       <c r="B148" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C148" t="s">
         <v>69</v>
       </c>
       <c r="D148"/>
       <c r="E148" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F148" t="s">
         <v>60</v>
@@ -15072,17 +15066,17 @@
         <v>102</v>
       </c>
       <c r="J148" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K148"/>
       <c r="L148" t="s">
         <v>59</v>
       </c>
       <c r="M148" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="N148" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="O148" t="s">
         <v>64</v>
@@ -15095,7 +15089,7 @@
         <v>63</v>
       </c>
       <c r="S148" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="T148"/>
       <c r="U148"/>
@@ -15112,14 +15106,14 @@
         <v>209</v>
       </c>
       <c r="B149" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="C149" t="s">
         <v>69</v>
       </c>
       <c r="D149"/>
       <c r="E149" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F149" t="s">
         <v>60</v>
@@ -15134,17 +15128,17 @@
         <v>102</v>
       </c>
       <c r="J149" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K149"/>
       <c r="L149" t="s">
         <v>59</v>
       </c>
       <c r="M149" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="N149" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="O149" t="s">
         <v>64</v>
@@ -15157,7 +15151,7 @@
         <v>63</v>
       </c>
       <c r="S149" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="T149"/>
       <c r="U149"/>
@@ -15174,14 +15168,14 @@
         <v>209</v>
       </c>
       <c r="B150" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="C150" t="s">
         <v>69</v>
       </c>
       <c r="D150"/>
       <c r="E150" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F150" t="s">
         <v>60</v>
@@ -15203,10 +15197,10 @@
         <v>59</v>
       </c>
       <c r="M150" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="N150" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="O150" t="s">
         <v>64</v>
@@ -15219,7 +15213,7 @@
         <v>63</v>
       </c>
       <c r="S150" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="T150"/>
       <c r="U150"/>
@@ -15236,14 +15230,14 @@
         <v>209</v>
       </c>
       <c r="B151" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C151" t="s">
         <v>69</v>
       </c>
       <c r="D151"/>
       <c r="E151" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F151" t="s">
         <v>60</v>
@@ -15265,10 +15259,10 @@
         <v>59</v>
       </c>
       <c r="M151" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="N151" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="O151" t="s">
         <v>64</v>
@@ -15281,7 +15275,7 @@
         <v>63</v>
       </c>
       <c r="S151" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="T151"/>
       <c r="U151"/>
@@ -15298,14 +15292,14 @@
         <v>209</v>
       </c>
       <c r="B152" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C152" t="s">
         <v>69</v>
       </c>
       <c r="D152"/>
       <c r="E152" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F152" t="s">
         <v>60</v>
@@ -15327,10 +15321,10 @@
         <v>59</v>
       </c>
       <c r="M152" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="N152" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="O152" t="s">
         <v>64</v>
@@ -15343,7 +15337,7 @@
         <v>63</v>
       </c>
       <c r="S152" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="T152"/>
       <c r="U152"/>
@@ -15360,14 +15354,14 @@
         <v>209</v>
       </c>
       <c r="B153" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="C153" t="s">
         <v>69</v>
       </c>
       <c r="D153"/>
       <c r="E153" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F153" t="s">
         <v>60</v>
@@ -15382,17 +15376,17 @@
         <v>102</v>
       </c>
       <c r="J153" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K153"/>
       <c r="L153" t="s">
         <v>59</v>
       </c>
       <c r="M153" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="N153" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="O153" t="s">
         <v>64</v>
@@ -15405,7 +15399,7 @@
         <v>63</v>
       </c>
       <c r="S153" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="T153"/>
       <c r="U153"/>
@@ -15422,14 +15416,14 @@
         <v>209</v>
       </c>
       <c r="B154" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C154" t="s">
         <v>69</v>
       </c>
       <c r="D154"/>
       <c r="E154" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F154" t="s">
         <v>60</v>
@@ -15444,17 +15438,17 @@
         <v>102</v>
       </c>
       <c r="J154" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K154"/>
       <c r="L154" t="s">
         <v>59</v>
       </c>
       <c r="M154" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="N154" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="O154" t="s">
         <v>64</v>
@@ -15467,7 +15461,7 @@
         <v>63</v>
       </c>
       <c r="S154" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="T154"/>
       <c r="U154"/>
@@ -15484,14 +15478,14 @@
         <v>209</v>
       </c>
       <c r="B155" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C155" t="s">
         <v>69</v>
       </c>
       <c r="D155"/>
       <c r="E155" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F155" t="s">
         <v>60</v>
@@ -15506,17 +15500,17 @@
         <v>102</v>
       </c>
       <c r="J155" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K155"/>
       <c r="L155" t="s">
         <v>59</v>
       </c>
       <c r="M155" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="N155" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="O155" t="s">
         <v>64</v>
@@ -15529,7 +15523,7 @@
         <v>63</v>
       </c>
       <c r="S155" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="T155"/>
       <c r="U155"/>
@@ -15546,14 +15540,14 @@
         <v>209</v>
       </c>
       <c r="B156" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C156" t="s">
         <v>69</v>
       </c>
       <c r="D156"/>
       <c r="E156" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F156" t="s">
         <v>60</v>
@@ -15575,10 +15569,10 @@
         <v>59</v>
       </c>
       <c r="M156" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="N156" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="O156" t="s">
         <v>64</v>
@@ -15591,7 +15585,7 @@
         <v>63</v>
       </c>
       <c r="S156" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="T156"/>
       <c r="U156"/>
@@ -15608,14 +15602,14 @@
         <v>209</v>
       </c>
       <c r="B157" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C157" t="s">
         <v>69</v>
       </c>
       <c r="D157"/>
       <c r="E157" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F157" t="s">
         <v>60</v>
@@ -15637,10 +15631,10 @@
         <v>59</v>
       </c>
       <c r="M157" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="N157" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="O157" t="s">
         <v>64</v>
@@ -15653,7 +15647,7 @@
         <v>63</v>
       </c>
       <c r="S157" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="T157"/>
       <c r="U157"/>
@@ -15670,14 +15664,14 @@
         <v>209</v>
       </c>
       <c r="B158" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C158" t="s">
         <v>69</v>
       </c>
       <c r="D158"/>
       <c r="E158" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F158" t="s">
         <v>60</v>
@@ -15692,17 +15686,17 @@
         <v>102</v>
       </c>
       <c r="J158" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K158"/>
       <c r="L158" t="s">
         <v>59</v>
       </c>
       <c r="M158" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="N158" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="O158" t="s">
         <v>64</v>
@@ -15715,7 +15709,7 @@
         <v>63</v>
       </c>
       <c r="S158" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="T158"/>
       <c r="U158"/>
@@ -15732,14 +15726,14 @@
         <v>209</v>
       </c>
       <c r="B159" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="C159" t="s">
         <v>69</v>
       </c>
       <c r="D159"/>
       <c r="E159" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F159" t="s">
         <v>60</v>
@@ -15754,17 +15748,17 @@
         <v>102</v>
       </c>
       <c r="J159" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K159"/>
       <c r="L159" t="s">
         <v>59</v>
       </c>
       <c r="M159" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="N159" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="O159" t="s">
         <v>64</v>
@@ -15777,7 +15771,7 @@
         <v>63</v>
       </c>
       <c r="S159" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="T159"/>
       <c r="U159"/>
@@ -15794,14 +15788,14 @@
         <v>209</v>
       </c>
       <c r="B160" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="C160" t="s">
         <v>69</v>
       </c>
       <c r="D160"/>
       <c r="E160" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F160" t="s">
         <v>60</v>
@@ -15823,10 +15817,10 @@
         <v>59</v>
       </c>
       <c r="M160" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="N160" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="O160" t="s">
         <v>64</v>
@@ -15839,7 +15833,7 @@
         <v>63</v>
       </c>
       <c r="S160" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="T160"/>
       <c r="U160"/>
@@ -15856,14 +15850,14 @@
         <v>209</v>
       </c>
       <c r="B161" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="C161" t="s">
         <v>69</v>
       </c>
       <c r="D161"/>
       <c r="E161" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F161" t="s">
         <v>60</v>
@@ -15885,10 +15879,10 @@
         <v>59</v>
       </c>
       <c r="M161" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="N161" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="O161" t="s">
         <v>64</v>
@@ -15901,7 +15895,7 @@
         <v>63</v>
       </c>
       <c r="S161" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="T161"/>
       <c r="U161"/>
@@ -15918,14 +15912,14 @@
         <v>209</v>
       </c>
       <c r="B162" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="C162" t="s">
         <v>69</v>
       </c>
       <c r="D162"/>
       <c r="E162" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F162" t="s">
         <v>60</v>
@@ -15947,10 +15941,10 @@
         <v>59</v>
       </c>
       <c r="M162" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="N162" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="O162" t="s">
         <v>64</v>
@@ -15963,7 +15957,7 @@
         <v>63</v>
       </c>
       <c r="S162" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="T162"/>
       <c r="U162"/>
@@ -15980,14 +15974,14 @@
         <v>209</v>
       </c>
       <c r="B163" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="C163" t="s">
         <v>69</v>
       </c>
       <c r="D163"/>
       <c r="E163" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F163" t="s">
         <v>60</v>
@@ -16002,17 +15996,17 @@
         <v>102</v>
       </c>
       <c r="J163" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K163"/>
       <c r="L163" t="s">
         <v>59</v>
       </c>
       <c r="M163" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="N163" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="O163" t="s">
         <v>64</v>
@@ -16025,7 +16019,7 @@
         <v>63</v>
       </c>
       <c r="S163" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="T163"/>
       <c r="U163"/>
@@ -16042,14 +16036,14 @@
         <v>209</v>
       </c>
       <c r="B164" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="C164" t="s">
         <v>69</v>
       </c>
       <c r="D164"/>
       <c r="E164" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F164" t="s">
         <v>60</v>
@@ -16064,17 +16058,17 @@
         <v>102</v>
       </c>
       <c r="J164" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K164"/>
       <c r="L164" t="s">
         <v>59</v>
       </c>
       <c r="M164" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="N164" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="O164" t="s">
         <v>64</v>
@@ -16087,7 +16081,7 @@
         <v>63</v>
       </c>
       <c r="S164" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="T164"/>
       <c r="U164"/>
@@ -16104,14 +16098,14 @@
         <v>209</v>
       </c>
       <c r="B165" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="C165" t="s">
         <v>69</v>
       </c>
       <c r="D165"/>
       <c r="E165" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F165" t="s">
         <v>60</v>
@@ -16126,17 +16120,17 @@
         <v>102</v>
       </c>
       <c r="J165" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K165"/>
       <c r="L165" t="s">
         <v>59</v>
       </c>
       <c r="M165" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="N165" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="O165" t="s">
         <v>64</v>
@@ -16149,7 +16143,7 @@
         <v>63</v>
       </c>
       <c r="S165" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="T165"/>
       <c r="U165"/>
@@ -16166,14 +16160,14 @@
         <v>209</v>
       </c>
       <c r="B166" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="C166" t="s">
         <v>69</v>
       </c>
       <c r="D166"/>
       <c r="E166" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F166" t="s">
         <v>60</v>
@@ -16195,10 +16189,10 @@
         <v>59</v>
       </c>
       <c r="M166" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="N166" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="O166" t="s">
         <v>64</v>
@@ -16211,7 +16205,7 @@
         <v>63</v>
       </c>
       <c r="S166" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="T166"/>
       <c r="U166"/>
@@ -16228,14 +16222,14 @@
         <v>209</v>
       </c>
       <c r="B167" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="C167" t="s">
         <v>69</v>
       </c>
       <c r="D167"/>
       <c r="E167" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F167" t="s">
         <v>60</v>
@@ -16257,10 +16251,10 @@
         <v>59</v>
       </c>
       <c r="M167" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="N167" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="O167" t="s">
         <v>64</v>
@@ -16273,7 +16267,7 @@
         <v>63</v>
       </c>
       <c r="S167" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="T167"/>
       <c r="U167"/>
@@ -16290,14 +16284,14 @@
         <v>209</v>
       </c>
       <c r="B168" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="C168" t="s">
         <v>69</v>
       </c>
       <c r="D168"/>
       <c r="E168" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F168" t="s">
         <v>60</v>
@@ -16312,17 +16306,17 @@
         <v>102</v>
       </c>
       <c r="J168" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K168"/>
       <c r="L168" t="s">
         <v>59</v>
       </c>
       <c r="M168" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="N168" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="O168" t="s">
         <v>64</v>
@@ -16335,7 +16329,7 @@
         <v>63</v>
       </c>
       <c r="S168" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="T168"/>
       <c r="U168"/>
@@ -16352,14 +16346,14 @@
         <v>209</v>
       </c>
       <c r="B169" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="C169" t="s">
         <v>69</v>
       </c>
       <c r="D169"/>
       <c r="E169" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F169" t="s">
         <v>60</v>
@@ -16374,17 +16368,17 @@
         <v>102</v>
       </c>
       <c r="J169" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K169"/>
       <c r="L169" t="s">
         <v>59</v>
       </c>
       <c r="M169" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="N169" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="O169" t="s">
         <v>64</v>
@@ -16397,7 +16391,7 @@
         <v>63</v>
       </c>
       <c r="S169" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="T169"/>
       <c r="U169"/>
@@ -16414,14 +16408,14 @@
         <v>209</v>
       </c>
       <c r="B170" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="C170" t="s">
         <v>69</v>
       </c>
       <c r="D170"/>
       <c r="E170" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F170" t="s">
         <v>60</v>
@@ -16443,10 +16437,10 @@
         <v>59</v>
       </c>
       <c r="M170" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="N170" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="O170" t="s">
         <v>64</v>
@@ -16459,7 +16453,7 @@
         <v>63</v>
       </c>
       <c r="S170" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="T170"/>
       <c r="U170"/>
@@ -16476,14 +16470,14 @@
         <v>209</v>
       </c>
       <c r="B171" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C171" t="s">
         <v>69</v>
       </c>
       <c r="D171"/>
       <c r="E171" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F171" t="s">
         <v>60</v>
@@ -16505,10 +16499,10 @@
         <v>59</v>
       </c>
       <c r="M171" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="N171" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="O171" t="s">
         <v>64</v>
@@ -16521,7 +16515,7 @@
         <v>63</v>
       </c>
       <c r="S171" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="T171"/>
       <c r="U171"/>
@@ -16538,14 +16532,14 @@
         <v>209</v>
       </c>
       <c r="B172" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="C172" t="s">
         <v>69</v>
       </c>
       <c r="D172"/>
       <c r="E172" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F172" t="s">
         <v>60</v>
@@ -16567,10 +16561,10 @@
         <v>59</v>
       </c>
       <c r="M172" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="N172" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="O172" t="s">
         <v>64</v>
@@ -16583,7 +16577,7 @@
         <v>63</v>
       </c>
       <c r="S172" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="T172"/>
       <c r="U172"/>
@@ -16600,14 +16594,14 @@
         <v>209</v>
       </c>
       <c r="B173" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="C173" t="s">
         <v>69</v>
       </c>
       <c r="D173"/>
       <c r="E173" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F173" t="s">
         <v>60</v>
@@ -16622,17 +16616,17 @@
         <v>102</v>
       </c>
       <c r="J173" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K173"/>
       <c r="L173" t="s">
         <v>59</v>
       </c>
       <c r="M173" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="N173" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="O173" t="s">
         <v>64</v>
@@ -16645,7 +16639,7 @@
         <v>63</v>
       </c>
       <c r="S173" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="T173"/>
       <c r="U173"/>
@@ -16662,14 +16656,14 @@
         <v>209</v>
       </c>
       <c r="B174" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="C174" t="s">
         <v>69</v>
       </c>
       <c r="D174"/>
       <c r="E174" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F174" t="s">
         <v>60</v>
@@ -16684,17 +16678,17 @@
         <v>102</v>
       </c>
       <c r="J174" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K174"/>
       <c r="L174" t="s">
         <v>59</v>
       </c>
       <c r="M174" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="N174" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="O174" t="s">
         <v>64</v>
@@ -16707,7 +16701,7 @@
         <v>63</v>
       </c>
       <c r="S174" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="T174"/>
       <c r="U174"/>
@@ -16724,14 +16718,14 @@
         <v>209</v>
       </c>
       <c r="B175" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="C175" t="s">
         <v>69</v>
       </c>
       <c r="D175"/>
       <c r="E175" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F175" t="s">
         <v>60</v>
@@ -16746,17 +16740,17 @@
         <v>102</v>
       </c>
       <c r="J175" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K175"/>
       <c r="L175" t="s">
         <v>59</v>
       </c>
       <c r="M175" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="N175" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="O175" t="s">
         <v>64</v>
@@ -16769,7 +16763,7 @@
         <v>63</v>
       </c>
       <c r="S175" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="T175"/>
       <c r="U175"/>
@@ -16786,14 +16780,14 @@
         <v>209</v>
       </c>
       <c r="B176" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="C176" t="s">
         <v>69</v>
       </c>
       <c r="D176"/>
       <c r="E176" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F176" t="s">
         <v>60</v>
@@ -16815,10 +16809,10 @@
         <v>59</v>
       </c>
       <c r="M176" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="N176" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="O176" t="s">
         <v>64</v>
@@ -16831,7 +16825,7 @@
         <v>63</v>
       </c>
       <c r="S176" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="T176"/>
       <c r="U176"/>
@@ -16848,14 +16842,14 @@
         <v>209</v>
       </c>
       <c r="B177" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="C177" t="s">
         <v>69</v>
       </c>
       <c r="D177"/>
       <c r="E177" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F177" t="s">
         <v>60</v>
@@ -16877,10 +16871,10 @@
         <v>59</v>
       </c>
       <c r="M177" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="N177" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="O177" t="s">
         <v>64</v>
@@ -16893,7 +16887,7 @@
         <v>63</v>
       </c>
       <c r="S177" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="T177"/>
       <c r="U177"/>
@@ -16910,14 +16904,14 @@
         <v>209</v>
       </c>
       <c r="B178" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="C178" t="s">
         <v>69</v>
       </c>
       <c r="D178"/>
       <c r="E178" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F178" t="s">
         <v>60</v>
@@ -16932,17 +16926,17 @@
         <v>102</v>
       </c>
       <c r="J178" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K178"/>
       <c r="L178" t="s">
         <v>59</v>
       </c>
       <c r="M178" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="N178" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="O178" t="s">
         <v>64</v>
@@ -16955,7 +16949,7 @@
         <v>63</v>
       </c>
       <c r="S178" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="T178"/>
       <c r="U178"/>
@@ -16972,14 +16966,14 @@
         <v>209</v>
       </c>
       <c r="B179" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="C179" t="s">
         <v>69</v>
       </c>
       <c r="D179"/>
       <c r="E179" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F179" t="s">
         <v>60</v>
@@ -16994,17 +16988,17 @@
         <v>102</v>
       </c>
       <c r="J179" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K179"/>
       <c r="L179" t="s">
         <v>59</v>
       </c>
       <c r="M179" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="N179" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="O179" t="s">
         <v>64</v>
@@ -17017,7 +17011,7 @@
         <v>63</v>
       </c>
       <c r="S179" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="T179"/>
       <c r="U179"/>
@@ -17034,14 +17028,14 @@
         <v>209</v>
       </c>
       <c r="B180" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="C180" t="s">
         <v>69</v>
       </c>
       <c r="D180"/>
       <c r="E180" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F180" t="s">
         <v>60</v>
@@ -17063,10 +17057,10 @@
         <v>59</v>
       </c>
       <c r="M180" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="N180" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="O180" t="s">
         <v>64</v>
@@ -17079,7 +17073,7 @@
         <v>63</v>
       </c>
       <c r="S180" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="T180"/>
       <c r="U180"/>
@@ -17096,14 +17090,14 @@
         <v>209</v>
       </c>
       <c r="B181" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="C181" t="s">
         <v>69</v>
       </c>
       <c r="D181"/>
       <c r="E181" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F181" t="s">
         <v>60</v>
@@ -17125,10 +17119,10 @@
         <v>59</v>
       </c>
       <c r="M181" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="N181" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="O181" t="s">
         <v>64</v>
@@ -17141,7 +17135,7 @@
         <v>63</v>
       </c>
       <c r="S181" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="T181"/>
       <c r="U181"/>
@@ -17158,14 +17152,14 @@
         <v>209</v>
       </c>
       <c r="B182" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C182" t="s">
         <v>69</v>
       </c>
       <c r="D182"/>
       <c r="E182" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F182" t="s">
         <v>60</v>
@@ -17187,10 +17181,10 @@
         <v>59</v>
       </c>
       <c r="M182" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="N182" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="O182" t="s">
         <v>64</v>
@@ -17203,7 +17197,7 @@
         <v>63</v>
       </c>
       <c r="S182" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="T182"/>
       <c r="U182"/>
@@ -17220,14 +17214,14 @@
         <v>209</v>
       </c>
       <c r="B183" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C183" t="s">
         <v>69</v>
       </c>
       <c r="D183"/>
       <c r="E183" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F183" t="s">
         <v>60</v>
@@ -17242,17 +17236,17 @@
         <v>102</v>
       </c>
       <c r="J183" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K183"/>
       <c r="L183" t="s">
         <v>59</v>
       </c>
       <c r="M183" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="N183" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="O183" t="s">
         <v>64</v>
@@ -17265,7 +17259,7 @@
         <v>63</v>
       </c>
       <c r="S183" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="T183"/>
       <c r="U183"/>
@@ -17282,14 +17276,14 @@
         <v>209</v>
       </c>
       <c r="B184" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="C184" t="s">
         <v>69</v>
       </c>
       <c r="D184"/>
       <c r="E184" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F184" t="s">
         <v>60</v>
@@ -17304,17 +17298,17 @@
         <v>102</v>
       </c>
       <c r="J184" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K184"/>
       <c r="L184" t="s">
         <v>59</v>
       </c>
       <c r="M184" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="N184" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="O184" t="s">
         <v>64</v>
@@ -17327,7 +17321,7 @@
         <v>63</v>
       </c>
       <c r="S184" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="T184"/>
       <c r="U184"/>
@@ -17344,14 +17338,14 @@
         <v>209</v>
       </c>
       <c r="B185" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="C185" t="s">
         <v>69</v>
       </c>
       <c r="D185"/>
       <c r="E185" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F185" t="s">
         <v>60</v>
@@ -17366,17 +17360,17 @@
         <v>102</v>
       </c>
       <c r="J185" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K185"/>
       <c r="L185" t="s">
         <v>59</v>
       </c>
       <c r="M185" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="N185" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="O185" t="s">
         <v>64</v>
@@ -17389,7 +17383,7 @@
         <v>63</v>
       </c>
       <c r="S185" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="T185"/>
       <c r="U185"/>
@@ -17406,14 +17400,14 @@
         <v>209</v>
       </c>
       <c r="B186" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="C186" t="s">
         <v>69</v>
       </c>
       <c r="D186"/>
       <c r="E186" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F186" t="s">
         <v>60</v>
@@ -17435,10 +17429,10 @@
         <v>59</v>
       </c>
       <c r="M186" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="N186" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="O186" t="s">
         <v>64</v>
@@ -17451,7 +17445,7 @@
         <v>63</v>
       </c>
       <c r="S186" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="T186"/>
       <c r="U186"/>
@@ -17468,14 +17462,14 @@
         <v>209</v>
       </c>
       <c r="B187" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="C187" t="s">
         <v>69</v>
       </c>
       <c r="D187"/>
       <c r="E187" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F187" t="s">
         <v>60</v>
@@ -17497,10 +17491,10 @@
         <v>59</v>
       </c>
       <c r="M187" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="N187" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="O187" t="s">
         <v>64</v>
@@ -17513,7 +17507,7 @@
         <v>63</v>
       </c>
       <c r="S187" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="T187"/>
       <c r="U187"/>
@@ -17530,14 +17524,14 @@
         <v>209</v>
       </c>
       <c r="B188" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="C188" t="s">
         <v>69</v>
       </c>
       <c r="D188"/>
       <c r="E188" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F188" t="s">
         <v>60</v>
@@ -17552,17 +17546,17 @@
         <v>102</v>
       </c>
       <c r="J188" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K188"/>
       <c r="L188" t="s">
         <v>59</v>
       </c>
       <c r="M188" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="N188" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="O188" t="s">
         <v>64</v>
@@ -17575,7 +17569,7 @@
         <v>63</v>
       </c>
       <c r="S188" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="T188"/>
       <c r="U188"/>
@@ -17592,14 +17586,14 @@
         <v>209</v>
       </c>
       <c r="B189" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="C189" t="s">
         <v>69</v>
       </c>
       <c r="D189"/>
       <c r="E189" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F189" t="s">
         <v>60</v>
@@ -17614,17 +17608,17 @@
         <v>102</v>
       </c>
       <c r="J189" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="K189"/>
       <c r="L189" t="s">
         <v>59</v>
       </c>
       <c r="M189" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="N189" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="O189" t="s">
         <v>64</v>
@@ -17637,7 +17631,7 @@
         <v>63</v>
       </c>
       <c r="S189" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="T189"/>
       <c r="U189"/>
@@ -17654,14 +17648,14 @@
         <v>209</v>
       </c>
       <c r="B190" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="C190" t="s">
         <v>69</v>
       </c>
       <c r="D190"/>
       <c r="E190" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F190" t="s">
         <v>60</v>
@@ -17683,10 +17677,10 @@
         <v>59</v>
       </c>
       <c r="M190" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="N190" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="O190" t="s">
         <v>64</v>
@@ -17699,7 +17693,7 @@
         <v>63</v>
       </c>
       <c r="S190" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="T190"/>
       <c r="U190"/>
@@ -17716,7 +17710,7 @@
         <v>209</v>
       </c>
       <c r="B191" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C191" t="s">
         <v>69</v>
@@ -17745,10 +17739,10 @@
         <v>59</v>
       </c>
       <c r="M191" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="N191" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="O191" t="s">
         <v>64</v>
@@ -17761,7 +17755,7 @@
         <v>63</v>
       </c>
       <c r="S191" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="T191"/>
       <c r="U191"/>
@@ -17778,7 +17772,7 @@
         <v>209</v>
       </c>
       <c r="B192" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="C192" t="s">
         <v>69</v>
@@ -17807,10 +17801,10 @@
         <v>59</v>
       </c>
       <c r="M192" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="N192" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="O192" t="s">
         <v>64</v>
@@ -17823,7 +17817,7 @@
         <v>63</v>
       </c>
       <c r="S192" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="T192"/>
       <c r="U192"/>
@@ -17840,7 +17834,7 @@
         <v>209</v>
       </c>
       <c r="B193" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="C193" t="s">
         <v>69</v>
@@ -17862,17 +17856,17 @@
         <v>102</v>
       </c>
       <c r="J193" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K193"/>
       <c r="L193" t="s">
         <v>59</v>
       </c>
       <c r="M193" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="N193" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="O193" t="s">
         <v>64</v>
@@ -17885,7 +17879,7 @@
         <v>63</v>
       </c>
       <c r="S193" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="T193"/>
       <c r="U193"/>
@@ -17902,7 +17896,7 @@
         <v>209</v>
       </c>
       <c r="B194" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C194" t="s">
         <v>69</v>
@@ -17931,10 +17925,10 @@
         <v>59</v>
       </c>
       <c r="M194" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="N194" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="O194" t="s">
         <v>64</v>
@@ -17947,7 +17941,7 @@
         <v>63</v>
       </c>
       <c r="S194" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="T194"/>
       <c r="U194"/>
@@ -17964,7 +17958,7 @@
         <v>209</v>
       </c>
       <c r="B195" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="C195" t="s">
         <v>69</v>
@@ -17993,10 +17987,10 @@
         <v>59</v>
       </c>
       <c r="M195" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="N195" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="O195" t="s">
         <v>64</v>
@@ -18009,7 +18003,7 @@
         <v>63</v>
       </c>
       <c r="S195" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="T195"/>
       <c r="U195"/>
@@ -18026,7 +18020,7 @@
         <v>209</v>
       </c>
       <c r="B196" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="C196" t="s">
         <v>69</v>
@@ -18048,17 +18042,17 @@
         <v>102</v>
       </c>
       <c r="J196" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K196"/>
       <c r="L196" t="s">
         <v>59</v>
       </c>
       <c r="M196" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="N196" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="O196" t="s">
         <v>64</v>
@@ -18071,7 +18065,7 @@
         <v>63</v>
       </c>
       <c r="S196" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="T196"/>
       <c r="U196"/>
@@ -18088,7 +18082,7 @@
         <v>209</v>
       </c>
       <c r="B197" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="C197" t="s">
         <v>69</v>
@@ -18117,10 +18111,10 @@
         <v>59</v>
       </c>
       <c r="M197" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="N197" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="O197" t="s">
         <v>64</v>
@@ -18133,7 +18127,7 @@
         <v>63</v>
       </c>
       <c r="S197" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="T197"/>
       <c r="U197"/>
@@ -18150,7 +18144,7 @@
         <v>209</v>
       </c>
       <c r="B198" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="C198" t="s">
         <v>69</v>
@@ -18179,10 +18173,10 @@
         <v>59</v>
       </c>
       <c r="M198" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="N198" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="O198" t="s">
         <v>64</v>
@@ -18195,7 +18189,7 @@
         <v>63</v>
       </c>
       <c r="S198" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="T198"/>
       <c r="U198"/>
@@ -18212,7 +18206,7 @@
         <v>209</v>
       </c>
       <c r="B199" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="C199" t="s">
         <v>69</v>
@@ -18234,17 +18228,17 @@
         <v>102</v>
       </c>
       <c r="J199" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K199"/>
       <c r="L199" t="s">
         <v>59</v>
       </c>
       <c r="M199" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="N199" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="O199" t="s">
         <v>64</v>
@@ -18257,7 +18251,7 @@
         <v>63</v>
       </c>
       <c r="S199" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="T199"/>
       <c r="U199"/>
@@ -18274,7 +18268,7 @@
         <v>209</v>
       </c>
       <c r="B200" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="C200" t="s">
         <v>69</v>
@@ -18303,10 +18297,10 @@
         <v>59</v>
       </c>
       <c r="M200" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="N200" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="O200" t="s">
         <v>64</v>
@@ -18319,7 +18313,7 @@
         <v>63</v>
       </c>
       <c r="S200" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="T200"/>
       <c r="U200"/>
@@ -18336,7 +18330,7 @@
         <v>209</v>
       </c>
       <c r="B201" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="C201" t="s">
         <v>69</v>
@@ -18365,10 +18359,10 @@
         <v>59</v>
       </c>
       <c r="M201" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="N201" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="O201" t="s">
         <v>64</v>
@@ -18381,7 +18375,7 @@
         <v>63</v>
       </c>
       <c r="S201" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="T201"/>
       <c r="U201"/>
@@ -18398,7 +18392,7 @@
         <v>209</v>
       </c>
       <c r="B202" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="C202" t="s">
         <v>69</v>
@@ -18420,17 +18414,17 @@
         <v>102</v>
       </c>
       <c r="J202" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K202"/>
       <c r="L202" t="s">
         <v>59</v>
       </c>
       <c r="M202" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="N202" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="O202" t="s">
         <v>64</v>
@@ -18443,7 +18437,7 @@
         <v>63</v>
       </c>
       <c r="S202" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="T202"/>
       <c r="U202"/>
@@ -18460,7 +18454,7 @@
         <v>209</v>
       </c>
       <c r="B203" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="C203" t="s">
         <v>69</v>
@@ -18489,10 +18483,10 @@
         <v>59</v>
       </c>
       <c r="M203" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="N203" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="O203" t="s">
         <v>64</v>
@@ -18505,7 +18499,7 @@
         <v>63</v>
       </c>
       <c r="S203" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="T203"/>
       <c r="U203"/>
@@ -18522,7 +18516,7 @@
         <v>209</v>
       </c>
       <c r="B204" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="C204" t="s">
         <v>69</v>
@@ -18551,10 +18545,10 @@
         <v>59</v>
       </c>
       <c r="M204" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="N204" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="O204" t="s">
         <v>64</v>
@@ -18567,7 +18561,7 @@
         <v>63</v>
       </c>
       <c r="S204" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="T204"/>
       <c r="U204"/>
@@ -18584,7 +18578,7 @@
         <v>209</v>
       </c>
       <c r="B205" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="C205" t="s">
         <v>69</v>
@@ -18606,17 +18600,17 @@
         <v>102</v>
       </c>
       <c r="J205" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K205"/>
       <c r="L205" t="s">
         <v>59</v>
       </c>
       <c r="M205" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="N205" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="O205" t="s">
         <v>64</v>
@@ -18629,7 +18623,7 @@
         <v>63</v>
       </c>
       <c r="S205" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="T205"/>
       <c r="U205"/>
@@ -18646,7 +18640,7 @@
         <v>209</v>
       </c>
       <c r="B206" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="C206" t="s">
         <v>69</v>
@@ -18675,10 +18669,10 @@
         <v>59</v>
       </c>
       <c r="M206" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="N206" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="O206" t="s">
         <v>64</v>
@@ -18691,7 +18685,7 @@
         <v>63</v>
       </c>
       <c r="S206" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="T206"/>
       <c r="U206"/>
@@ -18708,7 +18702,7 @@
         <v>209</v>
       </c>
       <c r="B207" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="C207" t="s">
         <v>69</v>
@@ -18737,10 +18731,10 @@
         <v>59</v>
       </c>
       <c r="M207" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="N207" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="O207" t="s">
         <v>64</v>
@@ -18753,7 +18747,7 @@
         <v>63</v>
       </c>
       <c r="S207" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="T207"/>
       <c r="U207"/>
@@ -18770,7 +18764,7 @@
         <v>209</v>
       </c>
       <c r="B208" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="C208" t="s">
         <v>69</v>
@@ -18792,17 +18786,17 @@
         <v>102</v>
       </c>
       <c r="J208" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K208"/>
       <c r="L208" t="s">
         <v>59</v>
       </c>
       <c r="M208" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="N208" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="O208" t="s">
         <v>64</v>
@@ -18815,7 +18809,7 @@
         <v>63</v>
       </c>
       <c r="S208" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="T208"/>
       <c r="U208"/>
@@ -18832,7 +18826,7 @@
         <v>209</v>
       </c>
       <c r="B209" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="C209" t="s">
         <v>69</v>
@@ -18861,10 +18855,10 @@
         <v>59</v>
       </c>
       <c r="M209" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="N209" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="O209" t="s">
         <v>64</v>
@@ -18877,7 +18871,7 @@
         <v>63</v>
       </c>
       <c r="S209" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="T209"/>
       <c r="U209"/>
@@ -18894,7 +18888,7 @@
         <v>209</v>
       </c>
       <c r="B210" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="C210" t="s">
         <v>69</v>
@@ -18923,10 +18917,10 @@
         <v>59</v>
       </c>
       <c r="M210" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="N210" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="O210" t="s">
         <v>64</v>
@@ -18939,7 +18933,7 @@
         <v>63</v>
       </c>
       <c r="S210" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="T210"/>
       <c r="U210"/>
@@ -18956,7 +18950,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C211" t="s">
         <v>69</v>
@@ -18978,17 +18972,17 @@
         <v>102</v>
       </c>
       <c r="J211" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K211"/>
       <c r="L211" t="s">
         <v>59</v>
       </c>
       <c r="M211" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="N211" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="O211" t="s">
         <v>64</v>
@@ -19001,7 +18995,7 @@
         <v>63</v>
       </c>
       <c r="S211" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="T211"/>
       <c r="U211"/>
@@ -19018,7 +19012,7 @@
         <v>209</v>
       </c>
       <c r="B212" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="C212" t="s">
         <v>69</v>
@@ -19047,10 +19041,10 @@
         <v>59</v>
       </c>
       <c r="M212" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="N212" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="O212" t="s">
         <v>64</v>
@@ -19063,7 +19057,7 @@
         <v>63</v>
       </c>
       <c r="S212" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="T212"/>
       <c r="U212"/>
@@ -19080,7 +19074,7 @@
         <v>209</v>
       </c>
       <c r="B213" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="C213" t="s">
         <v>69</v>
@@ -19109,10 +19103,10 @@
         <v>59</v>
       </c>
       <c r="M213" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="N213" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="O213" t="s">
         <v>64</v>
@@ -19125,7 +19119,7 @@
         <v>63</v>
       </c>
       <c r="S213" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="T213"/>
       <c r="U213"/>
@@ -19142,7 +19136,7 @@
         <v>209</v>
       </c>
       <c r="B214" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="C214" t="s">
         <v>69</v>
@@ -19164,17 +19158,17 @@
         <v>102</v>
       </c>
       <c r="J214" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K214"/>
       <c r="L214" t="s">
         <v>59</v>
       </c>
       <c r="M214" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="N214" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="O214" t="s">
         <v>64</v>
@@ -19187,7 +19181,7 @@
         <v>63</v>
       </c>
       <c r="S214" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="T214"/>
       <c r="U214"/>
@@ -19204,7 +19198,7 @@
         <v>209</v>
       </c>
       <c r="B215" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C215" t="s">
         <v>69</v>
@@ -19233,10 +19227,10 @@
         <v>59</v>
       </c>
       <c r="M215" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="N215" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="O215" t="s">
         <v>64</v>
@@ -19249,7 +19243,7 @@
         <v>63</v>
       </c>
       <c r="S215" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="T215"/>
       <c r="U215"/>
@@ -19266,7 +19260,7 @@
         <v>209</v>
       </c>
       <c r="B216" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C216" t="s">
         <v>69</v>
@@ -19295,10 +19289,10 @@
         <v>59</v>
       </c>
       <c r="M216" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="N216" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="O216" t="s">
         <v>64</v>
@@ -19311,7 +19305,7 @@
         <v>63</v>
       </c>
       <c r="S216" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="T216"/>
       <c r="U216"/>
@@ -19328,7 +19322,7 @@
         <v>209</v>
       </c>
       <c r="B217" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="C217" t="s">
         <v>69</v>
@@ -19350,17 +19344,17 @@
         <v>102</v>
       </c>
       <c r="J217" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K217"/>
       <c r="L217" t="s">
         <v>59</v>
       </c>
       <c r="M217" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="N217" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="O217" t="s">
         <v>64</v>
@@ -19373,7 +19367,7 @@
         <v>63</v>
       </c>
       <c r="S217" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="T217"/>
       <c r="U217"/>
@@ -19390,7 +19384,7 @@
         <v>209</v>
       </c>
       <c r="B218" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="C218" t="s">
         <v>69</v>
@@ -19419,10 +19413,10 @@
         <v>59</v>
       </c>
       <c r="M218" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="N218" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="O218" t="s">
         <v>64</v>
@@ -19435,7 +19429,7 @@
         <v>63</v>
       </c>
       <c r="S218" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="T218"/>
       <c r="U218"/>
@@ -19452,7 +19446,7 @@
         <v>209</v>
       </c>
       <c r="B219" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="C219" t="s">
         <v>69</v>
@@ -19481,10 +19475,10 @@
         <v>59</v>
       </c>
       <c r="M219" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="N219" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="O219" t="s">
         <v>64</v>
@@ -19497,7 +19491,7 @@
         <v>63</v>
       </c>
       <c r="S219" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="T219"/>
       <c r="U219"/>
@@ -19514,7 +19508,7 @@
         <v>209</v>
       </c>
       <c r="B220" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="C220" t="s">
         <v>69</v>
@@ -19536,17 +19530,17 @@
         <v>102</v>
       </c>
       <c r="J220" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K220"/>
       <c r="L220" t="s">
         <v>59</v>
       </c>
       <c r="M220" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="N220" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="O220" t="s">
         <v>64</v>
@@ -19559,7 +19553,7 @@
         <v>63</v>
       </c>
       <c r="S220" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="T220"/>
       <c r="U220"/>
